--- a/chapters/CH06/registry/CH06_registry_v0.1_current.xlsx
+++ b/chapters/CH06/registry/CH06_registry_v0.1_current.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Блоки" sheetId="1" r:id="R12edb68482ba4adc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Блоки" sheetId="1" r:id="Rc9a1de05815b4812"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8533,7 +8533,9 @@
       <x:c r="J82" s="2" t="str">
         <x:v>Mechanism</x:v>
       </x:c>
-      <x:c r="K82" s="2"/>
+      <x:c r="K82" s="2" t="str">
+        <x:v>Механизм</x:v>
+      </x:c>
       <x:c r="L82" s="2" t="str">
         <x:v>&lt;th xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-head" scope="col"&gt;
        &lt;p class="normal"&gt;
@@ -8546,7 +8548,18 @@
       &lt;/th&gt;
       </x:v>
       </x:c>
-      <x:c r="M82" s="2"/>
+      <x:c r="M82" s="2" t="str">
+        <x:v>&lt;th xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-head" scope="col"&gt;
+       &lt;p class="normal"&gt;
+        &lt;strong class="keyWord"&gt;
+         &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.223.1"&gt;
+          Механизм
+         &lt;/span&gt;
+        &lt;/strong&gt;
+       &lt;/p&gt;
+      &lt;/th&gt;
+      </x:v>
+      </x:c>
       <x:c r="N82" s="2"/>
       <x:c r="O82" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -8559,29 +8572,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U82" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V82" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W82" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X82" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y82" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z82" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA82" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB82" s="2"/>
+      <x:c r="AB82" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC82" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -8613,7 +8628,9 @@
       <x:c r="J83" s="2" t="str">
         <x:v>Durability</x:v>
       </x:c>
-      <x:c r="K83" s="2"/>
+      <x:c r="K83" s="2" t="str">
+        <x:v>Устойчивость</x:v>
+      </x:c>
       <x:c r="L83" s="2" t="str">
         <x:v>&lt;th xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-head" scope="col"&gt;
        &lt;p class="normal"&gt;
@@ -8626,7 +8643,18 @@
       &lt;/th&gt;
       </x:v>
       </x:c>
-      <x:c r="M83" s="2"/>
+      <x:c r="M83" s="2" t="str">
+        <x:v>&lt;th xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-head" scope="col"&gt;
+       &lt;p class="normal"&gt;
+        &lt;strong class="keyWord"&gt;
+         &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.224.1"&gt;
+          Устойчивость
+         &lt;/span&gt;
+        &lt;/strong&gt;
+       &lt;/p&gt;
+      &lt;/th&gt;
+      </x:v>
+      </x:c>
       <x:c r="N83" s="2"/>
       <x:c r="O83" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -8639,29 +8667,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U83" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V83" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W83" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X83" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y83" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z83" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA83" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB83" s="2"/>
+      <x:c r="AB83" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC83" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -8693,7 +8723,9 @@
       <x:c r="J84" s="2" t="str">
         <x:v>ML4T examples</x:v>
       </x:c>
-      <x:c r="K84" s="2"/>
+      <x:c r="K84" s="2" t="str">
+        <x:v>Примеры в ML4T</x:v>
+      </x:c>
       <x:c r="L84" s="2" t="str">
         <x:v>&lt;th xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-head" scope="col"&gt;
        &lt;p class="normal"&gt;
@@ -8706,7 +8738,18 @@
       &lt;/th&gt;
      </x:v>
       </x:c>
-      <x:c r="M84" s="2"/>
+      <x:c r="M84" s="2" t="str">
+        <x:v>&lt;th xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-head" scope="col"&gt;
+       &lt;p class="normal"&gt;
+        &lt;strong class="keyWord"&gt;
+         &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.225.1"&gt;
+          Примеры в ML4T
+         &lt;/span&gt;
+        &lt;/strong&gt;
+       &lt;/p&gt;
+      &lt;/th&gt;
+     </x:v>
+      </x:c>
       <x:c r="N84" s="2"/>
       <x:c r="O84" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -8719,29 +8762,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U84" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V84" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W84" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X84" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y84" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z84" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA84" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB84" s="2"/>
+      <x:c r="AB84" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC84" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -8773,7 +8818,9 @@
       <x:c r="J85" s="2" t="str">
         <x:v>Risk compensation</x:v>
       </x:c>
-      <x:c r="K85" s="2"/>
+      <x:c r="K85" s="2" t="str">
+        <x:v>Компенсация за риск</x:v>
+      </x:c>
       <x:c r="L85" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -8784,7 +8831,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M85" s="2"/>
+      <x:c r="M85" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.226.1"&gt;
+         Компенсация за риск
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N85" s="2"/>
       <x:c r="O85" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -8795,29 +8851,31 @@
       <x:c r="S85" s="2"/>
       <x:c r="T85" s="2"/>
       <x:c r="U85" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V85" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W85" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X85" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y85" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z85" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA85" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB85" s="2"/>
+      <x:c r="AB85" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC85" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -8841,15 +8899,17 @@
       </x:c>
       <x:c r="G86" s="2"/>
       <x:c r="H86" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="I86" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="J86" s="2" t="str">
         <x:v>Bearing exposures others avoid (tail, volatility, illiquidity risk)</x:v>
       </x:c>
-      <x:c r="K86" s="2"/>
+      <x:c r="K86" s="2" t="str">
+        <x:v>Принятие на себя факторов риска, которых избегают другие (хвостовой риск, риск волатильности, риск неликвидности)</x:v>
+      </x:c>
       <x:c r="L86" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -8860,7 +8920,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M86" s="2"/>
+      <x:c r="M86" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.227.1"&gt;
+         Принятие на себя факторов риска, которых избегают другие (хвостовой риск, риск волатильности, риск неликвидности)
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N86" s="2"/>
       <x:c r="O86" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -8871,29 +8940,31 @@
       <x:c r="S86" s="2"/>
       <x:c r="T86" s="2"/>
       <x:c r="U86" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V86" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W86" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X86" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y86" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z86" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA86" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB86" s="2"/>
+      <x:c r="AB86" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 170/129; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC86" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -8917,15 +8988,17 @@
       </x:c>
       <x:c r="G87" s="2"/>
       <x:c r="H87" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="I87" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="J87" s="2" t="str">
         <x:v>High — persists as long as investors are risk averse</x:v>
       </x:c>
-      <x:c r="K87" s="2"/>
+      <x:c r="K87" s="2" t="str">
+        <x:v>Высокая — сохраняется, пока инвесторы избегают риска</x:v>
+      </x:c>
       <x:c r="L87" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -8936,7 +9009,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M87" s="2"/>
+      <x:c r="M87" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.228.1"&gt;
+         Высокая — сохраняется, пока инвесторы избегают риска
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N87" s="2"/>
       <x:c r="O87" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -8947,29 +9029,31 @@
       <x:c r="S87" s="2"/>
       <x:c r="T87" s="2"/>
       <x:c r="U87" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V87" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W87" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X87" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y87" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z87" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA87" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB87" s="2"/>
+      <x:c r="AB87" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 170/129; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC87" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -8993,15 +9077,17 @@
       </x:c>
       <x:c r="G88" s="2"/>
       <x:c r="H88" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="I88" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="J88" s="2" t="str">
         <x:v>cme_futures carry, sp500_options volatility risk premium</x:v>
       </x:c>
-      <x:c r="K88" s="2"/>
+      <x:c r="K88" s="2" t="str">
+        <x:v>кэрри в cme_futures, премия за риск волатильности в sp500_options</x:v>
+      </x:c>
       <x:c r="L88" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -9012,7 +9098,16 @@
       &lt;/td&gt;
      </x:v>
       </x:c>
-      <x:c r="M88" s="2"/>
+      <x:c r="M88" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.229.1"&gt;
+         кэрри в cme_futures, премия за риск волатильности в sp500_options
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+     </x:v>
+      </x:c>
       <x:c r="N88" s="2"/>
       <x:c r="O88" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -9023,29 +9118,31 @@
       <x:c r="S88" s="2"/>
       <x:c r="T88" s="2"/>
       <x:c r="U88" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V88" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W88" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X88" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y88" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z88" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA88" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB88" s="2"/>
+      <x:c r="AB88" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 170/129; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC88" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -9077,7 +9174,9 @@
       <x:c r="J89" s="2" t="str">
         <x:v>Liquidity provision</x:v>
       </x:c>
-      <x:c r="K89" s="2"/>
+      <x:c r="K89" s="2" t="str">
+        <x:v>Предоставление ликвидности</x:v>
+      </x:c>
       <x:c r="L89" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -9088,7 +9187,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M89" s="2"/>
+      <x:c r="M89" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.230.1"&gt;
+         Предоставление ликвидности
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N89" s="2"/>
       <x:c r="O89" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -9099,29 +9207,31 @@
       <x:c r="S89" s="2"/>
       <x:c r="T89" s="2"/>
       <x:c r="U89" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V89" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W89" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X89" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y89" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z89" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA89" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB89" s="2"/>
+      <x:c r="AB89" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC89" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -9145,15 +9255,17 @@
       </x:c>
       <x:c r="G90" s="2"/>
       <x:c r="H90" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="I90" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="J90" s="2" t="str">
         <x:v>Earning a premium for supplying immediacy or absorbing inventory</x:v>
       </x:c>
-      <x:c r="K90" s="2"/>
+      <x:c r="K90" s="2" t="str">
+        <x:v>Получение премии за обеспечение немедленного исполнения или принятие позиций на баланс</x:v>
+      </x:c>
       <x:c r="L90" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -9164,7 +9276,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M90" s="2"/>
+      <x:c r="M90" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.231.1"&gt;
+         Получение премии за обеспечение немедленного исполнения или принятие позиций на баланс
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N90" s="2"/>
       <x:c r="O90" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -9175,29 +9296,31 @@
       <x:c r="S90" s="2"/>
       <x:c r="T90" s="2"/>
       <x:c r="U90" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V90" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W90" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X90" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y90" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z90" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA90" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB90" s="2"/>
+      <x:c r="AB90" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 170/129; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC90" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -9221,15 +9344,17 @@
       </x:c>
       <x:c r="G91" s="2"/>
       <x:c r="H91" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="I91" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="J91" s="2" t="str">
         <x:v>High — structural demand for immediacy</x:v>
       </x:c>
-      <x:c r="K91" s="2"/>
+      <x:c r="K91" s="2" t="str">
+        <x:v>Высокая — структурный спрос на немедленное исполнение</x:v>
+      </x:c>
       <x:c r="L91" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -9240,7 +9365,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M91" s="2"/>
+      <x:c r="M91" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.232.1"&gt;
+         Высокая — структурный спрос на немедленное исполнение
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N91" s="2"/>
       <x:c r="O91" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -9251,29 +9385,31 @@
       <x:c r="S91" s="2"/>
       <x:c r="T91" s="2"/>
       <x:c r="U91" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V91" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W91" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X91" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y91" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z91" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA91" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB91" s="2"/>
+      <x:c r="AB91" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 170/129; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC91" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -9297,15 +9433,17 @@
       </x:c>
       <x:c r="G92" s="2"/>
       <x:c r="H92" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="I92" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="J92" s="2" t="str">
         <x:v>nasdaq100_microstructure intraday reversals</x:v>
       </x:c>
-      <x:c r="K92" s="2"/>
+      <x:c r="K92" s="2" t="str">
+        <x:v>внутридневные развороты в nasdaq100_microstructure</x:v>
+      </x:c>
       <x:c r="L92" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -9316,7 +9454,16 @@
       &lt;/td&gt;
      </x:v>
       </x:c>
-      <x:c r="M92" s="2"/>
+      <x:c r="M92" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.233.1"&gt;
+         внутридневные развороты в nasdaq100_microstructure
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+     </x:v>
+      </x:c>
       <x:c r="N92" s="2"/>
       <x:c r="O92" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -9327,29 +9474,31 @@
       <x:c r="S92" s="2"/>
       <x:c r="T92" s="2"/>
       <x:c r="U92" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V92" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W92" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X92" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y92" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z92" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA92" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB92" s="2"/>
+      <x:c r="AB92" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 170/129; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC92" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -9381,7 +9530,9 @@
       <x:c r="J93" s="2" t="str">
         <x:v>Funding constraints</x:v>
       </x:c>
-      <x:c r="K93" s="2"/>
+      <x:c r="K93" s="2" t="str">
+        <x:v>Ограничения финансирования</x:v>
+      </x:c>
       <x:c r="L93" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -9392,7 +9543,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M93" s="2"/>
+      <x:c r="M93" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.234.1"&gt;
+         Ограничения финансирования
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N93" s="2"/>
       <x:c r="O93" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -9403,29 +9563,31 @@
       <x:c r="S93" s="2"/>
       <x:c r="T93" s="2"/>
       <x:c r="U93" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V93" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W93" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X93" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y93" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z93" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA93" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB93" s="2"/>
+      <x:c r="AB93" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC93" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -9449,15 +9611,17 @@
       </x:c>
       <x:c r="G94" s="2"/>
       <x:c r="H94" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="I94" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="J94" s="2" t="str">
         <x:v>Exploiting dislocations when capital is scarce or leverage is restricted</x:v>
       </x:c>
-      <x:c r="K94" s="2"/>
+      <x:c r="K94" s="2" t="str">
+        <x:v>Использование ценовых отклонений в условиях дефицита капитала или ограничения кредитного плеча</x:v>
+      </x:c>
       <x:c r="L94" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -9468,7 +9632,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M94" s="2"/>
+      <x:c r="M94" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.235.1"&gt;
+         Использование ценовых отклонений в условиях дефицита капитала или ограничения кредитного плеча
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N94" s="2"/>
       <x:c r="O94" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -9479,29 +9652,31 @@
       <x:c r="S94" s="2"/>
       <x:c r="T94" s="2"/>
       <x:c r="U94" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V94" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W94" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X94" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y94" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z94" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA94" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB94" s="2"/>
+      <x:c r="AB94" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 170/129; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC94" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -9525,15 +9700,17 @@
       </x:c>
       <x:c r="G95" s="2"/>
       <x:c r="H95" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="I95" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="J95" s="2" t="str">
         <x:v>Moderate — episodic, strongest during stress</x:v>
       </x:c>
-      <x:c r="K95" s="2"/>
+      <x:c r="K95" s="2" t="str">
+        <x:v>Умеренная — проявляется эпизодически и наиболее сильна в периоды стресса</x:v>
+      </x:c>
       <x:c r="L95" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -9544,7 +9721,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M95" s="2"/>
+      <x:c r="M95" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.236.1"&gt;
+         Умеренная — проявляется эпизодически и наиболее сильна в периоды стресса
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N95" s="2"/>
       <x:c r="O95" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -9555,29 +9741,31 @@
       <x:c r="S95" s="2"/>
       <x:c r="T95" s="2"/>
       <x:c r="U95" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V95" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W95" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X95" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y95" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z95" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA95" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB95" s="2"/>
+      <x:c r="AB95" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 170/129; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC95" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -9601,15 +9789,17 @@
       </x:c>
       <x:c r="G96" s="2"/>
       <x:c r="H96" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="I96" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="J96" s="2" t="str">
         <x:v>Short-horizon mean reversion after forced liquidations</x:v>
       </x:c>
-      <x:c r="K96" s="2"/>
+      <x:c r="K96" s="2" t="str">
+        <x:v>Краткосрочный возврат к среднему после вынужденных ликвидаций</x:v>
+      </x:c>
       <x:c r="L96" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -9620,7 +9810,16 @@
       &lt;/td&gt;
      </x:v>
       </x:c>
-      <x:c r="M96" s="2"/>
+      <x:c r="M96" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.237.1"&gt;
+         Краткосрочный возврат к среднему после вынужденных ликвидаций
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+     </x:v>
+      </x:c>
       <x:c r="N96" s="2"/>
       <x:c r="O96" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -9631,29 +9830,31 @@
       <x:c r="S96" s="2"/>
       <x:c r="T96" s="2"/>
       <x:c r="U96" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V96" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W96" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X96" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y96" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z96" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA96" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB96" s="2"/>
+      <x:c r="AB96" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 170/129; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC96" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -9685,7 +9886,9 @@
       <x:c r="J97" s="2" t="str">
         <x:v>Flow predictability</x:v>
       </x:c>
-      <x:c r="K97" s="2"/>
+      <x:c r="K97" s="2" t="str">
+        <x:v>Предсказуемость потоков</x:v>
+      </x:c>
       <x:c r="L97" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -9696,7 +9899,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M97" s="2"/>
+      <x:c r="M97" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.238.1"&gt;
+         Предсказуемость потоков
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N97" s="2"/>
       <x:c r="O97" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -9707,29 +9919,31 @@
       <x:c r="S97" s="2"/>
       <x:c r="T97" s="2"/>
       <x:c r="U97" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V97" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W97" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X97" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y97" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z97" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA97" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB97" s="2"/>
+      <x:c r="AB97" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC97" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -9761,7 +9975,9 @@
       <x:c r="J98" s="2" t="str">
         <x:v>Front-positioning around mandated or rules-based demand (index rebalancing, hedging programs)</x:v>
       </x:c>
-      <x:c r="K98" s="2"/>
+      <x:c r="K98" s="2" t="str">
+        <x:v>Заблаговременное открытие позиций в ожидании обязательного или основанного на правилах спроса (ребалансировка индексов, программы хеджирования)</x:v>
+      </x:c>
       <x:c r="L98" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -9772,7 +9988,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M98" s="2"/>
+      <x:c r="M98" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.239.1"&gt;
+         Заблаговременное открытие позиций в ожидании обязательного или основанного на правилах спроса (ребалансировка индексов, программы хеджирования)
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N98" s="2"/>
       <x:c r="O98" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -9783,29 +10008,31 @@
       <x:c r="S98" s="2"/>
       <x:c r="T98" s="2"/>
       <x:c r="U98" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V98" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W98" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X98" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y98" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z98" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA98" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB98" s="2"/>
+      <x:c r="AB98" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC98" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -9829,15 +10056,17 @@
       </x:c>
       <x:c r="G99" s="2"/>
       <x:c r="H99" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I99" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="J99" s="2" t="str">
         <x:v>Moderate — erodes with crowding but recurs with each event</x:v>
       </x:c>
-      <x:c r="K99" s="2"/>
+      <x:c r="K99" s="2" t="str">
+        <x:v>Умеренная — ослабевает по мере притока участников, но повторяется при каждом событии</x:v>
+      </x:c>
       <x:c r="L99" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -9848,7 +10077,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M99" s="2"/>
+      <x:c r="M99" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.240.1"&gt;
+         Умеренная — ослабевает по мере притока участников, но повторяется при каждом событии
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N99" s="2"/>
       <x:c r="O99" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -9859,29 +10097,31 @@
       <x:c r="S99" s="2"/>
       <x:c r="T99" s="2"/>
       <x:c r="U99" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V99" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W99" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X99" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y99" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z99" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA99" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB99" s="2"/>
+      <x:c r="AB99" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 171/130; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC99" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -9905,15 +10145,17 @@
       </x:c>
       <x:c r="G100" s="2"/>
       <x:c r="H100" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I100" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="J100" s="2" t="str">
         <x:v>Index reconstitution trades, ETF creation/redemption flows</x:v>
       </x:c>
-      <x:c r="K100" s="2"/>
+      <x:c r="K100" s="2" t="str">
+        <x:v>Сделки при пересмотре состава индексов, потоки создания и погашения ETF</x:v>
+      </x:c>
       <x:c r="L100" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -9924,7 +10166,16 @@
       &lt;/td&gt;
      </x:v>
       </x:c>
-      <x:c r="M100" s="2"/>
+      <x:c r="M100" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.241.1"&gt;
+         Сделки при пересмотре состава индексов, потоки создания и погашения ETF
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+     </x:v>
+      </x:c>
       <x:c r="N100" s="2"/>
       <x:c r="O100" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -9935,29 +10186,31 @@
       <x:c r="S100" s="2"/>
       <x:c r="T100" s="2"/>
       <x:c r="U100" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V100" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W100" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X100" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y100" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z100" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA100" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB100" s="2"/>
+      <x:c r="AB100" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 171/130; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC100" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -9981,15 +10234,17 @@
       </x:c>
       <x:c r="G101" s="2"/>
       <x:c r="H101" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I101" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="J101" s="2" t="str">
         <x:v>Informational advantage</x:v>
       </x:c>
-      <x:c r="K101" s="2"/>
+      <x:c r="K101" s="2" t="str">
+        <x:v>Информационное преимущество</x:v>
+      </x:c>
       <x:c r="L101" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -10000,7 +10255,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M101" s="2"/>
+      <x:c r="M101" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.242.1"&gt;
+         Информационное преимущество
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N101" s="2"/>
       <x:c r="O101" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -10011,29 +10275,31 @@
       <x:c r="S101" s="2"/>
       <x:c r="T101" s="2"/>
       <x:c r="U101" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V101" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W101" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X101" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y101" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z101" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA101" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB101" s="2"/>
+      <x:c r="AB101" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 171/130; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC101" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -10065,7 +10331,9 @@
       <x:c r="J102" s="2" t="str">
         <x:v>Better inference from public data: cleaner features, faster processing, superior models</x:v>
       </x:c>
-      <x:c r="K102" s="2"/>
+      <x:c r="K102" s="2" t="str">
+        <x:v>Более качественные выводы на основе общедоступных данных: более чистые признаки, более быстрая обработка, более совершенные модели</x:v>
+      </x:c>
       <x:c r="L102" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -10076,7 +10344,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M102" s="2"/>
+      <x:c r="M102" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.243.1"&gt;
+         Более качественные выводы на основе общедоступных данных: более чистые признаки, более быстрая обработка, более совершенные модели
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N102" s="2"/>
       <x:c r="O102" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -10087,29 +10364,31 @@
       <x:c r="S102" s="2"/>
       <x:c r="T102" s="2"/>
       <x:c r="U102" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V102" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W102" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X102" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y102" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z102" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA102" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB102" s="2"/>
+      <x:c r="AB102" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC102" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -10133,15 +10412,17 @@
       </x:c>
       <x:c r="G103" s="2"/>
       <x:c r="H103" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I103" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="J103" s="2" t="str">
         <x:v>Low to moderate — erodes as competitors replicate methods</x:v>
       </x:c>
-      <x:c r="K103" s="2"/>
+      <x:c r="K103" s="2" t="str">
+        <x:v>Низкая или умеренная — снижается по мере того, как конкуренты воспроизводят методы</x:v>
+      </x:c>
       <x:c r="L103" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -10152,7 +10433,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M103" s="2"/>
+      <x:c r="M103" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.244.1"&gt;
+         Низкая или умеренная — снижается по мере того, как конкуренты воспроизводят методы
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N103" s="2"/>
       <x:c r="O103" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -10163,29 +10453,31 @@
       <x:c r="S103" s="2"/>
       <x:c r="T103" s="2"/>
       <x:c r="U103" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V103" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W103" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X103" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y103" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z103" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA103" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB103" s="2"/>
+      <x:c r="AB103" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 171/130; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC103" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -10209,15 +10501,17 @@
       </x:c>
       <x:c r="G104" s="2"/>
       <x:c r="H104" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I104" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="J104" s="2" t="str">
         <x:v>ML-based feature engineering across case studies</x:v>
       </x:c>
-      <x:c r="K104" s="2"/>
+      <x:c r="K104" s="2" t="str">
+        <x:v>Конструирование признаков с помощью ML во всех практических примерах</x:v>
+      </x:c>
       <x:c r="L104" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -10228,7 +10522,16 @@
       &lt;/td&gt;
      </x:v>
       </x:c>
-      <x:c r="M104" s="2"/>
+      <x:c r="M104" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.245.1"&gt;
+         Конструирование признаков с помощью ML во всех практических примерах
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+     </x:v>
+      </x:c>
       <x:c r="N104" s="2"/>
       <x:c r="O104" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -10239,29 +10542,31 @@
       <x:c r="S104" s="2"/>
       <x:c r="T104" s="2"/>
       <x:c r="U104" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V104" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W104" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X104" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y104" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z104" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA104" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB104" s="2"/>
+      <x:c r="AB104" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 171/130; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC104" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -10293,7 +10598,9 @@
       <x:c r="J105" s="2" t="str">
         <x:v>Pure arbitrage</x:v>
       </x:c>
-      <x:c r="K105" s="2"/>
+      <x:c r="K105" s="2" t="str">
+        <x:v>Чистый арбитраж</x:v>
+      </x:c>
       <x:c r="L105" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -10304,7 +10611,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M105" s="2"/>
+      <x:c r="M105" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.246.1"&gt;
+         Чистый арбитраж
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N105" s="2"/>
       <x:c r="O105" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -10315,29 +10631,31 @@
       <x:c r="S105" s="2"/>
       <x:c r="T105" s="2"/>
       <x:c r="U105" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V105" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W105" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X105" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y105" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z105" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA105" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB105" s="2"/>
+      <x:c r="AB105" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC105" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -10361,15 +10679,17 @@
       </x:c>
       <x:c r="G106" s="2"/>
       <x:c r="H106" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I106" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="J106" s="2" t="str">
         <x:v>Exploiting identical-asset mispricing across venues or structures</x:v>
       </x:c>
-      <x:c r="K106" s="2"/>
+      <x:c r="K106" s="2" t="str">
+        <x:v>Использование расхождений в ценах идентичных активов на разных торговых площадках или в разных структурах</x:v>
+      </x:c>
       <x:c r="L106" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -10380,7 +10700,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M106" s="2"/>
+      <x:c r="M106" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.247.1"&gt;
+         Использование расхождений в ценах идентичных активов на разных торговых площадках или в разных структурах
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N106" s="2"/>
       <x:c r="O106" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -10391,29 +10720,31 @@
       <x:c r="S106" s="2"/>
       <x:c r="T106" s="2"/>
       <x:c r="U106" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V106" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W106" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X106" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y106" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z106" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA106" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB106" s="2"/>
+      <x:c r="AB106" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 171/130; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC106" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -10437,15 +10768,17 @@
       </x:c>
       <x:c r="G107" s="2"/>
       <x:c r="H107" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I107" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="J107" s="2" t="str">
         <x:v>Very low — fleeting, capacity-constrained, operationally intensive</x:v>
       </x:c>
-      <x:c r="K107" s="2"/>
+      <x:c r="K107" s="2" t="str">
+        <x:v>Очень низкая — кратковременна, ограничена ёмкостью стратегии и требует значительных операционных усилий</x:v>
+      </x:c>
       <x:c r="L107" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -10456,7 +10789,16 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M107" s="2"/>
+      <x:c r="M107" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.248.1"&gt;
+         Очень низкая — кратковременна, ограничена ёмкостью стратегии и требует значительных операционных усилий
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+      </x:v>
+      </x:c>
       <x:c r="N107" s="2"/>
       <x:c r="O107" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -10467,29 +10809,31 @@
       <x:c r="S107" s="2"/>
       <x:c r="T107" s="2"/>
       <x:c r="U107" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V107" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W107" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X107" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y107" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z107" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA107" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB107" s="2"/>
+      <x:c r="AB107" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 171/130; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC107" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -10513,15 +10857,17 @@
       </x:c>
       <x:c r="G108" s="2"/>
       <x:c r="H108" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I108" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="J108" s="2" t="str">
         <x:v>Not represented in our case studies</x:v>
       </x:c>
-      <x:c r="K108" s="2"/>
+      <x:c r="K108" s="2" t="str">
+        <x:v>Не представлен в наших практических примерах</x:v>
+      </x:c>
       <x:c r="L108" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -10532,7 +10878,16 @@
       &lt;/td&gt;
      </x:v>
       </x:c>
-      <x:c r="M108" s="2"/>
+      <x:c r="M108" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
+       &lt;p class="normal"&gt;
+        &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.249.1"&gt;
+         Не представлен в наших практических примерах
+        &lt;/span&gt;
+       &lt;/p&gt;
+      &lt;/td&gt;
+     </x:v>
+      </x:c>
       <x:c r="N108" s="2"/>
       <x:c r="O108" s="2" t="str">
         <x:v>CH06-TABLE-001</x:v>
@@ -10543,29 +10898,31 @@
       <x:c r="S108" s="2"/>
       <x:c r="T108" s="2"/>
       <x:c r="U108" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V108" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W108" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X108" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y108" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z108" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA108" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB108" s="2"/>
+      <x:c r="AB108" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 171/130; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC108" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -10597,7 +10954,9 @@
       <x:c r="J109" s="2" t="str">
         <x:v>Table 6.1: Comparing six sources of excess</x:v>
       </x:c>
-      <x:c r="K109" s="2"/>
+      <x:c r="K109" s="2" t="str">
+        <x:v>Таблица 6.1: Сравнение шести источников избыточной доходности</x:v>
+      </x:c>
       <x:c r="L109" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="packt_figref"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.250.1"&gt;
@@ -10606,7 +10965,14 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M109" s="2"/>
+      <x:c r="M109" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="packt_figref"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.250.1"&gt;
+     Таблица 6.1: Сравнение шести источников избыточной доходности
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N109" s="2"/>
       <x:c r="O109" s="2"/>
       <x:c r="P109" s="2"/>
@@ -10615,29 +10981,31 @@
       <x:c r="S109" s="2"/>
       <x:c r="T109" s="2"/>
       <x:c r="U109" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V109" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W109" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X109" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y109" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z109" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA109" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB109" s="2"/>
+      <x:c r="AB109" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC109" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -10669,7 +11037,9 @@
       <x:c r="J110" s="2" t="str">
         <x:v>The following subsections expand on several of these sources and related mechanisms. Most real strategies blend two or more; the table helps identify which ones anchor a thesis and which failure modes to test first.</x:v>
       </x:c>
-      <x:c r="K110" s="2"/>
+      <x:c r="K110" s="2" t="str">
+        <x:v>В следующих подразделах подробнее рассматриваются некоторые из этих источников и связанные с ними механизмы. Большинство реальных стратегий объединяют два или более источника; таблица помогает определить, какие из них лежат в основе тезиса и какие режимы отказа следует проверить в первую очередь.</x:v>
+      </x:c>
       <x:c r="L110" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.251.1"&gt;
@@ -10681,7 +11051,17 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M110" s="2"/>
+      <x:c r="M110" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.251.1"&gt;
+     В следующих подразделах подробнее рассматриваются некоторые из этих источников и связанные с ними механизмы.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.251.2"&gt;
+     Большинство реальных стратегий объединяют два или более источника; таблица помогает определить, какие из них лежат в основе тезиса и какие режимы отказа следует проверить в первую очередь.
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N110" s="2"/>
       <x:c r="O110" s="2"/>
       <x:c r="P110" s="2"/>
@@ -10690,29 +11070,31 @@
       <x:c r="S110" s="2"/>
       <x:c r="T110" s="2"/>
       <x:c r="U110" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V110" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W110" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X110" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y110" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z110" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA110" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB110" s="2"/>
+      <x:c r="AB110" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC110" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -10744,7 +11126,9 @@
       <x:c r="J111" s="2" t="str">
         <x:v>Box 6.2: Why most published anomalies fail in practice</x:v>
       </x:c>
-      <x:c r="K111" s="2"/>
+      <x:c r="K111" s="2" t="str">
+        <x:v>Вставка 6.2: Почему большинство опубликованных аномалий не работают на практике</x:v>
+      </x:c>
       <x:c r="L111" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
      &lt;strong class="screenText"&gt;
@@ -10760,7 +11144,21 @@
     &lt;/p&gt;
     </x:v>
       </x:c>
-      <x:c r="M111" s="2"/>
+      <x:c r="M111" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+     &lt;strong class="screenText"&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.252.1"&gt;
+       Вставка 6.2: Почему большинство опубликованных аномалий не работают
+      &lt;/span&gt;
+     &lt;/strong&gt;
+     &lt;strong class="screenText"&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.253.1"&gt;
+       на практике
+      &lt;/span&gt;
+     &lt;/strong&gt;
+    &lt;/p&gt;
+    </x:v>
+      </x:c>
       <x:c r="N111" s="2"/>
       <x:c r="O111" s="2"/>
       <x:c r="P111" s="2"/>
@@ -10771,29 +11169,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U111" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V111" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W111" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X111" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y111" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z111" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA111" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB111" s="2"/>
+      <x:c r="AB111" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC111" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -10825,7 +11225,9 @@
       <x:c r="J112" s="2" t="str">
         <x:v>The academic literature documents hundreds of cross- al predictors, yet very few survive as tradable strategies. Three gaps account for most of the attrition:</x:v>
       </x:c>
-      <x:c r="K112" s="2"/>
+      <x:c r="K112" s="2" t="str">
+        <x:v>В академической литературе описаны сотни кросс-секционных предикторов, однако лишь немногие из них выдерживают проверку как реализуемые торговые стратегии. Большая часть отсева объясняется тремя разрывами:</x:v>
+      </x:c>
       <x:c r="L112" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.254.1"&gt;
@@ -10842,7 +11244,22 @@
     &lt;/p&gt;
     </x:v>
       </x:c>
-      <x:c r="M112" s="2"/>
+      <x:c r="M112" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.254.1"&gt;
+      В академической
+     &lt;/span&gt;
+     &lt;a id="_idIndexMarker671"&gt;
+     &lt;/a&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.255.1"&gt;
+      литературе описаны сотни кросс-секционных предикторов, однако лишь немногие из них выдерживают проверку как реализуемые торговые стратегии.
+     &lt;/span&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.255.2"&gt;
+      Большая часть отсева объясняется тремя разрывами:
+     &lt;/span&gt;
+    &lt;/p&gt;
+    </x:v>
+      </x:c>
       <x:c r="N112" s="2"/>
       <x:c r="O112" s="2"/>
       <x:c r="P112" s="2"/>
@@ -10853,29 +11270,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U112" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V112" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W112" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X112" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y112" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z112" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA112" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB112" s="2"/>
+      <x:c r="AB112" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC112" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -10907,7 +11326,9 @@
       <x:c r="J113" s="2" t="str">
         <x:v>Post-publication decay. McLean and Pontiff (2016) show that anomaly alphas decline roughly 50% after publication, partly due to overfitting corrections, partly due to arbitrage capital flowing in.</x:v>
       </x:c>
-      <x:c r="K113" s="2"/>
+      <x:c r="K113" s="2" t="str">
+        <x:v>Снижение после публикации. McLean и Pontiff (2016) показывают, что альфа аномалий после публикации снижается примерно на 50%: отчасти из-за поправок на переобучение, отчасти из-за притока арбитражного капитала.</x:v>
+      </x:c>
       <x:c r="L113" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
       &lt;strong class="keyWord"&gt;
@@ -10926,7 +11347,24 @@
      &lt;/li&gt;
      </x:v>
       </x:c>
-      <x:c r="M113" s="2"/>
+      <x:c r="M113" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
+      &lt;strong class="keyWord"&gt;
+       &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.256.1"&gt;
+        Снижение после публикации.
+       &lt;/span&gt;
+      &lt;/strong&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.257.1"&gt;
+       McLean
+      &lt;/span&gt;
+      &lt;a id="_idIndexMarker672"&gt;
+      &lt;/a&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.258.1"&gt;
+       и Pontiff (2016) показывают, что альфа аномалий после публикации снижается примерно на 50%: отчасти из-за поправок на переобучение, отчасти из-за притока арбитражного капитала.
+      &lt;/span&gt;
+     &lt;/li&gt;
+     </x:v>
+      </x:c>
       <x:c r="N113" s="2"/>
       <x:c r="O113" s="2"/>
       <x:c r="P113" s="2"/>
@@ -10937,29 +11375,31 @@
         <x:v>strong,a</x:v>
       </x:c>
       <x:c r="U113" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V113" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W113" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X113" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y113" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z113" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA113" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB113" s="2"/>
+      <x:c r="AB113" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC113" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -10991,7 +11431,9 @@
       <x:c r="J114" s="2" t="str">
         <x:v>Implementation gap. Academic studies typically use simplified portfolio construction (equal-weight long-short deciles, monthly rebalancing, no costs), which overstates live performance. Turnover, bid-ask spreads, and borrow costs often consume the reported alpha.</x:v>
       </x:c>
-      <x:c r="K114" s="2"/>
+      <x:c r="K114" s="2" t="str">
+        <x:v>Разрыв между исследованием и реализацией. В академических исследованиях обычно используется упрощённое формирование портфеля (равновзвешенные длинные и короткие позиции по децилям, ежемесячная ребалансировка, отсутствие издержек), что завышает результативность при торговле в реальном режиме. Оборот портфеля, спреды между лучшими ценами покупки и продажи и стоимость заимствования ценных бумаг нередко поглощают заявленную альфу.</x:v>
+      </x:c>
       <x:c r="L114" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
       &lt;strong class="keyWord"&gt;
@@ -11013,7 +11455,27 @@
      &lt;/li&gt;
      </x:v>
       </x:c>
-      <x:c r="M114" s="2"/>
+      <x:c r="M114" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
+      &lt;strong class="keyWord"&gt;
+       &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.259.1"&gt;
+        Разрыв между исследованием и реализацией.
+       &lt;/span&gt;
+      &lt;/strong&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.260.1"&gt;
+       В академических
+      &lt;/span&gt;
+      &lt;a id="_idIndexMarker673"&gt;
+      &lt;/a&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.261.1"&gt;
+       исследованиях обычно используется упрощённое формирование портфеля (равновзвешенные длинные и короткие позиции по децилям, ежемесячная ребалансировка, отсутствие издержек), что завышает результативность при торговле в реальном режиме.
+      &lt;/span&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.261.2"&gt;
+       Оборот портфеля, спреды между лучшими ценами покупки и продажи и стоимость заимствования ценных бумаг нередко поглощают заявленную альфу.
+      &lt;/span&gt;
+     &lt;/li&gt;
+     </x:v>
+      </x:c>
       <x:c r="N114" s="2"/>
       <x:c r="O114" s="2"/>
       <x:c r="P114" s="2"/>
@@ -11024,29 +11486,31 @@
         <x:v>strong,a</x:v>
       </x:c>
       <x:c r="U114" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V114" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W114" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X114" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y114" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z114" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA114" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB114" s="2"/>
+      <x:c r="AB114" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC114" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -11078,7 +11542,9 @@
       <x:c r="J115" s="2" t="str">
         <x:v>Detail sensitivity. Small definitional choices (universe filters, rebalancing timing, winsorization thresholds) can flip the sign of a backtest result. A backtested anomaly is a hypothesis, not evidence; the evidence comes from out-of-sample evaluation under a fixed protocol ( Sections 6.5 and 6.6 ).</x:v>
       </x:c>
-      <x:c r="K115" s="2"/>
+      <x:c r="K115" s="2" t="str">
+        <x:v>Чувствительность к деталям. Небольшие различия в определениях (фильтры торгуемой совокупности активов, сроки ребалансировки, пороги винзоризации) могут изменить знак результата бэктеста. Аномалия, выявленная при бэктесте, — это гипотеза, а не доказательство; доказательством служит оценка вне обучающей выборки по фиксированному протоколу (разделы 6.5 и 6.6).</x:v>
+      </x:c>
       <x:c r="L115" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
       &lt;strong class="keyWord"&gt;
@@ -11116,7 +11582,43 @@
      &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M115" s="2"/>
+      <x:c r="M115" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
+      &lt;strong class="keyWord"&gt;
+       &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.262.1"&gt;
+        Чувствительность к деталям.
+       &lt;/span&gt;
+      &lt;/strong&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.263.1"&gt;
+       Небольшие
+      &lt;/span&gt;
+      &lt;a id="_idIndexMarker674"&gt;
+      &lt;/a&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.264.1"&gt;
+       различия в определениях (фильтры торгуемой совокупности активов, сроки ребалансировки, пороги винзоризации) могут изменить знак результата бэктеста.
+      &lt;/span&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.264.2"&gt;
+       Аномалия, выявленная при бэктесте, — это гипотеза, а не доказательство; доказательством служит оценка вне обучающей выборки по фиксированному протоколу (
+      &lt;/span&gt;
+      &lt;em class="italic"&gt;
+       &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.265.1"&gt;
+        разделы 6.5
+       &lt;/span&gt;
+      &lt;/em&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.266.1"&gt;
+       и
+      &lt;/span&gt;
+      &lt;em class="italic"&gt;
+       &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.267.1"&gt;
+        6.6
+       &lt;/span&gt;
+      &lt;/em&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.268.1"&gt;
+       ).
+      &lt;/span&gt;
+     &lt;/li&gt;
+    </x:v>
+      </x:c>
       <x:c r="N115" s="2"/>
       <x:c r="O115" s="2"/>
       <x:c r="P115" s="2"/>
@@ -11127,29 +11629,31 @@
         <x:v>strong,em,a</x:v>
       </x:c>
       <x:c r="U115" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V115" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W115" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X115" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y115" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z115" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA115" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB115" s="2"/>
+      <x:c r="AB115" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC115" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -11181,7 +11685,9 @@
       <x:c r="J116" s="2" t="str">
         <x:v>The defense is not to avoid published ideas but to treat them as starting points that require independent validation within a researcher’s own trading setup and cost assumptions.</x:v>
       </x:c>
-      <x:c r="K116" s="2"/>
+      <x:c r="K116" s="2" t="str">
+        <x:v>Защита от этих проблем состоит не в отказе от опубликованных идей, а в отношении к ним как к отправным точкам, требующим независимой проверки с учётом собственных параметров торговли и допущений исследователя об издержках.</x:v>
+      </x:c>
       <x:c r="L116" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.269.1"&gt;
@@ -11190,7 +11696,14 @@
     &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M116" s="2"/>
+      <x:c r="M116" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.269.1"&gt;
+      Защита от этих проблем состоит не в отказе от опубликованных идей, а в отношении к ним как к отправным точкам, требующим независимой проверки с учётом собственных параметров торговли и допущений исследователя об издержках.
+     &lt;/span&gt;
+    &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N116" s="2"/>
       <x:c r="O116" s="2"/>
       <x:c r="P116" s="2"/>
@@ -11199,29 +11712,31 @@
       <x:c r="S116" s="2"/>
       <x:c r="T116" s="2"/>
       <x:c r="U116" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V116" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W116" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X116" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y116" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z116" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA116" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB116" s="2"/>
+      <x:c r="AB116" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC116" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -11255,7 +11770,9 @@
       <x:c r="J117" s="2" t="str">
         <x:v>Slow adjustment and behavioral responses</x:v>
       </x:c>
-      <x:c r="K117" s="2"/>
+      <x:c r="K117" s="2" t="str">
+        <x:v>Медленная корректировка и поведенческие реакции</x:v>
+      </x:c>
       <x:c r="L117" s="2" t="str">
         <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-267"&gt;
     &lt;a id="_idTextAnchor259"&gt;
@@ -11266,7 +11783,16 @@
    &lt;/h3&gt;
    </x:v>
       </x:c>
-      <x:c r="M117" s="2"/>
+      <x:c r="M117" s="2" t="str">
+        <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-267"&gt;
+    &lt;a id="_idTextAnchor259"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.270.1"&gt;
+     Медленная корректировка и поведенческие реакции
+    &lt;/span&gt;
+   &lt;/h3&gt;
+   </x:v>
+      </x:c>
       <x:c r="N117" s="2"/>
       <x:c r="O117" s="2"/>
       <x:c r="P117" s="2"/>
@@ -11277,29 +11803,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U117" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V117" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W117" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X117" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y117" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z117" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA117" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB117" s="2"/>
+      <x:c r="AB117" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC117" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -11331,7 +11859,9 @@
       <x:c r="J118" s="2" t="str">
         <x:v>Prices may incorporate information gradually due to limited attention, delegated decision-making, or slow portfolio rebalancing, motivating underreaction narratives behind momentum and intermediate-horizon trend effects (Jegadeesh and Titman, 1993).</x:v>
       </x:c>
-      <x:c r="K118" s="2"/>
+      <x:c r="K118" s="2" t="str">
+        <x:v>Цены могут учитывать информацию постепенно из-за ограниченного внимания, делегированного принятия решений или медленной ребалансировки портфеля, что лежит в основе объяснений моментума и трендовых эффектов на промежуточном горизонте через недостаточную реакцию рынка (Jegadeesh и Titman, 1993).</x:v>
+      </x:c>
       <x:c r="L118" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.271.1"&gt;
@@ -11350,7 +11880,24 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M118" s="2"/>
+      <x:c r="M118" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.271.1"&gt;
+     Цены могут учитывать
+    &lt;/span&gt;
+    &lt;a id="_idIndexMarker675"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.272.1"&gt;
+     информацию постепенно из-за ограниченного внимания, делегированного
+    &lt;/span&gt;
+    &lt;a id="_idIndexMarker676"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.273.1"&gt;
+     принятия решений или медленной ребалансировки портфеля, что лежит в основе объяснений моментума и трендовых эффектов на промежуточном горизонте через недостаточную реакцию рынка (Jegadeesh и Titman, 1993).
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N118" s="2"/>
       <x:c r="O118" s="2"/>
       <x:c r="P118" s="2"/>
@@ -11361,29 +11908,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U118" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V118" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W118" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X118" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y118" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z118" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA118" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB118" s="2"/>
+      <x:c r="AB118" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC118" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -11407,15 +11956,17 @@
       </x:c>
       <x:c r="G119" s="2"/>
       <x:c r="H119" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="I119" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="J119" s="2" t="str">
         <x:v>Early failure-mode tests : Examine drawdown and rebound episodes (momentum crashes; Daniel and Moskowitz, 2016) and check whether performance concentrates under benign conditions but reverses when volatility spikes or liquidity dries up, a pattern that often reveals that alpha partly compensates for state-contingent risk.</x:v>
       </x:c>
-      <x:c r="K119" s="2"/>
+      <x:c r="K119" s="2" t="str">
+        <x:v>Первые проверки режимов отказа: Проанализируйте эпизоды просадок и последующего восстановления (крахи моментума; Daniel и Moskowitz, 2016) и проверьте, не сосредоточена ли результативность в благоприятных условиях с последующим разворотом при резком росте волатильности или иссякании ликвидности. Такая закономерность часто указывает на то, что альфа отчасти служит компенсацией за риск, зависящий от состояния рынка.</x:v>
+      </x:c>
       <x:c r="L119" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;strong class="screenText"&gt;
@@ -11429,7 +11980,19 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M119" s="2"/>
+      <x:c r="M119" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;strong class="screenText"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.274.1"&gt;
+      Первые проверки режимов отказа
+     &lt;/span&gt;
+    &lt;/strong&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.275.1"&gt;
+     : Проанализируйте эпизоды просадок и последующего восстановления (крахи моментума; Daniel и Moskowitz, 2016) и проверьте, не сосредоточена ли результативность в благоприятных условиях с последующим разворотом при резком росте волатильности или иссякании ликвидности. Такая закономерность часто указывает на то, что альфа отчасти служит компенсацией за риск, зависящий от состояния рынка.
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N119" s="2"/>
       <x:c r="O119" s="2"/>
       <x:c r="P119" s="2"/>
@@ -11440,29 +12003,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U119" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V119" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W119" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X119" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y119" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z119" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA119" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB119" s="2"/>
+      <x:c r="AB119" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 172/131; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC119" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -11488,15 +12053,17 @@
         <x:v>_idParaDest-268</x:v>
       </x:c>
       <x:c r="H120" s="2" t="n">
-        <x:v>170</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="I120" s="2" t="n">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="J120" s="2" t="str">
         <x:v>Risk compensation</x:v>
       </x:c>
-      <x:c r="K120" s="2"/>
+      <x:c r="K120" s="2" t="str">
+        <x:v>Компенсация за риск</x:v>
+      </x:c>
       <x:c r="L120" s="2" t="str">
         <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-268"&gt;
     &lt;a id="_idTextAnchor260"&gt;
@@ -11507,7 +12074,16 @@
    &lt;/h3&gt;
    </x:v>
       </x:c>
-      <x:c r="M120" s="2"/>
+      <x:c r="M120" s="2" t="str">
+        <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-268"&gt;
+    &lt;a id="_idTextAnchor260"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.276.1"&gt;
+     Компенсация за риск
+    &lt;/span&gt;
+   &lt;/h3&gt;
+   </x:v>
+      </x:c>
       <x:c r="N120" s="2"/>
       <x:c r="O120" s="2"/>
       <x:c r="P120" s="2"/>
@@ -11518,29 +12094,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U120" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V120" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W120" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X120" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y120" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z120" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA120" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB120" s="2"/>
+      <x:c r="AB120" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 172/131; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC120" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -11572,7 +12150,9 @@
       <x:c r="J121" s="2" t="str">
         <x:v>Some returns compensate for bearing exposures others avoid: liquidity risk, tail risk, volatility risk, or balance-sheet-intensive exposures. Persistence can coexist with widespread awareness because the constraint is risk tolerance and leverage capacity, not information.</x:v>
       </x:c>
-      <x:c r="K121" s="2"/>
+      <x:c r="K121" s="2" t="str">
+        <x:v>Некоторые виды доходности компенсируют принятие на себя факторов риска, которых избегают другие: риска ликвидности, хвостового риска, риска волатильности или факторов риска, требующих значительных ресурсов баланса. Устойчивость может сочетаться с широкой осведомлённостью, поскольку ограничением служат готовность принимать риск и возможности использования кредитного плеча, а не информация.</x:v>
+      </x:c>
       <x:c r="L121" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.277.1"&gt;
@@ -11589,7 +12169,22 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M121" s="2"/>
+      <x:c r="M121" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.277.1"&gt;
+     Некоторые виды доходности компенсируют
+    &lt;/span&gt;
+    &lt;a id="_idIndexMarker677"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.278.1"&gt;
+     принятие на себя факторов риска, которых избегают другие: риска ликвидности, хвостового риска, риска волатильности или факторов риска, требующих значительных ресурсов баланса.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.278.2"&gt;
+     Устойчивость может сочетаться с широкой осведомлённостью, поскольку ограничением служат готовность принимать риск и возможности использования кредитного плеча, а не информация.
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N121" s="2"/>
       <x:c r="O121" s="2"/>
       <x:c r="P121" s="2"/>
@@ -11600,29 +12195,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U121" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V121" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W121" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X121" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y121" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z121" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA121" s="2" t="str">
         <x:v>CH06-BATCH-003</x:v>
       </x:c>
-      <x:c r="AB121" s="2"/>
+      <x:c r="AB121" s="2" t="str">
+        <x:v>CH06-BATCH-003: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC121" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.4 / BATCH-003</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -11646,15 +12243,17 @@
       </x:c>
       <x:c r="G122" s="2"/>
       <x:c r="H122" s="2" t="n">
-        <x:v>164</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="I122" s="2" t="n">
-        <x:v>123</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="J122" s="2" t="str">
         <x:v>Early failure-mode tests : Performance during tail episodes when constraints bind (margin/funding shocks, forced deleveraging) and performance conditional on volatility and liquidity proxies.</x:v>
       </x:c>
-      <x:c r="K122" s="2"/>
+      <x:c r="K122" s="2" t="str">
+        <x:v>Первые проверки режимов отказа: Результативность во время хвостовых событий, когда ограничения становятся критическими (шоки маржинального обеспечения или финансирования, вынужденное сокращение кредитного плеча), и результативность в зависимости от прокси-показателей волатильности и ликвидности.</x:v>
+      </x:c>
       <x:c r="L122" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;strong class="screenText"&gt;
@@ -11668,7 +12267,19 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M122" s="2"/>
+      <x:c r="M122" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;strong class="screenText"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.279.1"&gt;
+      Первые проверки режимов отказа
+     &lt;/span&gt;
+    &lt;/strong&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.280.1"&gt;
+     : Результативность во время хвостовых событий, когда ограничения становятся критическими (шоки маржинального обеспечения или финансирования, вынужденное сокращение кредитного плеча), и результативность в зависимости от прокси-показателей волатильности и ликвидности.
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N122" s="2"/>
       <x:c r="O122" s="2"/>
       <x:c r="P122" s="2"/>
@@ -11679,29 +12290,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U122" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V122" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W122" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X122" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y122" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z122" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA122" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB122" s="2"/>
+      <x:c r="AB122" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS. Исправлена привязка PDF: 172/131; повторная визуальная сверка — PASS.</x:v>
+      </x:c>
       <x:c r="AC122" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -11735,7 +12348,9 @@
       <x:c r="J123" s="2" t="str">
         <x:v>Market segmentation and limits to arbitrage</x:v>
       </x:c>
-      <x:c r="K123" s="2"/>
+      <x:c r="K123" s="2" t="str">
+        <x:v>Сегментация рынков и пределы арбитража</x:v>
+      </x:c>
       <x:c r="L123" s="2" t="str">
         <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-269"&gt;
     &lt;a id="_idTextAnchor261"&gt;
@@ -11746,7 +12361,16 @@
    &lt;/h3&gt;
    </x:v>
       </x:c>
-      <x:c r="M123" s="2"/>
+      <x:c r="M123" s="2" t="str">
+        <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-269"&gt;
+    &lt;a id="_idTextAnchor261"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.281.1"&gt;
+     Сегментация рынков и пределы арбитража
+    &lt;/span&gt;
+   &lt;/h3&gt;
+   </x:v>
+      </x:c>
       <x:c r="N123" s="2"/>
       <x:c r="O123" s="2"/>
       <x:c r="P123" s="2"/>
@@ -11757,29 +12381,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U123" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V123" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W123" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X123" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y123" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z123" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA123" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB123" s="2"/>
+      <x:c r="AB123" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC123" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -11811,7 +12437,9 @@
       <x:c r="J124" s="2" t="str">
         <x:v>Segmented markets and institutional constraints create persistent wedges: funding differences, capital charges, short-selling constraints, inventory limits, and client-flow internalization. The edge persists because the arbitrage is balance-sheet intensive or operationally constrained.</x:v>
       </x:c>
-      <x:c r="K124" s="2"/>
+      <x:c r="K124" s="2" t="str">
+        <x:v>Сегментированные рынки и институциональные ограничения создают устойчивые диспропорции: различия в финансировании, требования к капиталу, ограничения коротких продаж, лимиты позиций на балансе и внутреннее исполнение клиентского потока. Преимущество сохраняется, поскольку арбитраж требует значительных ресурсов баланса или ограничен операционными возможностями.</x:v>
+      </x:c>
       <x:c r="L124" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.282.1"&gt;
@@ -11828,7 +12456,22 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M124" s="2"/>
+      <x:c r="M124" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.282.1"&gt;
+     Сегментированные рынки и
+    &lt;/span&gt;
+    &lt;a id="_idIndexMarker678"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.283.1"&gt;
+     институциональные ограничения создают устойчивые диспропорции: различия в финансировании, требования к капиталу, ограничения коротких продаж, лимиты позиций на балансе и внутреннее исполнение клиентского потока.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.283.2"&gt;
+     Преимущество сохраняется, поскольку арбитраж требует значительных ресурсов баланса или ограничен операционными возможностями.
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N124" s="2"/>
       <x:c r="O124" s="2"/>
       <x:c r="P124" s="2"/>
@@ -11839,29 +12482,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U124" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V124" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W124" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X124" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y124" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z124" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA124" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB124" s="2"/>
+      <x:c r="AB124" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC124" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -11893,7 +12538,9 @@
       <x:c r="J125" s="2" t="str">
         <x:v>Early tests: Stability under stressed financing and fee regimes, realism of access assumptions, and capacity/crowding behavior.</x:v>
       </x:c>
-      <x:c r="K125" s="2"/>
+      <x:c r="K125" s="2" t="str">
+        <x:v>Первые проверки: Устойчивость в стрессовых режимах финансирования и комиссий, реалистичность допущений о доступе, а также поведение ёмкости стратегии и скопления участников.</x:v>
+      </x:c>
       <x:c r="L125" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;strong class="keyWord"&gt;
@@ -11907,7 +12554,19 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M125" s="2"/>
+      <x:c r="M125" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;strong class="keyWord"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.284.1"&gt;
+      Первые проверки:
+     &lt;/span&gt;
+    &lt;/strong&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.285.1"&gt;
+     Устойчивость в стрессовых режимах финансирования и комиссий, реалистичность допущений о доступе, а также поведение ёмкости стратегии и скопления участников.
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N125" s="2"/>
       <x:c r="O125" s="2"/>
       <x:c r="P125" s="2"/>
@@ -11918,29 +12577,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U125" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V125" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W125" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X125" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y125" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z125" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA125" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB125" s="2"/>
+      <x:c r="AB125" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC125" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -11972,7 +12633,9 @@
       <x:c r="J126" s="2" t="str">
         <x:v>Box 6.3: Why prediction alone is insufficient</x:v>
       </x:c>
-      <x:c r="K126" s="2"/>
+      <x:c r="K126" s="2" t="str">
+        <x:v>Вставка 6.3: Почему одного прогнозирования недостаточно</x:v>
+      </x:c>
       <x:c r="L126" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
      &lt;strong class="screenText"&gt;
@@ -11983,7 +12646,16 @@
     &lt;/p&gt;
     </x:v>
       </x:c>
-      <x:c r="M126" s="2"/>
+      <x:c r="M126" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+     &lt;strong class="screenText"&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.286.1"&gt;
+       Вставка 6.3: Почему одного прогнозирования недостаточно
+      &lt;/span&gt;
+     &lt;/strong&gt;
+    &lt;/p&gt;
+    </x:v>
+      </x:c>
       <x:c r="N126" s="2"/>
       <x:c r="O126" s="2"/>
       <x:c r="P126" s="2"/>
@@ -11994,29 +12666,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U126" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V126" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W126" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X126" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y126" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z126" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA126" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB126" s="2"/>
+      <x:c r="AB126" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC126" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -12048,7 +12722,9 @@
       <x:c r="J127" s="2" t="str">
         <x:v>A correct forecast does not guarantee a profitable trade. When 3Com announced the IPO of its Palm subsidiary in 2000, Palm’s implied valuation quickly exceeded that of the parent—a textbook mispricing visible to every market participant. Yet the trade was nearly impossible to execute: Palm shares available to borrow were scarce, borrowing fees spiked to extreme levels, and uncertainty about the spin-off timeline created open-ended funding risk. The mispricing persisted for months despite being obvious. For ML-driven research, the lesson is concrete: before engineering features for a mispricing hypothesis, verify that the short side is accessible, that borrowing and funding costs do not consume the spread, and that the holding-period risk is bounded. A model that identifies unexploitable opportunities is operationally useless regardless of its predictive accuracy.</x:v>
       </x:c>
-      <x:c r="K127" s="2"/>
+      <x:c r="K127" s="2" t="str">
+        <x:v>Правильный прогноз не гарантирует прибыльной сделки. Когда в 2000 году компания 3Com объявила об IPO своей дочерней компании Palm, подразумеваемая оценка стоимости Palm быстро превысила стоимость материнской компании — классический пример ошибочного ценообразования, очевидный каждому участнику рынка. Однако реализовать сделку было практически невозможно: доступных для заимствования акций Palm было мало, плата за заимствование взлетела до экстремальных уровней, а неопределённость сроков выделения компании создавала неограниченный по времени риск финансирования. Несмотря на очевидность, ошибочное ценообразование сохранялось месяцами. Для исследований с применением ML вывод конкретен: прежде чем конструировать признаки для гипотезы об ошибочном ценообразовании, убедитесь, что короткая позиция доступна, затраты на заимствование и финансирование не поглощают спред, а риск периода удержания ограничен. Модель, выявляющая нереализуемые возможности, бесполезна с операционной точки зрения независимо от точности её прогнозов.</x:v>
+      </x:c>
       <x:c r="L127" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.287.1"&gt;
@@ -12072,7 +12748,29 @@
     &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M127" s="2"/>
+      <x:c r="M127" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.287.1"&gt;
+      Правильный прогноз не гарантирует прибыльной сделки.
+     &lt;/span&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.287.2"&gt;
+      Когда в 2000 году компания 3Com объявила об IPO своей дочерней компании Palm, подразумеваемая оценка стоимости Palm быстро превысила стоимость материнской компании — классический пример ошибочного ценообразования, очевидный каждому участнику рынка.
+     &lt;/span&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.287.3"&gt;
+      Однако реализовать сделку было практически невозможно: доступных для заимствования акций Palm было мало, плата за заимствование взлетела до экстремальных уровней, а неопределённость сроков выделения компании создавала неограниченный по времени риск финансирования.
+     &lt;/span&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.287.4"&gt;
+      Несмотря на очевидность, ошибочное ценообразование сохранялось месяцами.
+     &lt;/span&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.287.5"&gt;
+      Для исследований с применением ML вывод конкретен: прежде чем конструировать признаки для гипотезы об ошибочном ценообразовании, убедитесь, что короткая позиция доступна, затраты на заимствование и финансирование не поглощают спред, а риск периода удержания ограничен.
+     &lt;/span&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.287.6"&gt;
+      Модель, выявляющая нереализуемые возможности, бесполезна с операционной точки зрения независимо от точности её прогнозов.
+     &lt;/span&gt;
+    &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N127" s="2"/>
       <x:c r="O127" s="2"/>
       <x:c r="P127" s="2"/>
@@ -12081,29 +12779,31 @@
       <x:c r="S127" s="2"/>
       <x:c r="T127" s="2"/>
       <x:c r="U127" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V127" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W127" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X127" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y127" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z127" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA127" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB127" s="2"/>
+      <x:c r="AB127" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC127" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -12137,7 +12837,9 @@
       <x:c r="J128" s="2" t="str">
         <x:v>Mechanical and institutional flows</x:v>
       </x:c>
-      <x:c r="K128" s="2"/>
+      <x:c r="K128" s="2" t="str">
+        <x:v>Механические и институциональные потоки</x:v>
+      </x:c>
       <x:c r="L128" s="2" t="str">
         <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-270"&gt;
     &lt;a id="_idTextAnchor262"&gt;
@@ -12148,7 +12850,16 @@
    &lt;/h3&gt;
    </x:v>
       </x:c>
-      <x:c r="M128" s="2"/>
+      <x:c r="M128" s="2" t="str">
+        <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-270"&gt;
+    &lt;a id="_idTextAnchor262"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.288.1"&gt;
+     Механические и институциональные потоки
+    &lt;/span&gt;
+   &lt;/h3&gt;
+   </x:v>
+      </x:c>
       <x:c r="N128" s="2"/>
       <x:c r="O128" s="2"/>
       <x:c r="P128" s="2"/>
@@ -12159,29 +12870,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U128" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V128" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W128" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X128" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y128" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z128" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA128" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB128" s="2"/>
+      <x:c r="AB128" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC128" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -12213,7 +12926,9 @@
       <x:c r="J129" s="2" t="str">
         <x:v>Predictable demand from mandates, hedging, index rebalancing, roll schedules, or systematic execution programs creates transient or recurrent price pressure, driven by rules and constraints rather than beliefs.</x:v>
       </x:c>
-      <x:c r="K129" s="2"/>
+      <x:c r="K129" s="2" t="str">
+        <x:v>Предсказуемый спрос, обусловленный предписаниями, хеджированием, ребалансировкой индексов, графиками роллирования или программами систематического исполнения, создаёт временное или повторяющееся ценовое давление, вызванное правилами и ограничениями, а не убеждениями участников.</x:v>
+      </x:c>
       <x:c r="L129" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.289.1"&gt;
@@ -12227,7 +12942,19 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M129" s="2"/>
+      <x:c r="M129" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.289.1"&gt;
+     Предсказуемый спрос, обусловленный
+    &lt;/span&gt;
+    &lt;a id="_idIndexMarker679"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.290.1"&gt;
+     предписаниями, хеджированием, ребалансировкой индексов, графиками роллирования или программами систематического исполнения, создаёт временное или повторяющееся ценовое давление, вызванное правилами и ограничениями, а не убеждениями участников.
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N129" s="2"/>
       <x:c r="O129" s="2"/>
       <x:c r="P129" s="2"/>
@@ -12238,29 +12965,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U129" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V129" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W129" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X129" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y129" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z129" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA129" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB129" s="2"/>
+      <x:c r="AB129" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC129" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -12292,7 +13021,9 @@
       <x:c r="J130" s="2" t="str">
         <x:v>Early tests: Calendar dependence and event alignment, decay under crowding, and execution sensitivity (flow edges often live near the spread).</x:v>
       </x:c>
-      <x:c r="K130" s="2"/>
+      <x:c r="K130" s="2" t="str">
+        <x:v>Первые проверки: Календарная зависимость и согласованность с событиями, ослабление по мере скопления участников и чувствительность к исполнению (преимущества, основанные на потоках, часто существуют вблизи спреда).</x:v>
+      </x:c>
       <x:c r="L130" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;strong class="keyWord"&gt;
@@ -12306,7 +13037,19 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M130" s="2"/>
+      <x:c r="M130" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;strong class="keyWord"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.291.1"&gt;
+      Первые проверки:
+     &lt;/span&gt;
+    &lt;/strong&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.292.1"&gt;
+     Календарная зависимость и согласованность с событиями, ослабление по мере скопления участников и чувствительность к исполнению (преимущества, основанные на потоках, часто существуют вблизи спреда).
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N130" s="2"/>
       <x:c r="O130" s="2"/>
       <x:c r="P130" s="2"/>
@@ -12317,29 +13060,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U130" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V130" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W130" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X130" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y130" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z130" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA130" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB130" s="2"/>
+      <x:c r="AB130" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC130" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -12371,7 +13116,9 @@
       <x:c r="J131" s="2" t="str">
         <x:v>Index reconstitution is the standard example. When an index provider announces an addition or deletion, passive funds tracking that index must trade by the effective date, creating a demand shock whose direction, approximate magnitude, and timing are publicly known in advance. The edge is not in having private information but in positioning ahead of the mandated flow: predicting which securities will be added or removed, and when the demand will materialize. The risk is real: holding-period exposure to company-specific losses, potential event cancellations, and crowding as more participants exploit the same signal. As passive investment continues to grow (estimated at 35-40% of U.S. equity market capitalization), these flow events create larger dislocations and attract more competition, illustrating the tension between opportunity size and crowding that recurs across flow-based strategies. In our case studies, futures roll effects in cme_futures and ETF creation/redemption dynamics in etfs create analogous flow-driven patterns at different cadences.</x:v>
       </x:c>
-      <x:c r="K131" s="2"/>
+      <x:c r="K131" s="2" t="str">
+        <x:v>Пересмотр состава индекса — стандартный пример. Когда поставщик индекса объявляет о добавлении или исключении актива, пассивные фонды, отслеживающие этот индекс, должны совершить сделки к дате вступления изменений в силу, создавая шок спроса, направление, примерный масштаб и время которого заранее известны широкой публике. Преимущество заключается не в обладании закрытой информацией, а в заблаговременном открытии позиций перед обязательным потоком: прогнозировании того, какие ценные бумаги будут добавлены или исключены и когда возникнет спрос. Риск реален: в период удержания возможны убытки, связанные с конкретной компанией, отмена события и скопление участников по мере того, как всё больше трейдеров используют один и тот же сигнал. По мере дальнейшего роста пассивных инвестиций (их доля оценивается в 35-40% капитализации рынка акций США) такие потоковые события создают более крупные диспропорции и привлекают больше конкурентов, иллюстрируя противоречие между масштабом возможности и скоплением участников, характерное для стратегий, основанных на потоках. В наших практических примерах эффекты роллирования фьючерсов в cme_futures и динамика создания и погашения ETF в etfs формируют аналогичные закономерности, обусловленные потоками, но с разной периодичностью.</x:v>
+      </x:c>
       <x:c r="L131" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.293.1"&gt;
@@ -12430,7 +13177,64 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M131" s="2"/>
+      <x:c r="M131" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.293.1"&gt;
+     Пересмотр состава индекса — стандартный пример.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.293.2"&gt;
+     Когда поставщик индекса объявляет о добавлении или исключении актива, пассивные фонды, отслеживающие этот индекс, должны совершить сделки к дате вступления изменений в силу, создавая шок спроса, направление, примерный масштаб и время которого заранее известны широкой публике.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.293.3"&gt;
+     Преимущество заключается не в обладании закрытой информацией, а в заблаговременном открытии позиций перед обязательным потоком: прогнозировании того,
+    &lt;/span&gt;
+    &lt;em class="italic"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.294.1"&gt;
+      какие
+     &lt;/span&gt;
+    &lt;/em&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.295.1"&gt;
+     ценные бумаги будут добавлены или исключены и
+    &lt;/span&gt;
+    &lt;em class="italic"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.296.1"&gt;
+      когда
+     &lt;/span&gt;
+    &lt;/em&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.297.1"&gt;
+     возникнет спрос.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.297.2"&gt;
+     Риск реален: в период удержания возможны убытки, связанные с конкретной компанией, отмена события и скопление участников по мере того, как всё больше трейдеров используют один и тот же сигнал.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.297.3"&gt;
+     По мере дальнейшего роста пассивных инвестиций (их доля оценивается в 35-40% капитализации рынка акций США)
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.297.4"&gt;
+     такие потоковые события создают более крупные диспропорции и привлекают больше конкурентов, иллюстрируя противоречие между масштабом возможности и скоплением участников, характерное для стратегий, основанных на потоках.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.297.5"&gt;
+     В наших практических примерах эффекты роллирования фьючерсов в
+    &lt;/span&gt;
+    &lt;code class="inlineCode"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.298.1"&gt;
+      cme_futures
+     &lt;/span&gt;
+    &lt;/code&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.299.1"&gt;
+     и динамика создания и погашения ETF в
+    &lt;/span&gt;
+    &lt;code class="inlineCode"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.300.1"&gt;
+      etfs
+     &lt;/span&gt;
+    &lt;/code&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.301.1"&gt;
+     формируют аналогичные закономерности, обусловленные потоками, но с разной периодичностью.
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N131" s="2"/>
       <x:c r="O131" s="2"/>
       <x:c r="P131" s="2"/>
@@ -12441,29 +13245,31 @@
         <x:v>em,code</x:v>
       </x:c>
       <x:c r="U131" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V131" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W131" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X131" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y131" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z131" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA131" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB131" s="2"/>
+      <x:c r="AB131" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC131" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -12497,7 +13303,9 @@
       <x:c r="J132" s="2" t="str">
         <x:v>Information and measurement advantages</x:v>
       </x:c>
-      <x:c r="K132" s="2"/>
+      <x:c r="K132" s="2" t="str">
+        <x:v>Преимущества в информации и измерениях</x:v>
+      </x:c>
       <x:c r="L132" s="2" t="str">
         <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-271"&gt;
     &lt;a id="_idTextAnchor263"&gt;
@@ -12508,7 +13316,16 @@
    &lt;/h3&gt;
    </x:v>
       </x:c>
-      <x:c r="M132" s="2"/>
+      <x:c r="M132" s="2" t="str">
+        <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-271"&gt;
+    &lt;a id="_idTextAnchor263"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.302.1"&gt;
+     Преимущества в информации и измерениях
+    &lt;/span&gt;
+   &lt;/h3&gt;
+   </x:v>
+      </x:c>
       <x:c r="N132" s="2"/>
       <x:c r="O132" s="2"/>
       <x:c r="P132" s="2"/>
@@ -12519,29 +13336,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U132" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V132" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W132" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X132" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y132" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z132" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA132" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB132" s="2"/>
+      <x:c r="AB132" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC132" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -12573,7 +13392,9 @@
       <x:c r="J133" s="2" t="str">
         <x:v>Net returns can come from better inference: cleaner definitions, better timing discipline, more reliable labeling, and a more faithful mapping from observables to actions. This is rarely “free money”; it is often what turns a fragile backtest into a robust implementation within another category.</x:v>
       </x:c>
-      <x:c r="K133" s="2"/>
+      <x:c r="K133" s="2" t="str">
+        <x:v>Чистая доходность может быть результатом более точных выводов: более чётких определений, более строгого соблюдения временных границ, более надёжной разметки и более точного преобразования наблюдаемых данных в действия. Это редко бывает «бесплатными деньгами»; чаще именно это превращает хрупкий бэктест в надёжную реализацию в рамках другой категории.</x:v>
+      </x:c>
       <x:c r="L133" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.303.1"&gt;
@@ -12590,7 +13411,22 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M133" s="2"/>
+      <x:c r="M133" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.303.1"&gt;
+     Чистая доходность может быть результатом более точных
+    &lt;/span&gt;
+    &lt;a id="_idIndexMarker680"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.304.1"&gt;
+     выводов: более чётких определений, более строгого соблюдения временных границ, более надёжной разметки и более точного преобразования наблюдаемых данных в действия.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.304.2"&gt;
+     Это редко бывает «бесплатными деньгами»; чаще именно это превращает хрупкий бэктест в надёжную реализацию в рамках другой категории.
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N133" s="2"/>
       <x:c r="O133" s="2"/>
       <x:c r="P133" s="2"/>
@@ -12601,29 +13437,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U133" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V133" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W133" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X133" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y133" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z133" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA133" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB133" s="2"/>
+      <x:c r="AB133" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC133" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -12655,7 +13493,9 @@
       <x:c r="J134" s="2" t="str">
         <x:v>Early tests emphasize robustness to definition choices and conservative timing, sensitivity to coverage/missingness, and the extent to which incremental signal quality survives realistic costs and constraints.</x:v>
       </x:c>
-      <x:c r="K134" s="2"/>
+      <x:c r="K134" s="2" t="str">
+        <x:v>Первые проверки сосредоточены на устойчивости к выбору определений и консервативным временным допущениям, чувствительности к охвату и пропускам данных, а также на том, в какой степени дополнительное качество сигнала сохраняется после учёта реалистичных издержек и ограничений.</x:v>
+      </x:c>
       <x:c r="L134" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.305.1"&gt;
@@ -12664,7 +13504,14 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M134" s="2"/>
+      <x:c r="M134" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.305.1"&gt;
+     Первые проверки сосредоточены на устойчивости к выбору определений и консервативным временным допущениям, чувствительности к охвату и пропускам данных, а также на том, в какой степени дополнительное качество сигнала сохраняется после учёта реалистичных издержек и ограничений.
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N134" s="2"/>
       <x:c r="O134" s="2"/>
       <x:c r="P134" s="2"/>
@@ -12673,29 +13520,31 @@
       <x:c r="S134" s="2"/>
       <x:c r="T134" s="2"/>
       <x:c r="U134" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V134" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W134" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X134" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y134" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z134" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA134" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB134" s="2"/>
+      <x:c r="AB134" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC134" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -12729,7 +13578,9 @@
       <x:c r="J135" s="2" t="str">
         <x:v>Using the map</x:v>
       </x:c>
-      <x:c r="K135" s="2"/>
+      <x:c r="K135" s="2" t="str">
+        <x:v>Работа с картой</x:v>
+      </x:c>
       <x:c r="L135" s="2" t="str">
         <x:v>&lt;h2 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-2" id="_idParaDest-272"&gt;
     &lt;a id="_idTextAnchor264"&gt;
@@ -12740,7 +13591,16 @@
    &lt;/h2&gt;
    </x:v>
       </x:c>
-      <x:c r="M135" s="2"/>
+      <x:c r="M135" s="2" t="str">
+        <x:v>&lt;h2 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-2" id="_idParaDest-272"&gt;
+    &lt;a id="_idTextAnchor264"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.306.1"&gt;
+     Работа с картой
+    &lt;/span&gt;
+   &lt;/h2&gt;
+   </x:v>
+      </x:c>
       <x:c r="N135" s="2"/>
       <x:c r="O135" s="2"/>
       <x:c r="P135" s="2"/>
@@ -12751,29 +13611,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U135" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V135" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W135" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X135" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y135" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z135" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA135" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB135" s="2"/>
+      <x:c r="AB135" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC135" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -12805,7 +13667,9 @@
       <x:c r="J136" s="2" t="str">
         <x:v>A strategy is well posed when the following questions can be answered:</x:v>
       </x:c>
-      <x:c r="K136" s="2"/>
+      <x:c r="K136" s="2" t="str">
+        <x:v>Стратегия поставлена корректно, если можно ответить на следующие вопросы:</x:v>
+      </x:c>
       <x:c r="L136" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.307.1"&gt;
@@ -12819,7 +13683,19 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M136" s="2"/>
+      <x:c r="M136" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.307.1"&gt;
+     Стратегия поставлена корректно, если
+    &lt;/span&gt;
+    &lt;a id="_idIndexMarker681"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.308.1"&gt;
+     можно ответить на следующие вопросы:
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N136" s="2"/>
       <x:c r="O136" s="2"/>
       <x:c r="P136" s="2"/>
@@ -12830,29 +13706,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U136" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V136" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W136" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X136" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y136" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z136" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA136" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB136" s="2"/>
+      <x:c r="AB136" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC136" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -12884,7 +13762,9 @@
       <x:c r="J137" s="2" t="str">
         <x:v>Family and cadence: Which frictions dominate?</x:v>
       </x:c>
-      <x:c r="K137" s="2"/>
+      <x:c r="K137" s="2" t="str">
+        <x:v>Семейство и периодичность: Какие рыночные трения преобладают?</x:v>
+      </x:c>
       <x:c r="L137" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -12898,7 +13778,19 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M137" s="2"/>
+      <x:c r="M137" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
+     &lt;strong class="keyWord"&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.309.1"&gt;
+       Семейство и периодичность:
+      &lt;/span&gt;
+     &lt;/strong&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.310.1"&gt;
+      Какие рыночные трения преобладают?
+     &lt;/span&gt;
+    &lt;/li&gt;
+    </x:v>
+      </x:c>
       <x:c r="N137" s="2"/>
       <x:c r="O137" s="2"/>
       <x:c r="P137" s="2"/>
@@ -12909,29 +13801,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U137" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V137" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W137" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X137" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y137" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z137" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA137" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB137" s="2"/>
+      <x:c r="AB137" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC137" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -12963,7 +13857,9 @@
       <x:c r="J138" s="2" t="str">
         <x:v>PnL decomposition: Which payoffs generate returns, and which costs are first order?</x:v>
       </x:c>
-      <x:c r="K138" s="2"/>
+      <x:c r="K138" s="2" t="str">
+        <x:v>Декомпозиция PnL: Какие выплаты формируют доходность и какие издержки имеют первостепенное значение?</x:v>
+      </x:c>
       <x:c r="L138" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -12977,7 +13873,19 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M138" s="2"/>
+      <x:c r="M138" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
+     &lt;strong class="keyWord"&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.311.1"&gt;
+       Декомпозиция PnL:
+      &lt;/span&gt;
+     &lt;/strong&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.312.1"&gt;
+      Какие выплаты формируют доходность и какие издержки имеют первостепенное значение?
+     &lt;/span&gt;
+    &lt;/li&gt;
+    </x:v>
+      </x:c>
       <x:c r="N138" s="2"/>
       <x:c r="O138" s="2"/>
       <x:c r="P138" s="2"/>
@@ -12988,29 +13896,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U138" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V138" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W138" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X138" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y138" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z138" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA138" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB138" s="2"/>
+      <x:c r="AB138" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC138" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -13042,7 +13952,9 @@
       <x:c r="J139" s="2" t="str">
         <x:v>Edge narrative: What is the primary economic source, and why should it persist?</x:v>
       </x:c>
-      <x:c r="K139" s="2"/>
+      <x:c r="K139" s="2" t="str">
+        <x:v>Обоснование преимущества: Каков основной экономический источник и почему он должен сохраняться?</x:v>
+      </x:c>
       <x:c r="L139" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -13056,7 +13968,19 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M139" s="2"/>
+      <x:c r="M139" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
+     &lt;strong class="keyWord"&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.313.1"&gt;
+       Обоснование преимущества:
+      &lt;/span&gt;
+     &lt;/strong&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.314.1"&gt;
+      Каков основной экономический источник и почему он должен сохраняться?
+     &lt;/span&gt;
+    &lt;/li&gt;
+    </x:v>
+      </x:c>
       <x:c r="N139" s="2"/>
       <x:c r="O139" s="2"/>
       <x:c r="P139" s="2"/>
@@ -13067,29 +13991,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U139" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V139" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W139" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X139" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y139" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z139" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA139" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB139" s="2"/>
+      <x:c r="AB139" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC139" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -13121,7 +14047,9 @@
       <x:c r="J140" s="2" t="str">
         <x:v>Top failure modes: Two or three ways the strategy could fail.</x:v>
       </x:c>
-      <x:c r="K140" s="2"/>
+      <x:c r="K140" s="2" t="str">
+        <x:v>Основные режимы отказа: Два или три сценария, при которых стратегия может потерпеть неудачу.</x:v>
+      </x:c>
       <x:c r="L140" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -13135,7 +14063,19 @@
     &lt;/li&gt;
    </x:v>
       </x:c>
-      <x:c r="M140" s="2"/>
+      <x:c r="M140" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
+     &lt;strong class="keyWord"&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.315.1"&gt;
+       Основные режимы отказа:
+      &lt;/span&gt;
+     &lt;/strong&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.316.1"&gt;
+      Два или три сценария, при которых стратегия может потерпеть неудачу.
+     &lt;/span&gt;
+    &lt;/li&gt;
+   </x:v>
+      </x:c>
       <x:c r="N140" s="2"/>
       <x:c r="O140" s="2"/>
       <x:c r="P140" s="2"/>
@@ -13146,29 +14086,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U140" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V140" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W140" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X140" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y140" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z140" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA140" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB140" s="2"/>
+      <x:c r="AB140" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC140" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -13200,7 +14142,9 @@
       <x:c r="J141" s="2" t="str">
         <x:v>Answering these before expanding the search helps focus the next design decision: what to fix in the trading setup, which diagnostics to run first, and which stress tests are non-negotiable. We discuss the trading setup components next.</x:v>
       </x:c>
-      <x:c r="K141" s="2"/>
+      <x:c r="K141" s="2" t="str">
+        <x:v>Ответы на эти вопросы до расширения поиска помогают сосредоточиться на следующем проектном решении: что исправить в параметрах торговли, какую диагностику провести в первую очередь и какие стресс-тесты обязательны. Далее рассматриваются компоненты параметров торговли.</x:v>
+      </x:c>
       <x:c r="L141" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.317.1"&gt;
@@ -13212,7 +14156,17 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M141" s="2"/>
+      <x:c r="M141" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.317.1"&gt;
+     Ответы на эти вопросы до расширения поиска помогают сосредоточиться на следующем проектном решении: что исправить в параметрах торговли, какую диагностику провести в первую очередь и какие стресс-тесты обязательны.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.317.2"&gt;
+     Далее рассматриваются компоненты параметров торговли.
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N141" s="2"/>
       <x:c r="O141" s="2"/>
       <x:c r="P141" s="2"/>
@@ -13221,29 +14175,31 @@
       <x:c r="S141" s="2"/>
       <x:c r="T141" s="2"/>
       <x:c r="U141" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V141" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W141" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X141" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y141" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z141" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA141" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB141" s="2"/>
+      <x:c r="AB141" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC141" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -13277,7 +14233,9 @@
       <x:c r="J142" s="2" t="str">
         <x:v>6.3 Defining the trading setup</x:v>
       </x:c>
-      <x:c r="K142" s="2"/>
+      <x:c r="K142" s="2" t="str">
+        <x:v>6.3 Определение параметров торговли</x:v>
+      </x:c>
       <x:c r="L142" s="2" t="str">
         <x:v>&lt;h1 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-1" id="_idParaDest-273"&gt;
     &lt;a id="_idTextAnchor265"&gt;
@@ -13288,7 +14246,16 @@
    &lt;/h1&gt;
    </x:v>
       </x:c>
-      <x:c r="M142" s="2"/>
+      <x:c r="M142" s="2" t="str">
+        <x:v>&lt;h1 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-1" id="_idParaDest-273"&gt;
+    &lt;a id="_idTextAnchor265"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.318.1"&gt;
+     6.3 Определение параметров торговли
+    &lt;/span&gt;
+   &lt;/h1&gt;
+   </x:v>
+      </x:c>
       <x:c r="N142" s="2"/>
       <x:c r="O142" s="2"/>
       <x:c r="P142" s="2"/>
@@ -13299,29 +14266,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U142" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V142" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W142" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X142" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y142" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z142" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA142" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB142" s="2"/>
+      <x:c r="AB142" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC142" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -13353,7 +14322,9 @@
       <x:c r="J143" s="2" t="str">
         <x:v>Comparability breaks when the evaluation environment drifts without notice: the instrument set changes, the rebalance snapshot shifts, execution timing moves, or costs are treated differently. The trading setup is the fixed part of that environment: the invariants the code treats as constant within a research line, and every run automatically records. We can explore aggressively inside those invariants, but changing them defines a new setup and requires bumping the version.</x:v>
       </x:c>
-      <x:c r="K143" s="2"/>
+      <x:c r="K143" s="2" t="str">
+        <x:v>Сопоставимость нарушается, когда среда оценки незаметно изменяется: меняется набор инструментов, смещается срез на момент ребалансировки, изменяется время исполнения или по-разному учитываются издержки. Параметры торговли — это фиксированная часть такой среды: инварианты, которые код считает постоянными в рамках одного направления исследования и которые автоматически регистрируются при каждом запуске. Внутри этих инвариантов можно вести активный поиск, но их изменение определяет новый набор параметров и требует повышения версии.</x:v>
+      </x:c>
       <x:c r="L143" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.319.1"&gt;
@@ -13381,7 +14352,32 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M143" s="2"/>
+      <x:c r="M143" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.319.1"&gt;
+     Сопоставимость нарушается, когда среда оценки незаметно изменяется: меняется набор инструментов, смещается срез на момент ребалансировки, изменяется время исполнения или по-разному учитываются издержки.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.319.2"&gt;
+    &lt;/span&gt;
+    &lt;strong class="keyWord"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.320.1"&gt;
+      Параметры торговли
+     &lt;/span&gt;
+    &lt;/strong&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.321.1"&gt;
+     — это фиксированная
+    &lt;/span&gt;
+    &lt;a id="_idIndexMarker682"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.322.1"&gt;
+     часть такой среды: инварианты, которые код считает постоянными в рамках одного направления исследования и которые автоматически регистрируются при каждом запуске.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.322.2"&gt;
+     Внутри этих инвариантов можно вести активный поиск, но их изменение определяет новый набор параметров и требует повышения версии.
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N143" s="2"/>
       <x:c r="O143" s="2"/>
       <x:c r="P143" s="2"/>
@@ -13392,29 +14388,31 @@
         <x:v>strong,a</x:v>
       </x:c>
       <x:c r="U143" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V143" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W143" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X143" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y143" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z143" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA143" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB143" s="2"/>
+      <x:c r="AB143" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC143" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -13448,7 +14446,9 @@
       <x:c r="J144" s="2" t="str">
         <x:v>What the trading setup must fix</x:v>
       </x:c>
-      <x:c r="K144" s="2"/>
+      <x:c r="K144" s="2" t="str">
+        <x:v>Что должны фиксировать параметры торговли</x:v>
+      </x:c>
       <x:c r="L144" s="2" t="str">
         <x:v>&lt;h2 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-2" id="_idParaDest-274"&gt;
     &lt;a id="_idTextAnchor266"&gt;
@@ -13459,7 +14459,16 @@
    &lt;/h2&gt;
    </x:v>
       </x:c>
-      <x:c r="M144" s="2"/>
+      <x:c r="M144" s="2" t="str">
+        <x:v>&lt;h2 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-2" id="_idParaDest-274"&gt;
+    &lt;a id="_idTextAnchor266"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.323.1"&gt;
+     Что должны фиксировать параметры торговли
+    &lt;/span&gt;
+   &lt;/h2&gt;
+   </x:v>
+      </x:c>
       <x:c r="N144" s="2"/>
       <x:c r="O144" s="2"/>
       <x:c r="P144" s="2"/>
@@ -13470,29 +14479,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U144" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V144" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W144" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X144" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y144" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z144" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA144" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB144" s="2"/>
+      <x:c r="AB144" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC144" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -13524,7 +14535,9 @@
       <x:c r="J145" s="2" t="str">
         <x:v>The trading setup fixes the decision-time snapshot, mapping form, and friction regime, rather than enumerating every lookback or threshold. It should cover the following topics:</x:v>
       </x:c>
-      <x:c r="K145" s="2"/>
+      <x:c r="K145" s="2" t="str">
+        <x:v>Параметры торговли фиксируют срез на момент принятия решения, форму преобразования и режим учёта рыночных трений, а не перечисляют каждое ретроспективное окно или пороговое значение. Они должны охватывать следующие темы:</x:v>
+      </x:c>
       <x:c r="L145" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.324.1"&gt;
@@ -13536,7 +14549,17 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M145" s="2"/>
+      <x:c r="M145" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.324.1"&gt;
+     Параметры торговли фиксируют срез на момент принятия решения, форму преобразования и режим учёта рыночных трений, а не перечисляют каждое ретроспективное окно или пороговое значение.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.324.2"&gt;
+     Они должны охватывать следующие темы:
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N145" s="2"/>
       <x:c r="O145" s="2"/>
       <x:c r="P145" s="2"/>
@@ -13545,29 +14568,31 @@
       <x:c r="S145" s="2"/>
       <x:c r="T145" s="2"/>
       <x:c r="U145" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V145" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W145" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X145" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y145" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z145" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA145" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB145" s="2"/>
+      <x:c r="AB145" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC145" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -13601,7 +14626,9 @@
       <x:c r="J146" s="2" t="str">
         <x:v>Universe and tradability rules</x:v>
       </x:c>
-      <x:c r="K146" s="2"/>
+      <x:c r="K146" s="2" t="str">
+        <x:v>Правила формирования совокупности активов и допуска к торговле</x:v>
+      </x:c>
       <x:c r="L146" s="2" t="str">
         <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-275"&gt;
     &lt;a id="_idTextAnchor267"&gt;
@@ -13612,7 +14639,16 @@
    &lt;/h3&gt;
    </x:v>
       </x:c>
-      <x:c r="M146" s="2"/>
+      <x:c r="M146" s="2" t="str">
+        <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-275"&gt;
+    &lt;a id="_idTextAnchor267"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.325.1"&gt;
+     Правила формирования совокупности активов и допуска к торговле
+    &lt;/span&gt;
+   &lt;/h3&gt;
+   </x:v>
+      </x:c>
       <x:c r="N146" s="2"/>
       <x:c r="O146" s="2"/>
       <x:c r="P146" s="2"/>
@@ -13623,29 +14659,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U146" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V146" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W146" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X146" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y146" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z146" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA146" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB146" s="2"/>
+      <x:c r="AB146" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC146" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
@@ -13677,7 +14715,9 @@
       <x:c r="J147" s="2" t="str">
         <x:v>Define eligibility and membership mechanics that make pricing and execution economically meaningful. Specify filters (liquidity, listing venue, contract type), and how listings, delistings, and stale or missing prices are handled. For example, etfs need explicit investability filters and rules for ETF launches and closures; crypto_perps_funding needs venue and contract eligibility and a rule for how convention changes (such as fees, funding caps, margining) are treated.</x:v>
       </x:c>
-      <x:c r="K147" s="2"/>
+      <x:c r="K147" s="2" t="str">
+        <x:v>Определите механизмы допуска и включения активов, при которых ценообразование и исполнение имеют экономический смысл. Задайте фильтры (ликвидность, торговая площадка, тип контракта), а также порядок обработки листинга, делистинга и устаревших или отсутствующих цен. Например, для etfs нужны явные фильтры доступности для инвестирования и правила запуска и закрытия ETF; для crypto_perps_funding нужны критерии допуска торговых площадок и контрактов, а также правило учёта изменений рыночных соглашений (например, комиссий, ограничений ставок финансирования и порядка расчёта маржи).</x:v>
+      </x:c>
       <x:c r="L147" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.326.1"&gt;
@@ -13713,7 +14753,41 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M147" s="2"/>
+      <x:c r="M147" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.326.1"&gt;
+     Определите механизмы допуска и включения активов,
+    &lt;/span&gt;
+    &lt;a id="_idIndexMarker683"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.327.1"&gt;
+     при которых ценообразование и исполнение имеют экономический смысл.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.327.2"&gt;
+     Задайте фильтры (ликвидность, торговая площадка, тип контракта), а также порядок обработки листинга, делистинга и устаревших или отсутствующих цен.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.327.3"&gt;
+     Например, для
+    &lt;/span&gt;
+    &lt;code class="inlineCode"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.328.1"&gt;
+      etfs
+     &lt;/span&gt;
+    &lt;/code&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.329.1"&gt;
+     нужны явные фильтры доступности для инвестирования и правила запуска и закрытия ETF; для
+    &lt;/span&gt;
+    &lt;code class="inlineCode"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.330.1"&gt;
+      crypto_perps_funding
+     &lt;/span&gt;
+    &lt;/code&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.331.1"&gt;
+     нужны критерии допуска торговых площадок и контрактов, а также правило учёта изменений рыночных соглашений (например, комиссий, ограничений ставок финансирования и порядка расчёта маржи).
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N147" s="2"/>
       <x:c r="O147" s="2"/>
       <x:c r="P147" s="2"/>
@@ -13724,29 +14798,31 @@
         <x:v>code,a</x:v>
       </x:c>
       <x:c r="U147" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V147" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W147" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X147" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y147" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z147" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA147" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB147" s="2"/>
+      <x:c r="AB147" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC147" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -13780,7 +14856,9 @@
       <x:c r="J148" s="2" t="str">
         <x:v>Decision schedule and admissible information</x:v>
       </x:c>
-      <x:c r="K148" s="2"/>
+      <x:c r="K148" s="2" t="str">
+        <x:v>График принятия решений и допустимая информация</x:v>
+      </x:c>
       <x:c r="L148" s="2" t="str">
         <x:v>&lt;h2 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-2" id="_idParaDest-276"&gt;
     &lt;a id="_idTextAnchor268"&gt;
@@ -13791,7 +14869,16 @@
    &lt;/h2&gt;
    </x:v>
       </x:c>
-      <x:c r="M148" s="2"/>
+      <x:c r="M148" s="2" t="str">
+        <x:v>&lt;h2 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-2" id="_idParaDest-276"&gt;
+    &lt;a id="_idTextAnchor268"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.332.1"&gt;
+     График принятия решений и допустимая информация
+    &lt;/span&gt;
+   &lt;/h2&gt;
+   </x:v>
+      </x:c>
       <x:c r="N148" s="2"/>
       <x:c r="O148" s="2"/>
       <x:c r="P148" s="2"/>
@@ -13802,29 +14889,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U148" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V148" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W148" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X148" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y148" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z148" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA148" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB148" s="2"/>
+      <x:c r="AB148" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC148" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -13856,7 +14945,9 @@
       <x:c r="J149" s="2" t="str">
         <x:v>Specify the trading snapshot and what is knowable at that moment. This is the guardrail against leakage, so it must be explicit: the timestamp convention, the bar frequency (if any), and any mechanical execution delay. etfs might use a weekly or month-end snapshot; crypto_perps_funding aligns decisions with the funding timestamp; nasdaq100_microstructure requires a fixed bar schedule and a stated observation-to-execution delay because a one-bar shift can change results.</x:v>
       </x:c>
-      <x:c r="K149" s="2"/>
+      <x:c r="K149" s="2" t="str">
+        <x:v>Задайте торговый срез и сведения, которые могут быть известны в этот момент. Это защита от утечки информации, поэтому необходимо явно определить соглашение о временных метках, частоту баров (если применимо) и любую механическую задержку исполнения. Для etfs может использоваться еженедельный срез или срез на конец месяца; в crypto_perps_funding решения синхронизируются с моментом начисления финансирования; для nasdaq100_microstructure необходимы фиксированное расписание баров и заданная задержка между наблюдением и исполнением, поскольку сдвиг на один бар способен изменить результаты.</x:v>
+      </x:c>
       <x:c r="L149" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.333.1"&gt;
@@ -13902,7 +14993,51 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M149" s="2"/>
+      <x:c r="M149" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.333.1"&gt;
+     Задайте торговый
+    &lt;/span&gt;
+    &lt;a id="_idIndexMarker684"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.334.1"&gt;
+     срез и сведения, которые могут быть
+    &lt;/span&gt;
+    &lt;a id="_idIndexMarker685"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.335.1"&gt;
+     известны в этот момент.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.335.2"&gt;
+     Это защита от утечки информации, поэтому необходимо явно определить соглашение о временных метках, частоту баров (если применимо) и любую механическую задержку исполнения. Для
+    &lt;/span&gt;
+    &lt;code class="inlineCode"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.336.1"&gt;
+      etfs
+     &lt;/span&gt;
+    &lt;/code&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.337.1"&gt;
+     может использоваться еженедельный срез или срез на конец месяца; в
+    &lt;/span&gt;
+    &lt;code class="inlineCode"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.338.1"&gt;
+      crypto_perps_funding
+     &lt;/span&gt;
+    &lt;/code&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.339.1"&gt;
+     решения синхронизируются с моментом начисления финансирования; для
+    &lt;/span&gt;
+    &lt;code class="inlineCode"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.340.1"&gt;
+      nasdaq100_microstructure
+     &lt;/span&gt;
+    &lt;/code&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.341.1"&gt;
+     необходимы фиксированное расписание баров и заданная задержка между наблюдением и исполнением, поскольку сдвиг на один бар способен изменить результаты.
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N149" s="2"/>
       <x:c r="O149" s="2"/>
       <x:c r="P149" s="2"/>
@@ -13913,29 +15048,31 @@
         <x:v>code,a</x:v>
       </x:c>
       <x:c r="U149" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V149" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W149" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X149" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y149" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z149" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA149" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB149" s="2"/>
+      <x:c r="AB149" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC149" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -13969,7 +15106,9 @@
       <x:c r="J150" s="2" t="str">
         <x:v>Cadence and horizon feasibility</x:v>
       </x:c>
-      <x:c r="K150" s="2"/>
+      <x:c r="K150" s="2" t="str">
+        <x:v>Осуществимость периодичности и горизонта</x:v>
+      </x:c>
       <x:c r="L150" s="2" t="str">
         <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-277"&gt;
     &lt;a id="_idTextAnchor269"&gt;
@@ -13980,7 +15119,16 @@
    &lt;/h3&gt;
    </x:v>
       </x:c>
-      <x:c r="M150" s="2"/>
+      <x:c r="M150" s="2" t="str">
+        <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-277"&gt;
+    &lt;a id="_idTextAnchor269"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.342.1"&gt;
+     Осуществимость периодичности и горизонта
+    &lt;/span&gt;
+   &lt;/h3&gt;
+   </x:v>
+      </x:c>
       <x:c r="N150" s="2"/>
       <x:c r="O150" s="2"/>
       <x:c r="P150" s="2"/>
@@ -13991,29 +15139,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U150" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V150" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W150" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X150" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y150" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z150" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA150" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB150" s="2"/>
+      <x:c r="AB150" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC150" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
@@ -14045,7 +15195,9 @@
       <x:c r="J151" s="2" t="str">
         <x:v>The cadence choice is intimately linked to costs: at each horizon, what fraction of typical price moves exceeds round-trip transaction costs? This principle determines feasibility before considering any signal.</x:v>
       </x:c>
-      <x:c r="K151" s="2"/>
+      <x:c r="K151" s="2" t="str">
+        <x:v>Выбор периодичности неразрывно связан с издержками: какая доля типичных ценовых движений на каждом горизонте превышает транзакционные издержки полного цикла сделки? Этот принцип определяет осуществимость ещё до рассмотрения какого-либо сигнала.</x:v>
+      </x:c>
       <x:c r="L151" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.343.1"&gt;
@@ -14062,7 +15214,22 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M151" s="2"/>
+      <x:c r="M151" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.343.1"&gt;
+     Выбор периодичности
+    &lt;/span&gt;
+    &lt;a id="_idIndexMarker686"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.344.1"&gt;
+     неразрывно связан с издержками: какая доля типичных ценовых движений на каждом горизонте превышает транзакционные издержки полного цикла сделки?
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.344.2"&gt;
+     Этот принцип определяет осуществимость ещё до рассмотрения какого-либо сигнала.
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N151" s="2"/>
       <x:c r="O151" s="2"/>
       <x:c r="P151" s="2"/>
@@ -14073,29 +15240,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U151" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V151" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W151" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X151" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y151" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z151" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA151" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB151" s="2"/>
+      <x:c r="AB151" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC151" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
@@ -14127,7 +15296,9 @@
       <x:c r="J152" s="2" t="str">
         <x:v>Each case study includes a setup notebook with a horizon feasibility analysis that shows return distributions across multiple cadences and a cost reference line. These identify three regimes:</x:v>
       </x:c>
-      <x:c r="K152" s="2"/>
+      <x:c r="K152" s="2" t="str">
+        <x:v>Каждый практический пример включает ноутбук настройки с анализом осуществимости горизонта, который показывает распределения доходности при нескольких вариантах периодичности и контрольную линию издержек. Такой анализ выделяет три режима:</x:v>
+      </x:c>
       <x:c r="L152" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.345.1"&gt;
@@ -14144,7 +15315,22 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M152" s="2"/>
+      <x:c r="M152" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.345.1"&gt;
+     Каждый практический пример включает ноутбук настройки с
+    &lt;/span&gt;
+    &lt;a id="_idIndexMarker687"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.346.1"&gt;
+     анализом осуществимости горизонта, который показывает распределения доходности при нескольких вариантах периодичности и контрольную линию издержек.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.346.2"&gt;
+     Такой анализ выделяет три режима:
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N152" s="2"/>
       <x:c r="O152" s="2"/>
       <x:c r="P152" s="2"/>
@@ -14155,29 +15341,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U152" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V152" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W152" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X152" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y152" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z152" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA152" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB152" s="2"/>
+      <x:c r="AB152" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC152" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -14209,7 +15397,9 @@
       <x:c r="J153" s="2" t="str">
         <x:v>A hard floor where costs clearly dominate (for example, nasdaq100_microstructure at 15-minute bars)</x:v>
       </x:c>
-      <x:c r="K153" s="2"/>
+      <x:c r="K153" s="2" t="str">
+        <x:v>Жёсткая нижняя граница, ниже которой издержки явно преобладают (например, nasdaq100_microstructure при 15-минутных барах)</x:v>
+      </x:c>
       <x:c r="L153" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.347.1"&gt;
@@ -14239,7 +15429,34 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M153" s="2"/>
+      <x:c r="M153" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.347.1"&gt;
+     &lt;/span&gt;
+     &lt;strong class="keyWord"&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.348.1"&gt;
+       Жёсткая нижняя граница
+      &lt;/span&gt;
+     &lt;/strong&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.349.1"&gt;
+      , ниже которой
+     &lt;/span&gt;
+     &lt;a id="_idIndexMarker688"&gt;
+     &lt;/a&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.350.1"&gt;
+      издержки явно преобладают (например,
+     &lt;/span&gt;
+     &lt;code class="inlineCode"&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.351.1"&gt;
+       nasdaq100_microstructure
+      &lt;/span&gt;
+     &lt;/code&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.352.1"&gt;
+      при 15-минутных барах)
+     &lt;/span&gt;
+    &lt;/li&gt;
+    </x:v>
+      </x:c>
       <x:c r="N153" s="2"/>
       <x:c r="O153" s="2"/>
       <x:c r="P153" s="2"/>
@@ -14250,29 +15467,31 @@
         <x:v>strong,code,a</x:v>
       </x:c>
       <x:c r="U153" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V153" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W153" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X153" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y153" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z153" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA153" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB153" s="2"/>
+      <x:c r="AB153" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC153" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -14304,7 +15523,9 @@
       <x:c r="J154" s="2" t="str">
         <x:v>A gray zone where feasibility depends on signal strength and turnover (for example, etfs for daily trading)</x:v>
       </x:c>
-      <x:c r="K154" s="2"/>
+      <x:c r="K154" s="2" t="str">
+        <x:v>Серая зона, в которой осуществимость зависит от силы сигнала и оборота портфеля (например, etfs при ежедневной торговле)</x:v>
+      </x:c>
       <x:c r="L154" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.353.1"&gt;
@@ -14334,7 +15555,34 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M154" s="2"/>
+      <x:c r="M154" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.353.1"&gt;
+     &lt;/span&gt;
+     &lt;strong class="keyWord"&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.354.1"&gt;
+       Серая зона
+      &lt;/span&gt;
+     &lt;/strong&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.355.1"&gt;
+      , в которой
+     &lt;/span&gt;
+     &lt;a id="_idIndexMarker689"&gt;
+     &lt;/a&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.356.1"&gt;
+      осуществимость зависит от силы сигнала и оборота портфеля (например,
+     &lt;/span&gt;
+     &lt;code class="inlineCode"&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.357.1"&gt;
+       etfs
+      &lt;/span&gt;
+     &lt;/code&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.358.1"&gt;
+      при ежедневной торговле)
+     &lt;/span&gt;
+    &lt;/li&gt;
+    </x:v>
+      </x:c>
       <x:c r="N154" s="2"/>
       <x:c r="O154" s="2"/>
       <x:c r="P154" s="2"/>
@@ -14345,29 +15593,31 @@
         <x:v>strong,code,a</x:v>
       </x:c>
       <x:c r="U154" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V154" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W154" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X154" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y154" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z154" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA154" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB154" s="2"/>
+      <x:c r="AB154" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC154" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -14399,7 +15649,9 @@
       <x:c r="J155" s="2" t="str">
         <x:v>A comfortable zone where costs are not the binding constraint (for example, etfs with monthly rebalancing)</x:v>
       </x:c>
-      <x:c r="K155" s="2"/>
+      <x:c r="K155" s="2" t="str">
+        <x:v>Комфортная зона, в которой издержки не являются связывающим ограничением (например, etfs при ежемесячной ребалансировке)</x:v>
+      </x:c>
       <x:c r="L155" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.359.1"&gt;
@@ -14429,7 +15681,34 @@
     &lt;/li&gt;
    </x:v>
       </x:c>
-      <x:c r="M155" s="2"/>
+      <x:c r="M155" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.359.1"&gt;
+     &lt;/span&gt;
+     &lt;strong class="keyWord"&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.360.1"&gt;
+       Комфортная зона
+      &lt;/span&gt;
+     &lt;/strong&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.361.1"&gt;
+      , в которой
+     &lt;/span&gt;
+     &lt;a id="_idIndexMarker690"&gt;
+     &lt;/a&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.362.1"&gt;
+      издержки не являются связывающим ограничением (например,
+     &lt;/span&gt;
+     &lt;code class="inlineCode"&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.363.1"&gt;
+       etfs
+      &lt;/span&gt;
+     &lt;/code&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.364.1"&gt;
+      при ежемесячной ребалансировке)
+     &lt;/span&gt;
+    &lt;/li&gt;
+   </x:v>
+      </x:c>
       <x:c r="N155" s="2"/>
       <x:c r="O155" s="2"/>
       <x:c r="P155" s="2"/>
@@ -14440,29 +15719,31 @@
         <x:v>strong,code,a</x:v>
       </x:c>
       <x:c r="U155" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V155" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W155" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X155" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y155" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z155" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA155" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB155" s="2"/>
+      <x:c r="AB155" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC155" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -14494,7 +15775,9 @@
       <x:c r="J156" s="2" t="str">
         <x:v>The cadence decision is made in the following chapters, when signal diagnostics reveal whether features are sufficiently predictive, either on a standalone basis or in a model context, to justify trading at a given frequency.</x:v>
       </x:c>
-      <x:c r="K156" s="2"/>
+      <x:c r="K156" s="2" t="str">
+        <x:v>Решение о периодичности принимается в следующих главах, когда диагностика сигнала показывает, обладают ли признаки достаточной предсказательной способностью — самостоятельно или в контексте модели, — чтобы оправдать торговлю с заданной частотой.</x:v>
+      </x:c>
       <x:c r="L156" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.365.1"&gt;
@@ -14503,7 +15786,14 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M156" s="2"/>
+      <x:c r="M156" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.365.1"&gt;
+     Решение о периодичности принимается в следующих главах, когда диагностика сигнала показывает, обладают ли признаки достаточной предсказательной способностью — самостоятельно или в контексте модели, — чтобы оправдать торговлю с заданной частотой.
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N156" s="2"/>
       <x:c r="O156" s="2"/>
       <x:c r="P156" s="2"/>
@@ -14512,29 +15802,31 @@
       <x:c r="S156" s="2"/>
       <x:c r="T156" s="2"/>
       <x:c r="U156" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V156" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W156" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X156" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y156" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z156" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA156" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB156" s="2"/>
+      <x:c r="AB156" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC156" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
@@ -14568,7 +15860,9 @@
       <x:c r="J157" s="2" t="str">
         <x:v>Score-to-trade mapping</x:v>
       </x:c>
-      <x:c r="K157" s="2"/>
+      <x:c r="K157" s="2" t="str">
+        <x:v>Преобразование оценки модели в сделку</x:v>
+      </x:c>
       <x:c r="L157" s="2" t="str">
         <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-278"&gt;
     &lt;a id="_idTextAnchor270"&gt;
@@ -14579,7 +15873,16 @@
    &lt;/h3&gt;
    </x:v>
       </x:c>
-      <x:c r="M157" s="2"/>
+      <x:c r="M157" s="2" t="str">
+        <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-278"&gt;
+    &lt;a id="_idTextAnchor270"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.366.1"&gt;
+     Преобразование оценки модели в сделку
+    &lt;/span&gt;
+   &lt;/h3&gt;
+   </x:v>
+      </x:c>
       <x:c r="N157" s="2"/>
       <x:c r="O157" s="2"/>
       <x:c r="P157" s="2"/>
@@ -14590,29 +15893,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U157" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V157" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W157" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X157" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y157" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z157" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA157" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB157" s="2"/>
+      <x:c r="AB157" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC157" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -14644,7 +15949,9 @@
       <x:c r="J158" s="2" t="str">
         <x:v>Define how a model’s score translates into orders, positions, and exits. This mapping determines trade frequency, holding-period distribution, and where costs and constraints bite. At a minimum, determine the following design parameters to ensure results are comparable:</x:v>
       </x:c>
-      <x:c r="K158" s="2"/>
+      <x:c r="K158" s="2" t="str">
+        <x:v>Определите, как оценка модели преобразуется в заявки, позиции и выходы. Это преобразование определяет частоту сделок, распределение периодов удержания и то, где начинают сказываться издержки и ограничения. Чтобы обеспечить сопоставимость результатов, необходимо как минимум определить следующие проектные параметры:</x:v>
+      </x:c>
       <x:c r="L158" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.367.1"&gt;
@@ -14664,7 +15971,25 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M158" s="2"/>
+      <x:c r="M158" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.367.1"&gt;
+     Определите, как оценка модели
+    &lt;/span&gt;
+    &lt;a id="_idIndexMarker691"&gt;
+    &lt;/a&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.368.1"&gt;
+     преобразуется в заявки, позиции и выходы.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.368.2"&gt;
+     Это преобразование определяет частоту сделок, распределение периодов удержания и то, где начинают сказываться издержки и ограничения.
+    &lt;/span&gt;
+    &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.368.3"&gt;
+     Чтобы обеспечить сопоставимость результатов, необходимо как минимум определить следующие проектные параметры:
+    &lt;/span&gt;
+   &lt;/p&gt;
+   </x:v>
+      </x:c>
       <x:c r="N158" s="2"/>
       <x:c r="O158" s="2"/>
       <x:c r="P158" s="2"/>
@@ -14675,29 +16000,31 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U158" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V158" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W158" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X158" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y158" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z158" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA158" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB158" s="2"/>
+      <x:c r="AB158" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC158" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -14729,7 +16056,9 @@
       <x:c r="J159" s="2" t="str">
         <x:v>Position state space: For example, long-only, long/short, or multi-leg (spread/hedge).</x:v>
       </x:c>
-      <x:c r="K159" s="2"/>
+      <x:c r="K159" s="2" t="str">
+        <x:v>Пространство состояний позиции: Например, только длинные позиции, длинные/короткие позиции или позиции с несколькими компонентами (спред/хедж).</x:v>
+      </x:c>
       <x:c r="L159" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -14743,7 +16072,19 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M159" s="2"/>
+      <x:c r="M159" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
+     &lt;strong class="keyWord"&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.369.1"&gt;
+       Пространство состояний позиции:
+      &lt;/span&gt;
+     &lt;/strong&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.370.1"&gt;
+      Например, только длинные позиции, длинные/короткие позиции или позиции с несколькими компонентами (спред/хедж).
+     &lt;/span&gt;
+    &lt;/li&gt;
+    </x:v>
+      </x:c>
       <x:c r="N159" s="2"/>
       <x:c r="O159" s="2"/>
       <x:c r="P159" s="2"/>
@@ -14754,29 +16095,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U159" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V159" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W159" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X159" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y159" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z159" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA159" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB159" s="2"/>
+      <x:c r="AB159" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC159" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -14808,7 +16151,9 @@
       <x:c r="J160" s="2" t="str">
         <x:v>Entry logic: For example, rank selection or threshold gating.</x:v>
       </x:c>
-      <x:c r="K160" s="2"/>
+      <x:c r="K160" s="2" t="str">
+        <x:v>Логика входа: Например, отбор по рангу или применение порогового условия.</x:v>
+      </x:c>
       <x:c r="L160" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -14822,7 +16167,19 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M160" s="2"/>
+      <x:c r="M160" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
+     &lt;strong class="keyWord"&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.371.1"&gt;
+       Логика входа:
+      &lt;/span&gt;
+     &lt;/strong&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.372.1"&gt;
+      Например, отбор по рангу или применение порогового условия.
+     &lt;/span&gt;
+    &lt;/li&gt;
+    </x:v>
+      </x:c>
       <x:c r="N160" s="2"/>
       <x:c r="O160" s="2"/>
       <x:c r="P160" s="2"/>
@@ -14833,29 +16190,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U160" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V160" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W160" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X160" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y160" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z160" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA160" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB160" s="2"/>
+      <x:c r="AB160" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC160" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -14887,7 +16246,9 @@
       <x:c r="J161" s="2" t="str">
         <x:v>Exit logic: For example, time-, signal-, or risk-based exit.</x:v>
       </x:c>
-      <x:c r="K161" s="2"/>
+      <x:c r="K161" s="2" t="str">
+        <x:v>Логика выхода: Например, выход по времени, сигналу или риску.</x:v>
+      </x:c>
       <x:c r="L161" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -14901,7 +16262,19 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M161" s="2"/>
+      <x:c r="M161" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
+     &lt;strong class="keyWord"&gt;
+      &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.373.1"&gt;
+       Логика выхода:
+      &lt;/span&gt;
+     &lt;/strong&gt;
+     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.374.1"&gt;
+      Например, выход по времени, сигналу или риску.
+     &lt;/span&gt;
+    &lt;/li&gt;
+    </x:v>
+      </x:c>
       <x:c r="N161" s="2"/>
       <x:c r="O161" s="2"/>
       <x:c r="P161" s="2"/>
@@ -14912,29 +16285,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U161" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V161" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W161" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X161" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y161" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z161" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA161" s="2" t="str">
         <x:v>CH06-BATCH-004</x:v>
       </x:c>
-      <x:c r="AB161" s="2"/>
+      <x:c r="AB161" s="2" t="str">
+        <x:v>CH06-BATCH-004: выполнены 7 QA-проверок — смысловая точность, полнота, глоссарий, числа и обозначения, код и ссылки, структурная эквивалентность, форматирование; PASS.</x:v>
+      </x:c>
       <x:c r="AC161" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>CH06 v0.5 / BATCH-004</x:v>
       </x:c>
     </x:row>
     <x:row r="162">

--- a/chapters/CH06/registry/CH06_registry_v0.1_current.xlsx
+++ b/chapters/CH06/registry/CH06_registry_v0.1_current.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Блоки" sheetId="1" r:id="Rc9a1de05815b4812"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Блоки" sheetId="1" r:id="Rcedc46f915bb4461"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16332,16 +16332,18 @@
         <x:v>/*/*[2]/*/*[92]/*[4]</x:v>
       </x:c>
       <x:c r="G162" s="2"/>
-      <x:c r="H162" s="2" t="n">
+      <x:c r="H162" s="2" t="str">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="I162" s="2" t="n">
+      <x:c r="I162" s="2" t="str">
         <x:v>133</x:v>
       </x:c>
       <x:c r="J162" s="2" t="str">
         <x:v>Position sizing: How scores translate into exposures (for example, equal weight, volatility targeting).</x:v>
       </x:c>
-      <x:c r="K162" s="2"/>
+      <x:c r="K162" s="2" t="str">
+        <x:v>Определение размера позиции: как оценки преобразуются в величины подверженности риску (например, равные веса, таргетирование волатильности).</x:v>
+      </x:c>
       <x:c r="L162" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -16355,7 +16357,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M162" s="2"/>
+      <x:c r="M162" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.375.1"&gt;Определение размера позиции: &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.376.1"&gt;как оценки преобразуются в величины подверженности риску (например, равные веса, таргетирование волатильности).&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N162" s="2"/>
       <x:c r="O162" s="2"/>
       <x:c r="P162" s="2"/>
@@ -16366,29 +16370,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U162" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V162" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W162" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X162" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y162" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z162" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA162" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB162" s="2"/>
+      <x:c r="AB162" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC162" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -16411,16 +16417,18 @@
         <x:v>/*/*[2]/*/*[92]/*[5]</x:v>
       </x:c>
       <x:c r="G163" s="2"/>
-      <x:c r="H163" s="2" t="n">
+      <x:c r="H163" s="2" t="str">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="I163" s="2" t="n">
+      <x:c r="I163" s="2" t="str">
         <x:v>133</x:v>
       </x:c>
       <x:c r="J163" s="2" t="str">
         <x:v>Order timing: When orders are placed (at open, intraday window, execution delay).</x:v>
       </x:c>
-      <x:c r="K163" s="2"/>
+      <x:c r="K163" s="2" t="str">
+        <x:v>Время размещения заявок: когда размещаются заявки (на открытии, в течение внутридневного окна, с задержкой исполнения).</x:v>
+      </x:c>
       <x:c r="L163" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -16434,7 +16442,9 @@
     &lt;/li&gt;
    </x:v>
       </x:c>
-      <x:c r="M163" s="2"/>
+      <x:c r="M163" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.377.1"&gt;Время размещения заявок: &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.378.1"&gt;когда размещаются заявки (на открытии, в течение внутридневного окна, с задержкой исполнения).&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N163" s="2"/>
       <x:c r="O163" s="2"/>
       <x:c r="P163" s="2"/>
@@ -16445,29 +16455,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U163" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V163" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W163" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X163" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y163" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z163" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA163" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB163" s="2"/>
+      <x:c r="AB163" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC163" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -16490,16 +16502,18 @@
         <x:v>/*/*[2]/*/*[93]</x:v>
       </x:c>
       <x:c r="G164" s="2"/>
-      <x:c r="H164" s="2" t="n">
+      <x:c r="H164" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I164" s="2" t="n">
+      <x:c r="I164" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J164" s="2" t="str">
         <x:v>The specifics will likely evolve, but when they do, the reference for comparison will as well.</x:v>
       </x:c>
-      <x:c r="K164" s="2"/>
+      <x:c r="K164" s="2" t="str">
+        <x:v>Конкретные параметры, вероятно, будут меняться, но вместе с ними будет меняться и база сравнения.</x:v>
+      </x:c>
       <x:c r="L164" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.379.1"&gt;
@@ -16508,7 +16522,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M164" s="2"/>
+      <x:c r="M164" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.379.1"&gt;Конкретные параметры, вероятно, будут меняться, но вместе с ними будет меняться и база сравнения.&lt;/span&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N164" s="2"/>
       <x:c r="O164" s="2"/>
       <x:c r="P164" s="2"/>
@@ -16517,27 +16533,29 @@
       <x:c r="S164" s="2"/>
       <x:c r="T164" s="2"/>
       <x:c r="U164" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V164" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W164" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X164" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y164" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z164" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA164" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB164" s="2"/>
+      <x:c r="AB164" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC164" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -16564,16 +16582,18 @@
       <x:c r="G165" s="2" t="str">
         <x:v>_idParaDest-279</x:v>
       </x:c>
-      <x:c r="H165" s="2" t="n">
+      <x:c r="H165" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I165" s="2" t="n">
+      <x:c r="I165" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J165" s="2" t="str">
         <x:v>Constraints and risk controls in scope</x:v>
       </x:c>
-      <x:c r="K165" s="2"/>
+      <x:c r="K165" s="2" t="str">
+        <x:v>Ограничения и меры контроля риска, учитываемые в исследовании</x:v>
+      </x:c>
       <x:c r="L165" s="2" t="str">
         <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-279"&gt;
     &lt;a id="_idTextAnchor271"&gt;
@@ -16584,7 +16604,9 @@
    &lt;/h3&gt;
    </x:v>
       </x:c>
-      <x:c r="M165" s="2"/>
+      <x:c r="M165" s="2" t="str">
+        <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-279"&gt;&lt;a id="_idTextAnchor271"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.380.1"&gt;Ограничения и меры контроля риска, учитываемые в исследовании&lt;/span&gt;&lt;/h3&gt;</x:v>
+      </x:c>
       <x:c r="N165" s="2"/>
       <x:c r="O165" s="2"/>
       <x:c r="P165" s="2"/>
@@ -16595,27 +16617,29 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U165" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V165" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W165" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X165" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y165" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z165" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA165" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB165" s="2"/>
+      <x:c r="AB165" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC165" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -16640,16 +16664,18 @@
         <x:v>/*/*[2]/*/*[95]</x:v>
       </x:c>
       <x:c r="G166" s="2"/>
-      <x:c r="H166" s="2" t="n">
+      <x:c r="H166" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I166" s="2" t="n">
+      <x:c r="I166" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J166" s="2" t="str">
         <x:v>Specify the constraints treated as binding: exposure and leverage limits, concentration rules, and any liquidity or capacity limits enforced. Risk controls that alter trading actions (for example, a de-risking overlay or a kill switch) must be explicit and versioned, as they alter the effective strategy.</x:v>
       </x:c>
-      <x:c r="K166" s="2"/>
+      <x:c r="K166" s="2" t="str">
+        <x:v>Укажите ограничения, считающиеся обязательными: лимиты подверженности риску и кредитного плеча, правила концентрации, а также применяемые ограничения ликвидности или ёмкости стратегии. Меры контроля риска, изменяющие торговые действия (например, дополнительный механизм снижения риска или механизм аварийной остановки торговли), должны быть заданы явно и версионироваться, поскольку они изменяют фактическую стратегию.</x:v>
+      </x:c>
       <x:c r="L166" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.381.1"&gt;
@@ -16666,7 +16692,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M166" s="2"/>
+      <x:c r="M166" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.381.1"&gt;Укажите ограничения, считающиеся обязательными: лимиты подверженности риску и кредитного плеча, правила концентрации, а также применяемые ограничения ликвидности или ёмкости стратегии. Меры контроля риска, изменяющие торговые действия (например, дополнительный механизм снижения риска или механизм аварийной остановки торговли), должны быть заданы явно и версионироваться, поскольку они изменяют фактическую стратегию.&lt;/span&gt;&lt;a id="_idIndexMarker692"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.382.1"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.382.2"/&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N166" s="2"/>
       <x:c r="O166" s="2"/>
       <x:c r="P166" s="2"/>
@@ -16677,27 +16705,29 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U166" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V166" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W166" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X166" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y166" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z166" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA166" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB166" s="2"/>
+      <x:c r="AB166" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC166" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -16724,16 +16754,18 @@
       <x:c r="G167" s="2" t="str">
         <x:v>_idParaDest-280</x:v>
       </x:c>
-      <x:c r="H167" s="2" t="n">
+      <x:c r="H167" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I167" s="2" t="n">
+      <x:c r="I167" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J167" s="2" t="str">
         <x:v>Cost model class and components</x:v>
       </x:c>
-      <x:c r="K167" s="2"/>
+      <x:c r="K167" s="2" t="str">
+        <x:v>Класс и компоненты модели издержек</x:v>
+      </x:c>
       <x:c r="L167" s="2" t="str">
         <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-280"&gt;
     &lt;a id="_idTextAnchor272"&gt;
@@ -16744,7 +16776,9 @@
    &lt;/h3&gt;
    </x:v>
       </x:c>
-      <x:c r="M167" s="2"/>
+      <x:c r="M167" s="2" t="str">
+        <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-280"&gt;&lt;a id="_idTextAnchor272"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.383.1"&gt;Класс и компоненты модели издержек&lt;/span&gt;&lt;/h3&gt;</x:v>
+      </x:c>
       <x:c r="N167" s="2"/>
       <x:c r="O167" s="2"/>
       <x:c r="P167" s="2"/>
@@ -16755,27 +16789,29 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U167" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V167" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W167" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X167" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y167" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z167" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA167" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB167" s="2"/>
+      <x:c r="AB167" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC167" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -16800,16 +16836,18 @@
         <x:v>/*/*[2]/*/*[97]</x:v>
       </x:c>
       <x:c r="G168" s="2"/>
-      <x:c r="H168" s="2" t="n">
+      <x:c r="H168" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I168" s="2" t="n">
+      <x:c r="I168" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J168" s="2" t="str">
         <x:v>Early research does not need a perfect simulator, but it does require consistency about which frictions are treated as material. State the cost components included (fees, spreads, slippage/impact, financing or funding, borrow, roll) and how conservative the assumptions are. Later chapters expand the cost model; early screens use conservative, coarse assumptions.</x:v>
       </x:c>
-      <x:c r="K168" s="2"/>
+      <x:c r="K168" s="2" t="str">
+        <x:v>Исследованию на ранней стадии не нужен идеальный симулятор, однако необходимо последовательно определить, какие рыночные трения считаются существенными. Укажите включённые компоненты издержек (комиссии, спреды, проскальзывание и влияние на рынок, затраты на финансирование или выплаты по ставке финансирования, стоимость заимствования, издержки роллирования) и степень консервативности допущений. В последующих главах модель издержек уточняется; при предварительном отборе используются консервативные укрупнённые допущения.</x:v>
+      </x:c>
       <x:c r="L168" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.384.1"&gt;
@@ -16829,7 +16867,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M168" s="2"/>
+      <x:c r="M168" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.384.1"&gt;Исследованию на ранней стадии не нужен идеальный симулятор, однако необходимо последовательно определить, какие рыночные трения считаются существенными. Укажите включённые компоненты издержек (комиссии, спреды, проскальзывание и влияние на рынок, затраты на финансирование или выплаты по ставке финансирования, стоимость заимствования, издержки роллирования) и степень консервативности допущений. В последующих главах модель издержек уточняется; при предварительном отборе используются консервативные укрупнённые допущения.&lt;/span&gt;&lt;a id="_idIndexMarker693"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.385.1"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.385.2"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.385.3"/&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N168" s="2"/>
       <x:c r="O168" s="2"/>
       <x:c r="P168" s="2"/>
@@ -16840,27 +16880,29 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U168" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V168" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W168" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X168" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y168" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z168" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA168" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB168" s="2"/>
+      <x:c r="AB168" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC168" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -16885,16 +16927,18 @@
         <x:v>/*/*[2]/*/*[98]</x:v>
       </x:c>
       <x:c r="G169" s="2"/>
-      <x:c r="H169" s="2" t="n">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="I169" s="2" t="n">
-        <x:v>123</x:v>
+      <x:c r="H169" s="2" t="str">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="I169" s="2" t="str">
+        <x:v>134</x:v>
       </x:c>
       <x:c r="J169" s="2" t="str">
         <x:v>Example (perpetual futures) : in crypto_perps_funding , funding is a position-dependent cash flow that is part of the total return stream: a cost when paid and a benefit when received. Because it accrues only when a position is held at the funding timestamp and is settled under venue-specific conventions, the trading setup must specify (i) how trades and position changes are aligned to the funding snapshot, (ii) which pricing and funding formula (including any caps/floors) and fee schedule are assumed, and (iii) how convention changes are versioned. Otherwise, the same backtest can imply different effective exposures and produce materially different PnL.</x:v>
       </x:c>
-      <x:c r="K169" s="2"/>
+      <x:c r="K169" s="2" t="str">
+        <x:v>Пример (бессрочные фьючерсы): в crypto_perps_funding платежи по ставке финансирования представляют собой зависящий от позиции денежный поток, входящий в совокупную доходность: издержки при выплате и доход при получении. Поскольку он начисляется только при наличии позиции в момент фиксации ставки финансирования, а расчёты проводятся по правилам конкретной торговой площадки, параметры торговли должны определять: (i) как сделки и изменения позиций согласуются с моментом фиксации ставки финансирования; (ii) какие формулы ценообразования и расчёта ставки финансирования предполагаются (включая верхние и нижние ограничения), а также какая тарифная сетка комиссий используется; (iii) как версионируются изменения правил. Иначе один и тот же бэктест может подразумевать разную фактическую подверженность риску и давать существенно различающиеся PnL.</x:v>
+      </x:c>
       <x:c r="L169" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;em class="italic"&gt;
@@ -16922,7 +16966,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M169" s="2"/>
+      <x:c r="M169" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;em class="italic"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.386.1"&gt;Пример (бессрочные фьючерсы)&lt;/span&gt;&lt;/em&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.387.1"&gt;: в &lt;/span&gt;&lt;code class="inlineCode"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.388.1"&gt;crypto_perps_funding &lt;/span&gt;&lt;/code&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.389.1"&gt;платежи по ставке финансирования представляют собой зависящий от позиции денежный поток, входящий в совокупную доходность: издержки при выплате и доход при получении. &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.389.2"&gt;Поскольку он начисляется только при наличии позиции в момент фиксации ставки финансирования, а расчёты проводятся по правилам конкретной торговой площадки, параметры торговли должны определять: (i) как сделки и изменения позиций согласуются с моментом фиксации ставки финансирования; (ii) какие формулы ценообразования и расчёта ставки финансирования предполагаются (включая верхние и нижние ограничения), а также какая тарифная сетка комиссий используется; (iii) как версионируются изменения правил. &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.389.3"&gt;Иначе один и тот же бэктест может подразумевать разную фактическую подверженность риску и давать существенно различающиеся PnL.&lt;/span&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N169" s="2"/>
       <x:c r="O169" s="2"/>
       <x:c r="P169" s="2"/>
@@ -16933,27 +16979,29 @@
         <x:v>em,code</x:v>
       </x:c>
       <x:c r="U169" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V169" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W169" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X169" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y169" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z169" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA169" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB169" s="2"/>
+      <x:c r="AB169" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC169" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -16978,16 +17026,18 @@
         <x:v>/*/*[2]/*/*[99]</x:v>
       </x:c>
       <x:c r="G170" s="2"/>
-      <x:c r="H170" s="2" t="n">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="I170" s="2" t="n">
-        <x:v>123</x:v>
+      <x:c r="H170" s="2" t="str">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="I170" s="2" t="str">
+        <x:v>134</x:v>
       </x:c>
       <x:c r="J170" s="2" t="str">
         <x:v>Example : The ETF cross-asset momentum setup (v1) defines the following invariants:</x:v>
       </x:c>
-      <x:c r="K170" s="2"/>
+      <x:c r="K170" s="2" t="str">
+        <x:v>Пример: параметры моментум-стратегии по различным классам активов на основе ETF (v1) задают следующие инварианты:</x:v>
+      </x:c>
       <x:c r="L170" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;em class="italic"&gt;
@@ -17009,7 +17059,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M170" s="2"/>
+      <x:c r="M170" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;em class="italic"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.390.1"&gt;Пример&lt;/span&gt;&lt;/em&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.391.1"&gt;: &lt;/span&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.392.1"&gt;параметры моментум-стратегии по различным классам активов на основе ETF (v1) &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.393.1"&gt;задают следующие инварианты:&lt;/span&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N170" s="2"/>
       <x:c r="O170" s="2"/>
       <x:c r="P170" s="2"/>
@@ -17020,29 +17072,31 @@
         <x:v>strong,em</x:v>
       </x:c>
       <x:c r="U170" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V170" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W170" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X170" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y170" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z170" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA170" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB170" s="2"/>
+      <x:c r="AB170" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC170" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -17065,16 +17119,18 @@
         <x:v>/*/*[2]/*/*[100]/*[1]</x:v>
       </x:c>
       <x:c r="G171" s="2"/>
-      <x:c r="H171" s="2" t="n">
+      <x:c r="H171" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I171" s="2" t="n">
+      <x:c r="I171" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J171" s="2" t="str">
         <x:v>Universe: 100 cross-asset ETFs with point-in-time eligibility based on trailing annual ADV ≥ $10M. The lenient threshold preserves cross-sectional breadth in early sample years (70–95 eligible ETFs per year). Note that the universe composition has survivorship bias that cannot be fully resolved without historical constituent data, while within-universe eligibility is point-in-time correct.</x:v>
       </x:c>
-      <x:c r="K171" s="2"/>
+      <x:c r="K171" s="2" t="str">
+        <x:v>Совокупность активов: 100 ETF по различным классам активов, для которых допуск определяется на соответствующий момент времени на основе среднего дневного объёма торгов (ADV) за предшествующий год ≥ 10 млн долларов США. Мягкий порог сохраняет широту поперечного сечения в первые годы выборки (70–95 допустимых ETF в год). Следует учитывать, что состав совокупности активов подвержен смещению выживших, которое невозможно полностью устранить без исторических данных о её составе, тогда как критерии допуска внутри совокупности корректно применяются на соответствующий момент времени.</x:v>
+      </x:c>
       <x:c r="L171" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -17099,7 +17155,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M171" s="2"/>
+      <x:c r="M171" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.394.1"&gt;Совокупность активов: &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.395.1"&gt;100 ETF по различным классам активов, для которых допуск определяется на соответствующий момент времени на основе среднего дневного объёма торгов (ADV) за предшествующий год ≥ 10 млн долларов США. &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.395.2"&gt;Мягкий порог сохраняет широту поперечного сечения в первые годы выборки (70–95 допустимых ETF в год). &lt;/span&gt;&lt;a id="_idIndexMarker694"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.396.1"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.396.2"&gt;Следует учитывать, что состав совокупности активов подвержен смещению выживших, которое невозможно полностью устранить без исторических данных о её составе, тогда как критерии допуска внутри совокупности корректно применяются на соответствующий момент времени.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N171" s="2"/>
       <x:c r="O171" s="2"/>
       <x:c r="P171" s="2"/>
@@ -17110,29 +17168,31 @@
         <x:v>strong,a</x:v>
       </x:c>
       <x:c r="U171" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V171" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W171" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X171" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y171" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z171" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA171" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB171" s="2"/>
+      <x:c r="AB171" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC171" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -17155,16 +17215,18 @@
         <x:v>/*/*[2]/*/*[100]/*[2]</x:v>
       </x:c>
       <x:c r="G172" s="2"/>
-      <x:c r="H172" s="2" t="n">
+      <x:c r="H172" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I172" s="2" t="n">
+      <x:c r="I172" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J172" s="2" t="str">
         <x:v>Decision schedule: Monthly month-end close snapshot with execution at the next-day bar open. This aligns with momentum literature for benchmark comparability. Weekly (5-day) cadence is tested as a variant.</x:v>
       </x:c>
-      <x:c r="K172" s="2"/>
+      <x:c r="K172" s="2" t="str">
+        <x:v>График принятия решений: ежемесячный снимок цен закрытия на конец месяца с исполнением по цене открытия бара следующего дня. Это соответствует литературе о моментуме и обеспечивает сопоставимость с эталонными результатами исследований моментума. В качестве варианта тестируется недельная (5-дневная) периодичность.</x:v>
+      </x:c>
       <x:c r="L172" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -17189,7 +17251,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M172" s="2"/>
+      <x:c r="M172" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.397.1"&gt;График принятия решений: &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.398.1"&gt;ежемесячный &lt;/span&gt;&lt;a id="_idIndexMarker695"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.399.1"&gt;снимок цен закрытия на конец месяца с исполнением по цене открытия бара следующего дня. &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.399.2"&gt;Это соответствует литературе о моментуме и обеспечивает сопоставимость с эталонными результатами исследований моментума. &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.399.3"&gt;В качестве варианта тестируется недельная (5-дневная) периодичность.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N172" s="2"/>
       <x:c r="O172" s="2"/>
       <x:c r="P172" s="2"/>
@@ -17200,29 +17264,31 @@
         <x:v>strong,a</x:v>
       </x:c>
       <x:c r="U172" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V172" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W172" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X172" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y172" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z172" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA172" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB172" s="2"/>
+      <x:c r="AB172" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC172" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -17245,16 +17311,18 @@
         <x:v>/*/*[2]/*/*[100]/*[3]</x:v>
       </x:c>
       <x:c r="G173" s="2"/>
-      <x:c r="H173" s="2" t="n">
+      <x:c r="H173" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I173" s="2" t="n">
+      <x:c r="I173" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J173" s="2" t="str">
         <x:v>Mapping: Long-only, rank-select top-N, equal-weight, rebalanced on cadence. Long-only because ETFs are expensive to short; equal-weight because it isolates the ranking signal from sizing optimization that would confound evaluation.</x:v>
       </x:c>
-      <x:c r="K173" s="2"/>
+      <x:c r="K173" s="2" t="str">
+        <x:v>Преобразование: только длинные позиции, отбор top-N по рангу, равные веса, ребалансировка с заданной периодичностью. Только длинные позиции — потому что открывать короткие позиции по ETF дорого; равные веса — потому что они позволяют отделить сигнал ранжирования от оптимизации размеров позиций, которая затруднила бы интерпретацию результатов оценки.</x:v>
+      </x:c>
       <x:c r="L173" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -17276,7 +17344,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M173" s="2"/>
+      <x:c r="M173" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.400.1"&gt;Преобразование: &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.401.1"&gt;только длинные позиции, отбор top-N по рангу, равные веса, ребалансировка с заданной периодичностью. &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.401.2"&gt;Только длинные позиции — потому что &lt;/span&gt;&lt;a id="_idIndexMarker696"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.402.1"&gt;открывать короткие позиции по ETF дорого; равные веса — потому что они позволяют отделить сигнал ранжирования от оптимизации размеров позиций, которая затруднила бы интерпретацию результатов оценки.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N173" s="2"/>
       <x:c r="O173" s="2"/>
       <x:c r="P173" s="2"/>
@@ -17287,29 +17357,31 @@
         <x:v>strong,a</x:v>
       </x:c>
       <x:c r="U173" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V173" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W173" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X173" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y173" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z173" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA173" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB173" s="2"/>
+      <x:c r="AB173" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC173" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -17332,16 +17404,18 @@
         <x:v>/*/*[2]/*/*[100]/*[4]</x:v>
       </x:c>
       <x:c r="G174" s="2"/>
-      <x:c r="H174" s="2" t="n">
+      <x:c r="H174" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I174" s="2" t="n">
+      <x:c r="I174" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J174" s="2" t="str">
         <x:v>Constraints: Fully invested long-only with no leverage, a minimal constraint set appropriate for a pedagogical baseline.</x:v>
       </x:c>
-      <x:c r="K174" s="2"/>
+      <x:c r="K174" s="2" t="str">
+        <x:v>Ограничения: полностью инвестированный портфель только с длинными позициями, без кредитного плеча — минимальный набор ограничений, подходящий для учебного базового варианта.</x:v>
+      </x:c>
       <x:c r="L174" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -17360,7 +17434,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M174" s="2"/>
+      <x:c r="M174" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.403.1"&gt;Ограничения: &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.404.1"&gt;полностью &lt;/span&gt;&lt;a id="_idIndexMarker697"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.405.1"&gt;инвестированный портфель только с длинными позициями, без кредитного плеча — минимальный набор ограничений, подходящий для учебного базового варианта.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N174" s="2"/>
       <x:c r="O174" s="2"/>
       <x:c r="P174" s="2"/>
@@ -17371,29 +17447,31 @@
         <x:v>strong,a</x:v>
       </x:c>
       <x:c r="U174" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V174" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W174" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X174" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y174" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z174" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA174" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB174" s="2"/>
+      <x:c r="AB174" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC174" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -17416,16 +17494,18 @@
         <x:v>/*/*[2]/*/*[100]/*[5]</x:v>
       </x:c>
       <x:c r="G175" s="2"/>
-      <x:c r="H175" s="2" t="n">
+      <x:c r="H175" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I175" s="2" t="n">
+      <x:c r="I175" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J175" s="2" t="str">
         <x:v>Cost model: Material is a per-share commission ($0.0035/share, IBKR Pro Tiered) plus tiered half-spread slippage (0.5¢ for the most liquid mega-ETFs, 1¢ for sector ETFs, 2¢ default for thematic and regional ETFs). The horizon feasibility analysis uses a 5–15 bps-per-leg reference cost line to screen cadences and confirms that monthly moves exceed 30 bps round-trip costs in over 90% of observations; daily trading operates in the gray zone where feasibility depends on signal strength and turnover.</x:v>
       </x:c>
-      <x:c r="K175" s="2"/>
+      <x:c r="K175" s="2" t="str">
+        <x:v>Модель издержек: к существенным издержкам относятся комиссия в размере 0,0035 доллара США за акцию (тариф IBKR Pro Tiered) и дифференцированное проскальзывание в размере половины спреда (0,5 цента для наиболее ликвидных крупнейших ETF, 1 цент для отраслевых ETF и 2 цента по умолчанию для тематических и региональных ETF). При анализе осуществимости горизонта для отбора вариантов периодичности используется контрольная линия издержек 5–15 базисных пунктов (б.п.) на одну сторону сделки. Анализ подтверждает, что месячные ценовые движения превышают издержки полного цикла сделки, равные 30 б.п., более чем в 90 % наблюдений; ежедневная торговля находится в серой зоне, где осуществимость зависит от силы сигнала и оборота портфеля.</x:v>
+      </x:c>
       <x:c r="L175" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -17452,7 +17532,9 @@
     &lt;/li&gt;
    </x:v>
       </x:c>
-      <x:c r="M175" s="2"/>
+      <x:c r="M175" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.406.1"&gt;Модель издержек: &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.407.1"&gt;к существенным издержкам относятся &lt;/span&gt;&lt;a id="_idIndexMarker698"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.408.1"&gt;комиссия в размере 0,0035 доллара США за акцию (тариф IBKR Pro Tiered) и дифференцированное проскальзывание в размере половины спреда (0,5 цента для наиболее ликвидных крупнейших ETF, 1 цент для отраслевых ETF и 2 цента по умолчанию для тематических и региональных ETF). &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.408.2"&gt;При анализе осуществимости горизонта для отбора вариантов периодичности используется контрольная линия издержек 5–15 базисных пунктов (б.п.) на одну сторону сделки. Анализ подтверждает, что месячные ценовые движения превышают издержки полного цикла сделки, равные 30 б.п., более чем в 90 % наблюдений; ежедневная торговля находится в серой зоне, &lt;/span&gt;&lt;a id="_idIndexMarker699"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.409.1"&gt;где осуществимость зависит от силы сигнала и оборота портфеля.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N175" s="2"/>
       <x:c r="O175" s="2"/>
       <x:c r="P175" s="2"/>
@@ -17463,29 +17545,31 @@
         <x:v>strong,a</x:v>
       </x:c>
       <x:c r="U175" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V175" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W175" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X175" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y175" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z175" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA175" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB175" s="2"/>
+      <x:c r="AB175" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC175" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -17508,16 +17592,18 @@
         <x:v>/*/*[2]/*/*[101]</x:v>
       </x:c>
       <x:c r="G176" s="2"/>
-      <x:c r="H176" s="2" t="n">
+      <x:c r="H176" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I176" s="2" t="n">
+      <x:c r="I176" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J176" s="2" t="str">
         <x:v>The setup notebook writes these choices to versioned YAML artifacts ( setup.yaml ) that downstream chapters consume programmatically. Changing the mapping from long-only to long/short would require setup_version: v2 and a new baseline checkpoint; parameter changes, such as adjusting top-N from 10 to 20, remain within v1 .</x:v>
       </x:c>
-      <x:c r="K176" s="2"/>
+      <x:c r="K176" s="2" t="str">
+        <x:v>Ноутбук параметров торговли записывает эти решения в версионируемые артефакты YAML (setup.yaml), которые программно используются в последующих главах. Для изменения преобразования с только длинных позиций на длинные/короткие потребовались бы setup_version: v2 и новая контрольная точка базового варианта; изменения параметров, например увеличение top-N с 10 до 20, остаются в рамках v1.</x:v>
+      </x:c>
       <x:c r="L176" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.410.1"&gt;
@@ -17553,7 +17639,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M176" s="2"/>
+      <x:c r="M176" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.410.1"&gt;Ноутбук параметров торговли записывает эти решения в версионируемые артефакты YAML (&lt;/span&gt;&lt;code class="inlineCode"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.411.1"&gt;setup.yaml&lt;/span&gt;&lt;/code&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.412.1"&gt;), которые программно используются в последующих главах. &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.412.2"&gt;Для изменения преобразования с только длинных позиций на длинные/короткие потребовались бы &lt;/span&gt;&lt;code class="inlineCode"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.413.1"&gt;setup_version: v2 &lt;/span&gt;&lt;/code&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.414.1"&gt;и новая контрольная точка базового варианта; изменения параметров, например увеличение top-N с 10 до 20, остаются в рамках &lt;/span&gt;&lt;code class="inlineCode"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.415.1"&gt;v1&lt;/span&gt;&lt;/code&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.416.1"&gt;.&lt;/span&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N176" s="2"/>
       <x:c r="O176" s="2"/>
       <x:c r="P176" s="2"/>
@@ -17564,27 +17652,29 @@
         <x:v>code</x:v>
       </x:c>
       <x:c r="U176" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V176" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W176" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X176" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y176" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z176" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA176" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB176" s="2"/>
+      <x:c r="AB176" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC176" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -17611,16 +17701,18 @@
       <x:c r="G177" s="2" t="str">
         <x:v>_idParaDest-281</x:v>
       </x:c>
-      <x:c r="H177" s="2" t="n">
+      <x:c r="H177" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I177" s="2" t="n">
+      <x:c r="I177" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J177" s="2" t="str">
         <x:v>When a change requires a new setup version</x:v>
       </x:c>
-      <x:c r="K177" s="2"/>
+      <x:c r="K177" s="2" t="str">
+        <x:v>Когда изменение требует новой версии параметров торговли</x:v>
+      </x:c>
       <x:c r="L177" s="2" t="str">
         <x:v>&lt;h2 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-2" id="_idParaDest-281"&gt;
     &lt;a id="_idTextAnchor273"&gt;
@@ -17631,7 +17723,9 @@
    &lt;/h2&gt;
    </x:v>
       </x:c>
-      <x:c r="M177" s="2"/>
+      <x:c r="M177" s="2" t="str">
+        <x:v>&lt;h2 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-2" id="_idParaDest-281"&gt;&lt;a id="_idTextAnchor273"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.417.1"&gt;Когда изменение требует новой версии параметров торговли&lt;/span&gt;&lt;/h2&gt;</x:v>
+      </x:c>
       <x:c r="N177" s="2"/>
       <x:c r="O177" s="2"/>
       <x:c r="P177" s="2"/>
@@ -17642,27 +17736,29 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U177" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V177" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W177" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X177" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y177" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z177" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA177" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB177" s="2"/>
+      <x:c r="AB177" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC177" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -17687,16 +17783,18 @@
         <x:v>/*/*[2]/*/*[103]</x:v>
       </x:c>
       <x:c r="G178" s="2"/>
-      <x:c r="H178" s="2" t="n">
+      <x:c r="H178" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I178" s="2" t="n">
+      <x:c r="I178" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J178" s="2" t="str">
         <x:v>Treat the trading setup as versioned. Bump the setup version on any change that alters the strategy’s decision-time meaning or shifts its dominant frictions and constraints. Parameter tuning stays within a setup; changes to mechanics define a new setup. A change is a new setup version if it changes at least one of:</x:v>
       </x:c>
-      <x:c r="K178" s="2"/>
+      <x:c r="K178" s="2" t="str">
+        <x:v>Рассматривайте параметры торговли как версионируемый объект. Повышайте номер версии при любом изменении, которое меняет интерпретацию стратегии в момент принятия решения либо её преобладающие рыночные трения и ограничения. Настройка параметров выполняется в рамках одной версии; изменения торгового механизма определяют новую версию. Изменение требует новой версии параметров торговли, если затрагивает хотя бы один из следующих элементов:</x:v>
+      </x:c>
       <x:c r="L178" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.418.1"&gt;
@@ -17719,7 +17817,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M178" s="2"/>
+      <x:c r="M178" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.418.1"&gt;Рассматривайте параметры торговли как версионируемый объект. Повышайте номер версии при любом изменении, которое меняет интерпретацию стратегии в момент принятия решения либо её преобладающие рыночные трения и ограничения. Настройка параметров выполняется в рамках одной версии; изменения торгового механизма определяют новую версию. Изменение требует новой версии параметров торговли, если затрагивает хотя бы один из следующих элементов:&lt;/span&gt;&lt;a id="_idIndexMarker700"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.419.1"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.419.2"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.419.3"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.419.4"/&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N178" s="2"/>
       <x:c r="O178" s="2"/>
       <x:c r="P178" s="2"/>
@@ -17730,27 +17830,29 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U178" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V178" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W178" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X178" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y178" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z178" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA178" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB178" s="2"/>
+      <x:c r="AB178" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC178" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -17775,16 +17877,18 @@
         <x:v>/*/*[2]/*/*[104]/*[1]</x:v>
       </x:c>
       <x:c r="G179" s="2"/>
-      <x:c r="H179" s="2" t="n">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="I179" s="2" t="n">
-        <x:v>123</x:v>
+      <x:c r="H179" s="2" t="str">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="I179" s="2" t="str">
+        <x:v>135</x:v>
       </x:c>
       <x:c r="J179" s="2" t="str">
         <x:v>Universe or tradability rules , for example, eligibility, membership mechanics, instrument scope.</x:v>
       </x:c>
-      <x:c r="K179" s="2"/>
+      <x:c r="K179" s="2" t="str">
+        <x:v>Совокупность активов или правила торгуемости, например критерии включения, механизм изменения состава, охват инструментов.</x:v>
+      </x:c>
       <x:c r="L179" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -17798,7 +17902,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M179" s="2"/>
+      <x:c r="M179" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.420.1"&gt;Совокупность активов или правила торгуемости&lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.421.1"&gt;, например критерии включения, механизм изменения состава, охват инструментов.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N179" s="2"/>
       <x:c r="O179" s="2"/>
       <x:c r="P179" s="2"/>
@@ -17809,27 +17915,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U179" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V179" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W179" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X179" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y179" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z179" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA179" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB179" s="2"/>
+      <x:c r="AB179" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC179" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -17854,16 +17962,18 @@
         <x:v>/*/*[2]/*/*[104]/*[2]</x:v>
       </x:c>
       <x:c r="G180" s="2"/>
-      <x:c r="H180" s="2" t="n">
+      <x:c r="H180" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I180" s="2" t="n">
+      <x:c r="I180" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J180" s="2" t="str">
         <x:v>Decision schedule or admissible information , for example, rebalance snapshot, cadence, execution delay, and input availability rules.</x:v>
       </x:c>
-      <x:c r="K180" s="2"/>
+      <x:c r="K180" s="2" t="str">
+        <x:v>График принятия решений или допустимая информация, например момент снимка для ребалансировки, периодичность, задержка исполнения и правила доступности входных данных.</x:v>
+      </x:c>
       <x:c r="L180" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -17877,7 +17987,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M180" s="2"/>
+      <x:c r="M180" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.422.1"&gt;График принятия решений или допустимая информация&lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.423.1"&gt;, например момент снимка для ребалансировки, периодичность, задержка исполнения и правила доступности входных данных.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N180" s="2"/>
       <x:c r="O180" s="2"/>
       <x:c r="P180" s="2"/>
@@ -17888,27 +18000,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U180" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V180" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W180" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X180" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y180" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z180" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA180" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB180" s="2"/>
+      <x:c r="AB180" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC180" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -17933,16 +18047,18 @@
         <x:v>/*/*[2]/*/*[104]/*[3]</x:v>
       </x:c>
       <x:c r="G181" s="2"/>
-      <x:c r="H181" s="2" t="n">
+      <x:c r="H181" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I181" s="2" t="n">
+      <x:c r="I181" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J181" s="2" t="str">
         <x:v>Score-to-trade mapping at the level of state space, entry or exit form, sizing normalization, or order timing.</x:v>
       </x:c>
-      <x:c r="K181" s="2"/>
+      <x:c r="K181" s="2" t="str">
+        <x:v>Преобразование оценки модели в сделку на уровне пространства состояний, способа входа или выхода, нормализации размера позиции либо времени размещения заявок.</x:v>
+      </x:c>
       <x:c r="L181" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -17956,7 +18072,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M181" s="2"/>
+      <x:c r="M181" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.424.1"&gt;Преобразование оценки модели в сделку &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.425.1"&gt;на уровне пространства состояний, способа входа или выхода, нормализации размера позиции либо времени размещения заявок.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N181" s="2"/>
       <x:c r="O181" s="2"/>
       <x:c r="P181" s="2"/>
@@ -17967,27 +18085,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U181" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V181" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W181" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X181" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y181" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z181" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA181" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB181" s="2"/>
+      <x:c r="AB181" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC181" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18012,16 +18132,18 @@
         <x:v>/*/*[2]/*/*[104]/*[4]</x:v>
       </x:c>
       <x:c r="G182" s="2"/>
-      <x:c r="H182" s="2" t="n">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="I182" s="2" t="n">
-        <x:v>123</x:v>
+      <x:c r="H182" s="2" t="str">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="I182" s="2" t="str">
+        <x:v>135</x:v>
       </x:c>
       <x:c r="J182" s="2" t="str">
         <x:v>Constraint regime , such as binding exposure/leverage limits, concentration rules, capacity or liquidity constraints, action-changing overlays.</x:v>
       </x:c>
-      <x:c r="K182" s="2"/>
+      <x:c r="K182" s="2" t="str">
+        <x:v>Режим ограничений, например обязательные лимиты подверженности риску или кредитного плеча, правила концентрации, ограничения ёмкости стратегии или ликвидности, а также дополнительные механизмы, изменяющие торговые действия.</x:v>
+      </x:c>
       <x:c r="L182" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -18035,7 +18157,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M182" s="2"/>
+      <x:c r="M182" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.426.1"&gt;Режим ограничений&lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.427.1"&gt;, например обязательные лимиты подверженности риску или кредитного плеча, правила концентрации, ограничения ёмкости стратегии или ликвидности, а также дополнительные механизмы, изменяющие торговые действия.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N182" s="2"/>
       <x:c r="O182" s="2"/>
       <x:c r="P182" s="2"/>
@@ -18046,27 +18170,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U182" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V182" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W182" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X182" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y182" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z182" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA182" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB182" s="2"/>
+      <x:c r="AB182" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC182" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18091,16 +18217,18 @@
         <x:v>/*/*[2]/*/*[104]/*[5]</x:v>
       </x:c>
       <x:c r="G183" s="2"/>
-      <x:c r="H183" s="2" t="n">
+      <x:c r="H183" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I183" s="2" t="n">
+      <x:c r="I183" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J183" s="2" t="str">
         <x:v>Cost model class or included components , for example, adding funding or roll mechanics, or changing the slippage model in a way that affects feasibility.</x:v>
       </x:c>
-      <x:c r="K183" s="2"/>
+      <x:c r="K183" s="2" t="str">
+        <x:v>Класс модели издержек или включённые компоненты, например добавление механизма выплат по ставке финансирования или роллирования либо изменение модели проскальзывания, влияющее на осуществимость.</x:v>
+      </x:c>
       <x:c r="L183" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -18114,7 +18242,9 @@
     &lt;/li&gt;
    </x:v>
       </x:c>
-      <x:c r="M183" s="2"/>
+      <x:c r="M183" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.428.1"&gt;Класс модели издержек или включённые компоненты&lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.429.1"&gt;, например добавление механизма выплат по ставке финансирования или роллирования либо изменение модели проскальзывания, влияющее на осуществимость.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N183" s="2"/>
       <x:c r="O183" s="2"/>
       <x:c r="P183" s="2"/>
@@ -18125,27 +18255,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U183" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V183" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W183" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X183" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y183" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z183" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA183" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB183" s="2"/>
+      <x:c r="AB183" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC183" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18170,16 +18302,18 @@
         <x:v>/*/*[2]/*/*[105]</x:v>
       </x:c>
       <x:c r="G184" s="2"/>
-      <x:c r="H184" s="2" t="n">
+      <x:c r="H184" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I184" s="2" t="n">
+      <x:c r="I184" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J184" s="2" t="str">
         <x:v>To keep this boundary unambiguous, separate mechanics from parameters :</x:v>
       </x:c>
-      <x:c r="K184" s="2"/>
+      <x:c r="K184" s="2" t="str">
+        <x:v>Чтобы эта граница была однозначной, отделяйте торговый механизм от параметров:</x:v>
+      </x:c>
       <x:c r="L184" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.430.1"&gt;
@@ -18204,7 +18338,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M184" s="2"/>
+      <x:c r="M184" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.430.1"&gt;Чтобы эта граница была однозначной, отделяйте &lt;/span&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.431.1"&gt;торговый механизм &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.432.1"&gt;от &lt;/span&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.433.1"&gt;параметров&lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.434.1"&gt;:&lt;/span&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N184" s="2"/>
       <x:c r="O184" s="2"/>
       <x:c r="P184" s="2"/>
@@ -18215,27 +18351,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U184" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V184" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W184" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X184" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y184" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z184" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA184" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB184" s="2"/>
+      <x:c r="AB184" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC184" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18260,16 +18398,18 @@
         <x:v>/*/*[2]/*/*[106]/*[1]/*/*[1]</x:v>
       </x:c>
       <x:c r="G185" s="2"/>
-      <x:c r="H185" s="2" t="n">
+      <x:c r="H185" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I185" s="2" t="n">
+      <x:c r="I185" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J185" s="2" t="str">
         <x:v>Same setup version (parameter tuning)</x:v>
       </x:c>
-      <x:c r="K185" s="2"/>
+      <x:c r="K185" s="2" t="str">
+        <x:v>Та же версия параметров торговли (настройка параметров)</x:v>
+      </x:c>
       <x:c r="L185" s="2" t="str">
         <x:v>&lt;th xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-head" scope="col"&gt;
        &lt;p class="normal"&gt;
@@ -18282,7 +18422,9 @@
       &lt;/th&gt;
       </x:v>
       </x:c>
-      <x:c r="M185" s="2"/>
+      <x:c r="M185" s="2" t="str">
+        <x:v>&lt;th xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-head" scope="col"&gt;&lt;p class="normal"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.435.1"&gt;Та же версия параметров торговли (настройка параметров)&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;&lt;/th&gt;</x:v>
+      </x:c>
       <x:c r="N185" s="2"/>
       <x:c r="O185" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18295,27 +18437,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U185" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V185" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W185" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X185" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y185" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z185" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA185" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB185" s="2"/>
+      <x:c r="AB185" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC185" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18340,16 +18484,18 @@
         <x:v>/*/*[2]/*/*[106]/*[1]/*/*[2]</x:v>
       </x:c>
       <x:c r="G186" s="2"/>
-      <x:c r="H186" s="2" t="n">
+      <x:c r="H186" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I186" s="2" t="n">
+      <x:c r="I186" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J186" s="2" t="str">
         <x:v>New setup version (mechanics changed)</x:v>
       </x:c>
-      <x:c r="K186" s="2"/>
+      <x:c r="K186" s="2" t="str">
+        <x:v>Новая версия параметров торговли (изменён торговый механизм)</x:v>
+      </x:c>
       <x:c r="L186" s="2" t="str">
         <x:v>&lt;th xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-head" scope="col"&gt;
        &lt;p class="normal"&gt;
@@ -18362,7 +18508,9 @@
       &lt;/th&gt;
      </x:v>
       </x:c>
-      <x:c r="M186" s="2"/>
+      <x:c r="M186" s="2" t="str">
+        <x:v>&lt;th xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-head" scope="col"&gt;&lt;p class="normal"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.436.1"&gt;Новая версия параметров торговли (изменён торговый механизм)&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;&lt;/th&gt;</x:v>
+      </x:c>
       <x:c r="N186" s="2"/>
       <x:c r="O186" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18375,27 +18523,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U186" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V186" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W186" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X186" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y186" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z186" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA186" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB186" s="2"/>
+      <x:c r="AB186" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC186" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18420,16 +18570,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[1]/*[1]</x:v>
       </x:c>
       <x:c r="G187" s="2"/>
-      <x:c r="H187" s="2" t="n">
+      <x:c r="H187" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I187" s="2" t="n">
+      <x:c r="I187" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J187" s="2" t="str">
         <x:v>Threshold 1.8 → 2.0</x:v>
       </x:c>
-      <x:c r="K187" s="2"/>
+      <x:c r="K187" s="2" t="str">
+        <x:v>Порог 1,8 → 2,0</x:v>
+      </x:c>
       <x:c r="L187" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -18440,7 +18592,9 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M187" s="2"/>
+      <x:c r="M187" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.437.1"&gt;Порог 1,8 → 2,0&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N187" s="2"/>
       <x:c r="O187" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18451,29 +18605,31 @@
       <x:c r="S187" s="2"/>
       <x:c r="T187" s="2"/>
       <x:c r="U187" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V187" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W187" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X187" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y187" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z187" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA187" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB187" s="2"/>
+      <x:c r="AB187" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC187" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
@@ -18496,16 +18652,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[1]/*[2]</x:v>
       </x:c>
       <x:c r="G188" s="2"/>
-      <x:c r="H188" s="2" t="n">
+      <x:c r="H188" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I188" s="2" t="n">
+      <x:c r="I188" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J188" s="2" t="str">
         <x:v>Rank selection → threshold gating</x:v>
       </x:c>
-      <x:c r="K188" s="2"/>
+      <x:c r="K188" s="2" t="str">
+        <x:v>Отбор по рангу → применение порогового условия</x:v>
+      </x:c>
       <x:c r="L188" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -18516,7 +18674,9 @@
       &lt;/td&gt;
      </x:v>
       </x:c>
-      <x:c r="M188" s="2"/>
+      <x:c r="M188" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.438.1"&gt;Отбор по рангу → применение порогового условия&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N188" s="2"/>
       <x:c r="O188" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18527,27 +18687,29 @@
       <x:c r="S188" s="2"/>
       <x:c r="T188" s="2"/>
       <x:c r="U188" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V188" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W188" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X188" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y188" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z188" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA188" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB188" s="2"/>
+      <x:c r="AB188" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC188" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18572,16 +18734,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[2]/*[1]</x:v>
       </x:c>
       <x:c r="G189" s="2"/>
-      <x:c r="H189" s="2" t="n">
+      <x:c r="H189" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I189" s="2" t="n">
+      <x:c r="I189" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J189" s="2" t="str">
         <x:v>Top 10% → top 20%</x:v>
       </x:c>
-      <x:c r="K189" s="2"/>
+      <x:c r="K189" s="2" t="str">
+        <x:v>Верхние 10 % по рангу → верхние 20 % по рангу</x:v>
+      </x:c>
       <x:c r="L189" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -18592,7 +18756,9 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M189" s="2"/>
+      <x:c r="M189" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.439.1"&gt;Верхние 10 % по рангу → верхние 20 % по рангу&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N189" s="2"/>
       <x:c r="O189" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18603,29 +18769,31 @@
       <x:c r="S189" s="2"/>
       <x:c r="T189" s="2"/>
       <x:c r="U189" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V189" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W189" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X189" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y189" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z189" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA189" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB189" s="2"/>
+      <x:c r="AB189" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC189" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
@@ -18648,16 +18816,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[2]/*[2]</x:v>
       </x:c>
       <x:c r="G190" s="2"/>
-      <x:c r="H190" s="2" t="n">
+      <x:c r="H190" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I190" s="2" t="n">
+      <x:c r="I190" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J190" s="2" t="str">
         <x:v>Long-only → long/short</x:v>
       </x:c>
-      <x:c r="K190" s="2"/>
+      <x:c r="K190" s="2" t="str">
+        <x:v>Только длинные позиции → длинные/короткие позиции</x:v>
+      </x:c>
       <x:c r="L190" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -18668,7 +18838,9 @@
       &lt;/td&gt;
      </x:v>
       </x:c>
-      <x:c r="M190" s="2"/>
+      <x:c r="M190" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.440.1"&gt;Только длинные позиции → длинные/короткие позиции&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N190" s="2"/>
       <x:c r="O190" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18679,27 +18851,29 @@
       <x:c r="S190" s="2"/>
       <x:c r="T190" s="2"/>
       <x:c r="U190" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V190" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W190" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X190" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y190" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z190" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA190" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB190" s="2"/>
+      <x:c r="AB190" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC190" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18724,16 +18898,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[3]/*[1]</x:v>
       </x:c>
       <x:c r="G191" s="2"/>
-      <x:c r="H191" s="2" t="n">
+      <x:c r="H191" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I191" s="2" t="n">
+      <x:c r="I191" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J191" s="2" t="str">
         <x:v>20-day → 60-day normalization window</x:v>
       </x:c>
-      <x:c r="K191" s="2"/>
+      <x:c r="K191" s="2" t="str">
+        <x:v>20-дневное → 60-дневное окно нормализации</x:v>
+      </x:c>
       <x:c r="L191" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -18744,7 +18920,9 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M191" s="2"/>
+      <x:c r="M191" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.441.1"&gt;20-дневное → 60-дневное окно нормализации&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N191" s="2"/>
       <x:c r="O191" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18755,27 +18933,29 @@
       <x:c r="S191" s="2"/>
       <x:c r="T191" s="2"/>
       <x:c r="U191" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V191" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W191" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X191" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y191" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z191" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA191" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB191" s="2"/>
+      <x:c r="AB191" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC191" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18800,16 +18980,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[3]/*[2]</x:v>
       </x:c>
       <x:c r="G192" s="2"/>
-      <x:c r="H192" s="2" t="n">
+      <x:c r="H192" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I192" s="2" t="n">
+      <x:c r="I192" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J192" s="2" t="str">
         <x:v>Adding a stop rule when none existed</x:v>
       </x:c>
-      <x:c r="K192" s="2"/>
+      <x:c r="K192" s="2" t="str">
+        <x:v>Добавление правила принудительного выхода, которого раньше не было</x:v>
+      </x:c>
       <x:c r="L192" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -18820,7 +19002,9 @@
       &lt;/td&gt;
      </x:v>
       </x:c>
-      <x:c r="M192" s="2"/>
+      <x:c r="M192" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.442.1"&gt;Добавление правила принудительного выхода, которого раньше не было&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N192" s="2"/>
       <x:c r="O192" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18831,27 +19015,29 @@
       <x:c r="S192" s="2"/>
       <x:c r="T192" s="2"/>
       <x:c r="U192" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V192" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W192" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X192" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y192" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z192" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA192" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB192" s="2"/>
+      <x:c r="AB192" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC192" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18876,16 +19062,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[4]/*[1]</x:v>
       </x:c>
       <x:c r="G193" s="2"/>
-      <x:c r="H193" s="2" t="n">
+      <x:c r="H193" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I193" s="2" t="n">
+      <x:c r="I193" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J193" s="2" t="str">
         <x:v>Different lookback horizon</x:v>
       </x:c>
-      <x:c r="K193" s="2"/>
+      <x:c r="K193" s="2" t="str">
+        <x:v>Другой ретроспективный горизонт</x:v>
+      </x:c>
       <x:c r="L193" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -18896,7 +19084,9 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M193" s="2"/>
+      <x:c r="M193" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.443.1"&gt;Другой ретроспективный горизонт&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N193" s="2"/>
       <x:c r="O193" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18907,27 +19097,29 @@
       <x:c r="S193" s="2"/>
       <x:c r="T193" s="2"/>
       <x:c r="U193" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V193" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W193" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X193" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y193" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z193" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA193" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB193" s="2"/>
+      <x:c r="AB193" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC193" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18952,16 +19144,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[4]/*[2]</x:v>
       </x:c>
       <x:c r="G194" s="2"/>
-      <x:c r="H194" s="2" t="n">
+      <x:c r="H194" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I194" s="2" t="n">
+      <x:c r="I194" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J194" s="2" t="str">
         <x:v>Changing rebalance cadence or execution delay</x:v>
       </x:c>
-      <x:c r="K194" s="2"/>
+      <x:c r="K194" s="2" t="str">
+        <x:v>Изменение периодичности ребалансировки или задержки исполнения</x:v>
+      </x:c>
       <x:c r="L194" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -18972,7 +19166,9 @@
       &lt;/td&gt;
      </x:v>
       </x:c>
-      <x:c r="M194" s="2"/>
+      <x:c r="M194" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.444.1"&gt;Изменение периодичности ребалансировки или задержки исполнения&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N194" s="2"/>
       <x:c r="O194" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18983,27 +19179,29 @@
       <x:c r="S194" s="2"/>
       <x:c r="T194" s="2"/>
       <x:c r="U194" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V194" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W194" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X194" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y194" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z194" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA194" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB194" s="2"/>
+      <x:c r="AB194" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC194" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -19028,16 +19226,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[5]/*[1]</x:v>
       </x:c>
       <x:c r="G195" s="2"/>
-      <x:c r="H195" s="2" t="n">
+      <x:c r="H195" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I195" s="2" t="n">
+      <x:c r="I195" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J195" s="2" t="str">
         <x:v>Cost assumption 10 bps → 15 bps per leg</x:v>
       </x:c>
-      <x:c r="K195" s="2"/>
+      <x:c r="K195" s="2" t="str">
+        <x:v>Допущение об издержках: 10 б.п. → 15 б.п. на одну сторону сделки</x:v>
+      </x:c>
       <x:c r="L195" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -19048,7 +19248,9 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M195" s="2"/>
+      <x:c r="M195" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.445.1"&gt;Допущение об издержках: 10 б.п. → 15 б.п. на одну сторону сделки&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N195" s="2"/>
       <x:c r="O195" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -19059,29 +19261,31 @@
       <x:c r="S195" s="2"/>
       <x:c r="T195" s="2"/>
       <x:c r="U195" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V195" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W195" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X195" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y195" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z195" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA195" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB195" s="2"/>
+      <x:c r="AB195" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC195" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
@@ -19104,16 +19308,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[5]/*[2]</x:v>
       </x:c>
       <x:c r="G196" s="2"/>
-      <x:c r="H196" s="2" t="n">
+      <x:c r="H196" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I196" s="2" t="n">
+      <x:c r="I196" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J196" s="2" t="str">
         <x:v>Adding funding/roll as a cost component</x:v>
       </x:c>
-      <x:c r="K196" s="2"/>
+      <x:c r="K196" s="2" t="str">
+        <x:v>Добавление платежей по ставке финансирования или роллирования как компонента издержек</x:v>
+      </x:c>
       <x:c r="L196" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -19124,7 +19330,9 @@
       &lt;/td&gt;
      </x:v>
       </x:c>
-      <x:c r="M196" s="2"/>
+      <x:c r="M196" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.446.1"&gt;Добавление платежей по ставке финансирования или роллирования как компонента издержек&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N196" s="2"/>
       <x:c r="O196" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -19135,27 +19343,29 @@
       <x:c r="S196" s="2"/>
       <x:c r="T196" s="2"/>
       <x:c r="U196" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V196" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W196" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X196" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y196" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z196" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA196" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB196" s="2"/>
+      <x:c r="AB196" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC196" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -19180,16 +19390,18 @@
         <x:v>/*/*[2]/*/*[107]</x:v>
       </x:c>
       <x:c r="G197" s="2"/>
-      <x:c r="H197" s="2" t="n">
+      <x:c r="H197" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I197" s="2" t="n">
+      <x:c r="I197" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J197" s="2" t="str">
         <x:v>Table 6.2: Comparing mechanics and parameters</x:v>
       </x:c>
-      <x:c r="K197" s="2"/>
+      <x:c r="K197" s="2" t="str">
+        <x:v>Таблица 6.2. Сопоставление механизмов и параметров</x:v>
+      </x:c>
       <x:c r="L197" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="packt_figref"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.447.1"&gt;
@@ -19198,7 +19410,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M197" s="2"/>
+      <x:c r="M197" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="packt_figref"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.447.1"&gt;Таблица 6.2. Сопоставление механизмов и параметров&lt;/span&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N197" s="2"/>
       <x:c r="O197" s="2"/>
       <x:c r="P197" s="2"/>
@@ -19207,27 +19421,29 @@
       <x:c r="S197" s="2"/>
       <x:c r="T197" s="2"/>
       <x:c r="U197" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V197" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W197" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X197" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y197" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z197" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA197" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB197" s="2"/>
+      <x:c r="AB197" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC197" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -19252,16 +19468,18 @@
         <x:v>/*/*[2]/*/*[108]</x:v>
       </x:c>
       <x:c r="G198" s="2"/>
-      <x:c r="H198" s="2" t="n">
+      <x:c r="H198" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I198" s="2" t="n">
+      <x:c r="I198" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J198" s="2" t="str">
         <x:v>Results across setup versions can still be informative, but they are not direct competitors within a single research program. The next section defines what counts as improvement within a fixed setup, separating development diagnostics from strategy-level evaluation.</x:v>
       </x:c>
-      <x:c r="K198" s="2"/>
+      <x:c r="K198" s="2" t="str">
+        <x:v>Результаты разных версий параметров торговли по-прежнему могут быть информативными, однако они не подлежат прямому сопоставлению в рамках одной исследовательской программы. В следующем разделе определяется, что считается улучшением при фиксированных параметрах торговли, с отделением диагностики процесса разработки от оценки стратегии.</x:v>
+      </x:c>
       <x:c r="L198" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.448.1"&gt;
@@ -19273,7 +19491,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M198" s="2"/>
+      <x:c r="M198" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.448.1"&gt;Результаты разных версий параметров торговли по-прежнему могут быть информативными, однако они не подлежат прямому сопоставлению в рамках одной исследовательской программы. В следующем разделе определяется, что считается улучшением при фиксированных параметрах торговли, с отделением диагностики процесса разработки от оценки стратегии.&lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.448.2"/&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N198" s="2"/>
       <x:c r="O198" s="2"/>
       <x:c r="P198" s="2"/>
@@ -19282,27 +19502,29 @@
       <x:c r="S198" s="2"/>
       <x:c r="T198" s="2"/>
       <x:c r="U198" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V198" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W198" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X198" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y198" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z198" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA198" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB198" s="2"/>
+      <x:c r="AB198" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC198" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -19327,16 +19549,18 @@
         <x:v>/*/*[2]/*/*[109]/*</x:v>
       </x:c>
       <x:c r="G199" s="2"/>
-      <x:c r="H199" s="2" t="n">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="I199" s="2" t="n">
-        <x:v>123</x:v>
+      <x:c r="H199" s="2" t="str">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="I199" s="2" t="str">
+        <x:v>135</x:v>
       </x:c>
       <x:c r="J199" s="2" t="str">
         <x:v>Implementation : 02_case_study_overview inventories the trading setup for each of the nine case studies (universe, decision schedule, mapping, constraints, cost model) and is the source of the worked examples above.</x:v>
       </x:c>
-      <x:c r="K199" s="2"/>
+      <x:c r="K199" s="2" t="str">
+        <x:v>Реализация: 02_case_study_overview систематизирует параметры торговли для каждого из девяти практических примеров (совокупность активов, график принятия решений, преобразование, ограничения, модель издержек) и служит источником рассмотренных выше примеров.</x:v>
+      </x:c>
       <x:c r="L199" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
      &lt;strong class="screenText"&gt;
@@ -19358,7 +19582,9 @@
     &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M199" s="2"/>
+      <x:c r="M199" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;strong class="screenText"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.449.1"&gt;Реализация&lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.450.1"&gt;: &lt;/span&gt;&lt;code class="inlineCode"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.451.1"&gt;02_case_study_overview &lt;/span&gt;&lt;/code&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.452.1"&gt;систематизирует параметры торговли для каждого из девяти практических примеров (совокупность активов, график принятия решений, преобразование, ограничения, модель издержек) и служит источником рассмотренных выше примеров.&lt;/span&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N199" s="2"/>
       <x:c r="O199" s="2"/>
       <x:c r="P199" s="2"/>
@@ -19369,27 +19595,29 @@
         <x:v>strong,code</x:v>
       </x:c>
       <x:c r="U199" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V199" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W199" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X199" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y199" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z199" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA199" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB199" s="2"/>
+      <x:c r="AB199" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC199" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -19416,16 +19644,18 @@
       <x:c r="G200" s="2" t="str">
         <x:v>_idParaDest-282</x:v>
       </x:c>
-      <x:c r="H200" s="2" t="n">
+      <x:c r="H200" s="2" t="str">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="I200" s="2" t="n">
+      <x:c r="I200" s="2" t="str">
         <x:v>136</x:v>
       </x:c>
       <x:c r="J200" s="2" t="str">
         <x:v>6.4 Setting objectives and evaluation metrics</x:v>
       </x:c>
-      <x:c r="K200" s="2"/>
+      <x:c r="K200" s="2" t="str">
+        <x:v>6.4 Постановка целей и определение метрик оценки</x:v>
+      </x:c>
       <x:c r="L200" s="2" t="str">
         <x:v>&lt;h1 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-1" id="_idParaDest-282"&gt;
     &lt;a id="_idTextAnchor274"&gt;
@@ -19436,7 +19666,9 @@
    &lt;/h1&gt;
    </x:v>
       </x:c>
-      <x:c r="M200" s="2"/>
+      <x:c r="M200" s="2" t="str">
+        <x:v>&lt;h1 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-1" id="_idParaDest-282"&gt;&lt;a id="_idTextAnchor274"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.453.1"&gt;6.4 Постановка целей и определение метрик оценки&lt;/span&gt;&lt;/h1&gt;</x:v>
+      </x:c>
       <x:c r="N200" s="2"/>
       <x:c r="O200" s="2"/>
       <x:c r="P200" s="2"/>
@@ -19447,27 +19679,29 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U200" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V200" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W200" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X200" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y200" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z200" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA200" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB200" s="2"/>
+      <x:c r="AB200" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC200" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -19492,16 +19726,18 @@
         <x:v>/*/*[2]/*/*[111]</x:v>
       </x:c>
       <x:c r="G201" s="2"/>
-      <x:c r="H201" s="2" t="n">
+      <x:c r="H201" s="2" t="str">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="I201" s="2" t="n">
+      <x:c r="I201" s="2" t="str">
         <x:v>136</x:v>
       </x:c>
       <x:c r="J201" s="2" t="str">
         <x:v>A research program needs an explicit definition of “better” before running large experiment grids. Here, “better” means economic value under a fixed trading setup : portfolio returns produced by mapping model outputs into positions and applying constraints and costs. This section specifies three important rules:</x:v>
       </x:c>
-      <x:c r="K201" s="2"/>
+      <x:c r="K201" s="2" t="str">
+        <x:v>До запуска крупных сеток экспериментов исследовательская программа должна явно определить, что означает «лучше». Здесь под «лучше» понимается экономическая ценность при фиксированных параметрах торговли: доходность портфеля, получаемая путём преобразования выходных данных модели в позиции с последующим применением ограничений и учётом издержек. В этом разделе устанавливаются три важных правила:</x:v>
+      </x:c>
       <x:c r="L201" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.454.1"&gt;
@@ -19524,7 +19760,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M201" s="2"/>
+      <x:c r="M201" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.454.1"&gt;До запуска крупных сеток экспериментов исследовательская программа должна явно определить, что означает «лучше». &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.454.2"&gt;Здесь под «лучше» понимается &lt;/span&gt;&lt;strong class="screenText"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.455.1"&gt;экономическая ценность при фиксированных параметрах торговли&lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.456.1"&gt;: доходность портфеля, получаемая путём преобразования выходных данных модели в позиции с последующим применением ограничений и учётом издержек. &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.456.2"&gt;В этом разделе устанавливаются три важных правила:&lt;/span&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N201" s="2"/>
       <x:c r="O201" s="2"/>
       <x:c r="P201" s="2"/>
@@ -19535,27 +19773,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U201" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V201" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W201" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X201" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y201" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z201" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="AA201" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB201" s="2"/>
+      <x:c r="AB201" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC201" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>

--- a/chapters/CH06/registry/CH06_registry_v0.1_current.xlsx
+++ b/chapters/CH06/registry/CH06_registry_v0.1_current.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Блоки" sheetId="1" r:id="Rcedc46f915bb4461"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Блоки" sheetId="1" r:id="Re9daf3b6f1ea4c8a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16385,7 +16385,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z162" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA162" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -16470,7 +16470,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z163" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA163" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -16548,7 +16548,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z164" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA164" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -16632,7 +16632,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z165" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA165" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -16720,7 +16720,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z166" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA166" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -16804,7 +16804,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z167" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA167" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -16895,7 +16895,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z168" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA168" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -16994,7 +16994,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z169" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA169" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -17087,7 +17087,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z170" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA170" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -17183,7 +17183,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z171" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA171" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -17279,7 +17279,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z172" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA172" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -17372,7 +17372,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z173" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA173" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -17462,7 +17462,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z174" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA174" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -17560,7 +17560,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z175" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA175" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -17667,7 +17667,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z176" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA176" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -17751,7 +17751,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z177" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA177" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -17845,7 +17845,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z178" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA178" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -17930,7 +17930,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z179" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA179" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -18015,7 +18015,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z180" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA180" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -18100,7 +18100,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z181" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA181" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -18185,7 +18185,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z182" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA182" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -18270,7 +18270,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z183" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA183" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -18366,7 +18366,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z184" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA184" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -18452,7 +18452,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z185" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA185" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -18538,7 +18538,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z186" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA186" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -18620,7 +18620,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z187" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA187" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -18702,7 +18702,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z188" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA188" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -18784,7 +18784,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z189" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA189" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -18866,7 +18866,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z190" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA190" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -18948,7 +18948,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z191" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA191" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -19030,7 +19030,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z192" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA192" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -19112,7 +19112,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z193" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA193" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -19194,7 +19194,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z194" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA194" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -19276,7 +19276,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z195" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA195" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -19358,7 +19358,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z196" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA196" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -19436,7 +19436,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z197" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA197" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -19517,7 +19517,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z198" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA198" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -19610,7 +19610,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z199" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA199" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -19694,7 +19694,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z200" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA200" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
@@ -19788,7 +19788,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z201" s="2" t="str">
-        <x:v>PASS</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA201" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>

--- a/chapters/CH06/registry/CH06_registry_v0.1_current.xlsx
+++ b/chapters/CH06/registry/CH06_registry_v0.1_current.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Блоки" sheetId="1" r:id="Rc9a1de05815b4812"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Блоки" sheetId="1" r:id="Re9daf3b6f1ea4c8a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16332,16 +16332,18 @@
         <x:v>/*/*[2]/*/*[92]/*[4]</x:v>
       </x:c>
       <x:c r="G162" s="2"/>
-      <x:c r="H162" s="2" t="n">
+      <x:c r="H162" s="2" t="str">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="I162" s="2" t="n">
+      <x:c r="I162" s="2" t="str">
         <x:v>133</x:v>
       </x:c>
       <x:c r="J162" s="2" t="str">
         <x:v>Position sizing: How scores translate into exposures (for example, equal weight, volatility targeting).</x:v>
       </x:c>
-      <x:c r="K162" s="2"/>
+      <x:c r="K162" s="2" t="str">
+        <x:v>Определение размера позиции: как оценки преобразуются в величины подверженности риску (например, равные веса, таргетирование волатильности).</x:v>
+      </x:c>
       <x:c r="L162" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -16355,7 +16357,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M162" s="2"/>
+      <x:c r="M162" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.375.1"&gt;Определение размера позиции: &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.376.1"&gt;как оценки преобразуются в величины подверженности риску (например, равные веса, таргетирование волатильности).&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N162" s="2"/>
       <x:c r="O162" s="2"/>
       <x:c r="P162" s="2"/>
@@ -16366,29 +16370,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U162" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V162" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W162" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X162" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y162" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z162" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA162" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB162" s="2"/>
+      <x:c r="AB162" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC162" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -16411,16 +16417,18 @@
         <x:v>/*/*[2]/*/*[92]/*[5]</x:v>
       </x:c>
       <x:c r="G163" s="2"/>
-      <x:c r="H163" s="2" t="n">
+      <x:c r="H163" s="2" t="str">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="I163" s="2" t="n">
+      <x:c r="I163" s="2" t="str">
         <x:v>133</x:v>
       </x:c>
       <x:c r="J163" s="2" t="str">
         <x:v>Order timing: When orders are placed (at open, intraday window, execution delay).</x:v>
       </x:c>
-      <x:c r="K163" s="2"/>
+      <x:c r="K163" s="2" t="str">
+        <x:v>Время размещения заявок: когда размещаются заявки (на открытии, в течение внутридневного окна, с задержкой исполнения).</x:v>
+      </x:c>
       <x:c r="L163" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -16434,7 +16442,9 @@
     &lt;/li&gt;
    </x:v>
       </x:c>
-      <x:c r="M163" s="2"/>
+      <x:c r="M163" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.377.1"&gt;Время размещения заявок: &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.378.1"&gt;когда размещаются заявки (на открытии, в течение внутридневного окна, с задержкой исполнения).&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N163" s="2"/>
       <x:c r="O163" s="2"/>
       <x:c r="P163" s="2"/>
@@ -16445,29 +16455,31 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U163" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V163" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W163" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X163" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y163" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z163" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA163" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB163" s="2"/>
+      <x:c r="AB163" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC163" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -16490,16 +16502,18 @@
         <x:v>/*/*[2]/*/*[93]</x:v>
       </x:c>
       <x:c r="G164" s="2"/>
-      <x:c r="H164" s="2" t="n">
+      <x:c r="H164" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I164" s="2" t="n">
+      <x:c r="I164" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J164" s="2" t="str">
         <x:v>The specifics will likely evolve, but when they do, the reference for comparison will as well.</x:v>
       </x:c>
-      <x:c r="K164" s="2"/>
+      <x:c r="K164" s="2" t="str">
+        <x:v>Конкретные параметры, вероятно, будут меняться, но вместе с ними будет меняться и база сравнения.</x:v>
+      </x:c>
       <x:c r="L164" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.379.1"&gt;
@@ -16508,7 +16522,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M164" s="2"/>
+      <x:c r="M164" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.379.1"&gt;Конкретные параметры, вероятно, будут меняться, но вместе с ними будет меняться и база сравнения.&lt;/span&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N164" s="2"/>
       <x:c r="O164" s="2"/>
       <x:c r="P164" s="2"/>
@@ -16517,27 +16533,29 @@
       <x:c r="S164" s="2"/>
       <x:c r="T164" s="2"/>
       <x:c r="U164" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V164" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W164" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X164" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y164" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z164" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA164" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB164" s="2"/>
+      <x:c r="AB164" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC164" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -16564,16 +16582,18 @@
       <x:c r="G165" s="2" t="str">
         <x:v>_idParaDest-279</x:v>
       </x:c>
-      <x:c r="H165" s="2" t="n">
+      <x:c r="H165" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I165" s="2" t="n">
+      <x:c r="I165" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J165" s="2" t="str">
         <x:v>Constraints and risk controls in scope</x:v>
       </x:c>
-      <x:c r="K165" s="2"/>
+      <x:c r="K165" s="2" t="str">
+        <x:v>Ограничения и меры контроля риска, учитываемые в исследовании</x:v>
+      </x:c>
       <x:c r="L165" s="2" t="str">
         <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-279"&gt;
     &lt;a id="_idTextAnchor271"&gt;
@@ -16584,7 +16604,9 @@
    &lt;/h3&gt;
    </x:v>
       </x:c>
-      <x:c r="M165" s="2"/>
+      <x:c r="M165" s="2" t="str">
+        <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-279"&gt;&lt;a id="_idTextAnchor271"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.380.1"&gt;Ограничения и меры контроля риска, учитываемые в исследовании&lt;/span&gt;&lt;/h3&gt;</x:v>
+      </x:c>
       <x:c r="N165" s="2"/>
       <x:c r="O165" s="2"/>
       <x:c r="P165" s="2"/>
@@ -16595,27 +16617,29 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U165" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V165" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W165" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X165" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y165" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z165" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA165" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB165" s="2"/>
+      <x:c r="AB165" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC165" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -16640,16 +16664,18 @@
         <x:v>/*/*[2]/*/*[95]</x:v>
       </x:c>
       <x:c r="G166" s="2"/>
-      <x:c r="H166" s="2" t="n">
+      <x:c r="H166" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I166" s="2" t="n">
+      <x:c r="I166" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J166" s="2" t="str">
         <x:v>Specify the constraints treated as binding: exposure and leverage limits, concentration rules, and any liquidity or capacity limits enforced. Risk controls that alter trading actions (for example, a de-risking overlay or a kill switch) must be explicit and versioned, as they alter the effective strategy.</x:v>
       </x:c>
-      <x:c r="K166" s="2"/>
+      <x:c r="K166" s="2" t="str">
+        <x:v>Укажите ограничения, считающиеся обязательными: лимиты подверженности риску и кредитного плеча, правила концентрации, а также применяемые ограничения ликвидности или ёмкости стратегии. Меры контроля риска, изменяющие торговые действия (например, дополнительный механизм снижения риска или механизм аварийной остановки торговли), должны быть заданы явно и версионироваться, поскольку они изменяют фактическую стратегию.</x:v>
+      </x:c>
       <x:c r="L166" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.381.1"&gt;
@@ -16666,7 +16692,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M166" s="2"/>
+      <x:c r="M166" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.381.1"&gt;Укажите ограничения, считающиеся обязательными: лимиты подверженности риску и кредитного плеча, правила концентрации, а также применяемые ограничения ликвидности или ёмкости стратегии. Меры контроля риска, изменяющие торговые действия (например, дополнительный механизм снижения риска или механизм аварийной остановки торговли), должны быть заданы явно и версионироваться, поскольку они изменяют фактическую стратегию.&lt;/span&gt;&lt;a id="_idIndexMarker692"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.382.1"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.382.2"/&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N166" s="2"/>
       <x:c r="O166" s="2"/>
       <x:c r="P166" s="2"/>
@@ -16677,27 +16705,29 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U166" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V166" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W166" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X166" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y166" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z166" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA166" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB166" s="2"/>
+      <x:c r="AB166" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC166" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -16724,16 +16754,18 @@
       <x:c r="G167" s="2" t="str">
         <x:v>_idParaDest-280</x:v>
       </x:c>
-      <x:c r="H167" s="2" t="n">
+      <x:c r="H167" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I167" s="2" t="n">
+      <x:c r="I167" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J167" s="2" t="str">
         <x:v>Cost model class and components</x:v>
       </x:c>
-      <x:c r="K167" s="2"/>
+      <x:c r="K167" s="2" t="str">
+        <x:v>Класс и компоненты модели издержек</x:v>
+      </x:c>
       <x:c r="L167" s="2" t="str">
         <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-280"&gt;
     &lt;a id="_idTextAnchor272"&gt;
@@ -16744,7 +16776,9 @@
    &lt;/h3&gt;
    </x:v>
       </x:c>
-      <x:c r="M167" s="2"/>
+      <x:c r="M167" s="2" t="str">
+        <x:v>&lt;h3 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-3" id="_idParaDest-280"&gt;&lt;a id="_idTextAnchor272"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.383.1"&gt;Класс и компоненты модели издержек&lt;/span&gt;&lt;/h3&gt;</x:v>
+      </x:c>
       <x:c r="N167" s="2"/>
       <x:c r="O167" s="2"/>
       <x:c r="P167" s="2"/>
@@ -16755,27 +16789,29 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U167" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V167" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W167" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X167" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y167" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z167" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA167" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB167" s="2"/>
+      <x:c r="AB167" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC167" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -16800,16 +16836,18 @@
         <x:v>/*/*[2]/*/*[97]</x:v>
       </x:c>
       <x:c r="G168" s="2"/>
-      <x:c r="H168" s="2" t="n">
+      <x:c r="H168" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I168" s="2" t="n">
+      <x:c r="I168" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J168" s="2" t="str">
         <x:v>Early research does not need a perfect simulator, but it does require consistency about which frictions are treated as material. State the cost components included (fees, spreads, slippage/impact, financing or funding, borrow, roll) and how conservative the assumptions are. Later chapters expand the cost model; early screens use conservative, coarse assumptions.</x:v>
       </x:c>
-      <x:c r="K168" s="2"/>
+      <x:c r="K168" s="2" t="str">
+        <x:v>Исследованию на ранней стадии не нужен идеальный симулятор, однако необходимо последовательно определить, какие рыночные трения считаются существенными. Укажите включённые компоненты издержек (комиссии, спреды, проскальзывание и влияние на рынок, затраты на финансирование или выплаты по ставке финансирования, стоимость заимствования, издержки роллирования) и степень консервативности допущений. В последующих главах модель издержек уточняется; при предварительном отборе используются консервативные укрупнённые допущения.</x:v>
+      </x:c>
       <x:c r="L168" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.384.1"&gt;
@@ -16829,7 +16867,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M168" s="2"/>
+      <x:c r="M168" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.384.1"&gt;Исследованию на ранней стадии не нужен идеальный симулятор, однако необходимо последовательно определить, какие рыночные трения считаются существенными. Укажите включённые компоненты издержек (комиссии, спреды, проскальзывание и влияние на рынок, затраты на финансирование или выплаты по ставке финансирования, стоимость заимствования, издержки роллирования) и степень консервативности допущений. В последующих главах модель издержек уточняется; при предварительном отборе используются консервативные укрупнённые допущения.&lt;/span&gt;&lt;a id="_idIndexMarker693"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.385.1"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.385.2"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.385.3"/&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N168" s="2"/>
       <x:c r="O168" s="2"/>
       <x:c r="P168" s="2"/>
@@ -16840,27 +16880,29 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U168" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V168" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W168" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X168" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y168" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z168" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA168" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB168" s="2"/>
+      <x:c r="AB168" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC168" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -16885,16 +16927,18 @@
         <x:v>/*/*[2]/*/*[98]</x:v>
       </x:c>
       <x:c r="G169" s="2"/>
-      <x:c r="H169" s="2" t="n">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="I169" s="2" t="n">
-        <x:v>123</x:v>
+      <x:c r="H169" s="2" t="str">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="I169" s="2" t="str">
+        <x:v>134</x:v>
       </x:c>
       <x:c r="J169" s="2" t="str">
         <x:v>Example (perpetual futures) : in crypto_perps_funding , funding is a position-dependent cash flow that is part of the total return stream: a cost when paid and a benefit when received. Because it accrues only when a position is held at the funding timestamp and is settled under venue-specific conventions, the trading setup must specify (i) how trades and position changes are aligned to the funding snapshot, (ii) which pricing and funding formula (including any caps/floors) and fee schedule are assumed, and (iii) how convention changes are versioned. Otherwise, the same backtest can imply different effective exposures and produce materially different PnL.</x:v>
       </x:c>
-      <x:c r="K169" s="2"/>
+      <x:c r="K169" s="2" t="str">
+        <x:v>Пример (бессрочные фьючерсы): в crypto_perps_funding платежи по ставке финансирования представляют собой зависящий от позиции денежный поток, входящий в совокупную доходность: издержки при выплате и доход при получении. Поскольку он начисляется только при наличии позиции в момент фиксации ставки финансирования, а расчёты проводятся по правилам конкретной торговой площадки, параметры торговли должны определять: (i) как сделки и изменения позиций согласуются с моментом фиксации ставки финансирования; (ii) какие формулы ценообразования и расчёта ставки финансирования предполагаются (включая верхние и нижние ограничения), а также какая тарифная сетка комиссий используется; (iii) как версионируются изменения правил. Иначе один и тот же бэктест может подразумевать разную фактическую подверженность риску и давать существенно различающиеся PnL.</x:v>
+      </x:c>
       <x:c r="L169" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;em class="italic"&gt;
@@ -16922,7 +16966,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M169" s="2"/>
+      <x:c r="M169" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;em class="italic"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.386.1"&gt;Пример (бессрочные фьючерсы)&lt;/span&gt;&lt;/em&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.387.1"&gt;: в &lt;/span&gt;&lt;code class="inlineCode"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.388.1"&gt;crypto_perps_funding &lt;/span&gt;&lt;/code&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.389.1"&gt;платежи по ставке финансирования представляют собой зависящий от позиции денежный поток, входящий в совокупную доходность: издержки при выплате и доход при получении. &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.389.2"&gt;Поскольку он начисляется только при наличии позиции в момент фиксации ставки финансирования, а расчёты проводятся по правилам конкретной торговой площадки, параметры торговли должны определять: (i) как сделки и изменения позиций согласуются с моментом фиксации ставки финансирования; (ii) какие формулы ценообразования и расчёта ставки финансирования предполагаются (включая верхние и нижние ограничения), а также какая тарифная сетка комиссий используется; (iii) как версионируются изменения правил. &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.389.3"&gt;Иначе один и тот же бэктест может подразумевать разную фактическую подверженность риску и давать существенно различающиеся PnL.&lt;/span&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N169" s="2"/>
       <x:c r="O169" s="2"/>
       <x:c r="P169" s="2"/>
@@ -16933,27 +16979,29 @@
         <x:v>em,code</x:v>
       </x:c>
       <x:c r="U169" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V169" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W169" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X169" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y169" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z169" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA169" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB169" s="2"/>
+      <x:c r="AB169" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC169" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -16978,16 +17026,18 @@
         <x:v>/*/*[2]/*/*[99]</x:v>
       </x:c>
       <x:c r="G170" s="2"/>
-      <x:c r="H170" s="2" t="n">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="I170" s="2" t="n">
-        <x:v>123</x:v>
+      <x:c r="H170" s="2" t="str">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="I170" s="2" t="str">
+        <x:v>134</x:v>
       </x:c>
       <x:c r="J170" s="2" t="str">
         <x:v>Example : The ETF cross-asset momentum setup (v1) defines the following invariants:</x:v>
       </x:c>
-      <x:c r="K170" s="2"/>
+      <x:c r="K170" s="2" t="str">
+        <x:v>Пример: параметры моментум-стратегии по различным классам активов на основе ETF (v1) задают следующие инварианты:</x:v>
+      </x:c>
       <x:c r="L170" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;em class="italic"&gt;
@@ -17009,7 +17059,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M170" s="2"/>
+      <x:c r="M170" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;em class="italic"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.390.1"&gt;Пример&lt;/span&gt;&lt;/em&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.391.1"&gt;: &lt;/span&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.392.1"&gt;параметры моментум-стратегии по различным классам активов на основе ETF (v1) &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.393.1"&gt;задают следующие инварианты:&lt;/span&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N170" s="2"/>
       <x:c r="O170" s="2"/>
       <x:c r="P170" s="2"/>
@@ -17020,29 +17072,31 @@
         <x:v>strong,em</x:v>
       </x:c>
       <x:c r="U170" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V170" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W170" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X170" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y170" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z170" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA170" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB170" s="2"/>
+      <x:c r="AB170" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC170" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -17065,16 +17119,18 @@
         <x:v>/*/*[2]/*/*[100]/*[1]</x:v>
       </x:c>
       <x:c r="G171" s="2"/>
-      <x:c r="H171" s="2" t="n">
+      <x:c r="H171" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I171" s="2" t="n">
+      <x:c r="I171" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J171" s="2" t="str">
         <x:v>Universe: 100 cross-asset ETFs with point-in-time eligibility based on trailing annual ADV ≥ $10M. The lenient threshold preserves cross-sectional breadth in early sample years (70–95 eligible ETFs per year). Note that the universe composition has survivorship bias that cannot be fully resolved without historical constituent data, while within-universe eligibility is point-in-time correct.</x:v>
       </x:c>
-      <x:c r="K171" s="2"/>
+      <x:c r="K171" s="2" t="str">
+        <x:v>Совокупность активов: 100 ETF по различным классам активов, для которых допуск определяется на соответствующий момент времени на основе среднего дневного объёма торгов (ADV) за предшествующий год ≥ 10 млн долларов США. Мягкий порог сохраняет широту поперечного сечения в первые годы выборки (70–95 допустимых ETF в год). Следует учитывать, что состав совокупности активов подвержен смещению выживших, которое невозможно полностью устранить без исторических данных о её составе, тогда как критерии допуска внутри совокупности корректно применяются на соответствующий момент времени.</x:v>
+      </x:c>
       <x:c r="L171" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -17099,7 +17155,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M171" s="2"/>
+      <x:c r="M171" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.394.1"&gt;Совокупность активов: &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.395.1"&gt;100 ETF по различным классам активов, для которых допуск определяется на соответствующий момент времени на основе среднего дневного объёма торгов (ADV) за предшествующий год ≥ 10 млн долларов США. &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.395.2"&gt;Мягкий порог сохраняет широту поперечного сечения в первые годы выборки (70–95 допустимых ETF в год). &lt;/span&gt;&lt;a id="_idIndexMarker694"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.396.1"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.396.2"&gt;Следует учитывать, что состав совокупности активов подвержен смещению выживших, которое невозможно полностью устранить без исторических данных о её составе, тогда как критерии допуска внутри совокупности корректно применяются на соответствующий момент времени.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N171" s="2"/>
       <x:c r="O171" s="2"/>
       <x:c r="P171" s="2"/>
@@ -17110,29 +17168,31 @@
         <x:v>strong,a</x:v>
       </x:c>
       <x:c r="U171" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V171" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W171" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X171" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y171" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z171" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA171" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB171" s="2"/>
+      <x:c r="AB171" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC171" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -17155,16 +17215,18 @@
         <x:v>/*/*[2]/*/*[100]/*[2]</x:v>
       </x:c>
       <x:c r="G172" s="2"/>
-      <x:c r="H172" s="2" t="n">
+      <x:c r="H172" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I172" s="2" t="n">
+      <x:c r="I172" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J172" s="2" t="str">
         <x:v>Decision schedule: Monthly month-end close snapshot with execution at the next-day bar open. This aligns with momentum literature for benchmark comparability. Weekly (5-day) cadence is tested as a variant.</x:v>
       </x:c>
-      <x:c r="K172" s="2"/>
+      <x:c r="K172" s="2" t="str">
+        <x:v>График принятия решений: ежемесячный снимок цен закрытия на конец месяца с исполнением по цене открытия бара следующего дня. Это соответствует литературе о моментуме и обеспечивает сопоставимость с эталонными результатами исследований моментума. В качестве варианта тестируется недельная (5-дневная) периодичность.</x:v>
+      </x:c>
       <x:c r="L172" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -17189,7 +17251,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M172" s="2"/>
+      <x:c r="M172" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.397.1"&gt;График принятия решений: &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.398.1"&gt;ежемесячный &lt;/span&gt;&lt;a id="_idIndexMarker695"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.399.1"&gt;снимок цен закрытия на конец месяца с исполнением по цене открытия бара следующего дня. &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.399.2"&gt;Это соответствует литературе о моментуме и обеспечивает сопоставимость с эталонными результатами исследований моментума. &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.399.3"&gt;В качестве варианта тестируется недельная (5-дневная) периодичность.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N172" s="2"/>
       <x:c r="O172" s="2"/>
       <x:c r="P172" s="2"/>
@@ -17200,29 +17264,31 @@
         <x:v>strong,a</x:v>
       </x:c>
       <x:c r="U172" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V172" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W172" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X172" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y172" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z172" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA172" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB172" s="2"/>
+      <x:c r="AB172" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC172" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -17245,16 +17311,18 @@
         <x:v>/*/*[2]/*/*[100]/*[3]</x:v>
       </x:c>
       <x:c r="G173" s="2"/>
-      <x:c r="H173" s="2" t="n">
+      <x:c r="H173" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I173" s="2" t="n">
+      <x:c r="I173" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J173" s="2" t="str">
         <x:v>Mapping: Long-only, rank-select top-N, equal-weight, rebalanced on cadence. Long-only because ETFs are expensive to short; equal-weight because it isolates the ranking signal from sizing optimization that would confound evaluation.</x:v>
       </x:c>
-      <x:c r="K173" s="2"/>
+      <x:c r="K173" s="2" t="str">
+        <x:v>Преобразование: только длинные позиции, отбор top-N по рангу, равные веса, ребалансировка с заданной периодичностью. Только длинные позиции — потому что открывать короткие позиции по ETF дорого; равные веса — потому что они позволяют отделить сигнал ранжирования от оптимизации размеров позиций, которая затруднила бы интерпретацию результатов оценки.</x:v>
+      </x:c>
       <x:c r="L173" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -17276,7 +17344,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M173" s="2"/>
+      <x:c r="M173" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.400.1"&gt;Преобразование: &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.401.1"&gt;только длинные позиции, отбор top-N по рангу, равные веса, ребалансировка с заданной периодичностью. &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.401.2"&gt;Только длинные позиции — потому что &lt;/span&gt;&lt;a id="_idIndexMarker696"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.402.1"&gt;открывать короткие позиции по ETF дорого; равные веса — потому что они позволяют отделить сигнал ранжирования от оптимизации размеров позиций, которая затруднила бы интерпретацию результатов оценки.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N173" s="2"/>
       <x:c r="O173" s="2"/>
       <x:c r="P173" s="2"/>
@@ -17287,29 +17357,31 @@
         <x:v>strong,a</x:v>
       </x:c>
       <x:c r="U173" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V173" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W173" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X173" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y173" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z173" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA173" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB173" s="2"/>
+      <x:c r="AB173" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC173" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -17332,16 +17404,18 @@
         <x:v>/*/*[2]/*/*[100]/*[4]</x:v>
       </x:c>
       <x:c r="G174" s="2"/>
-      <x:c r="H174" s="2" t="n">
+      <x:c r="H174" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I174" s="2" t="n">
+      <x:c r="I174" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J174" s="2" t="str">
         <x:v>Constraints: Fully invested long-only with no leverage, a minimal constraint set appropriate for a pedagogical baseline.</x:v>
       </x:c>
-      <x:c r="K174" s="2"/>
+      <x:c r="K174" s="2" t="str">
+        <x:v>Ограничения: полностью инвестированный портфель только с длинными позициями, без кредитного плеча — минимальный набор ограничений, подходящий для учебного базового варианта.</x:v>
+      </x:c>
       <x:c r="L174" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -17360,7 +17434,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M174" s="2"/>
+      <x:c r="M174" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.403.1"&gt;Ограничения: &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.404.1"&gt;полностью &lt;/span&gt;&lt;a id="_idIndexMarker697"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.405.1"&gt;инвестированный портфель только с длинными позициями, без кредитного плеча — минимальный набор ограничений, подходящий для учебного базового варианта.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N174" s="2"/>
       <x:c r="O174" s="2"/>
       <x:c r="P174" s="2"/>
@@ -17371,29 +17447,31 @@
         <x:v>strong,a</x:v>
       </x:c>
       <x:c r="U174" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V174" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W174" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X174" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y174" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z174" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA174" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB174" s="2"/>
+      <x:c r="AB174" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC174" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -17416,16 +17494,18 @@
         <x:v>/*/*[2]/*/*[100]/*[5]</x:v>
       </x:c>
       <x:c r="G175" s="2"/>
-      <x:c r="H175" s="2" t="n">
+      <x:c r="H175" s="2" t="str">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="I175" s="2" t="n">
+      <x:c r="I175" s="2" t="str">
         <x:v>134</x:v>
       </x:c>
       <x:c r="J175" s="2" t="str">
         <x:v>Cost model: Material is a per-share commission ($0.0035/share, IBKR Pro Tiered) plus tiered half-spread slippage (0.5¢ for the most liquid mega-ETFs, 1¢ for sector ETFs, 2¢ default for thematic and regional ETFs). The horizon feasibility analysis uses a 5–15 bps-per-leg reference cost line to screen cadences and confirms that monthly moves exceed 30 bps round-trip costs in over 90% of observations; daily trading operates in the gray zone where feasibility depends on signal strength and turnover.</x:v>
       </x:c>
-      <x:c r="K175" s="2"/>
+      <x:c r="K175" s="2" t="str">
+        <x:v>Модель издержек: к существенным издержкам относятся комиссия в размере 0,0035 доллара США за акцию (тариф IBKR Pro Tiered) и дифференцированное проскальзывание в размере половины спреда (0,5 цента для наиболее ликвидных крупнейших ETF, 1 цент для отраслевых ETF и 2 цента по умолчанию для тематических и региональных ETF). При анализе осуществимости горизонта для отбора вариантов периодичности используется контрольная линия издержек 5–15 базисных пунктов (б.п.) на одну сторону сделки. Анализ подтверждает, что месячные ценовые движения превышают издержки полного цикла сделки, равные 30 б.п., более чем в 90 % наблюдений; ежедневная торговля находится в серой зоне, где осуществимость зависит от силы сигнала и оборота портфеля.</x:v>
+      </x:c>
       <x:c r="L175" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -17452,7 +17532,9 @@
     &lt;/li&gt;
    </x:v>
       </x:c>
-      <x:c r="M175" s="2"/>
+      <x:c r="M175" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.406.1"&gt;Модель издержек: &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.407.1"&gt;к существенным издержкам относятся &lt;/span&gt;&lt;a id="_idIndexMarker698"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.408.1"&gt;комиссия в размере 0,0035 доллара США за акцию (тариф IBKR Pro Tiered) и дифференцированное проскальзывание в размере половины спреда (0,5 цента для наиболее ликвидных крупнейших ETF, 1 цент для отраслевых ETF и 2 цента по умолчанию для тематических и региональных ETF). &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.408.2"&gt;При анализе осуществимости горизонта для отбора вариантов периодичности используется контрольная линия издержек 5–15 базисных пунктов (б.п.) на одну сторону сделки. Анализ подтверждает, что месячные ценовые движения превышают издержки полного цикла сделки, равные 30 б.п., более чем в 90 % наблюдений; ежедневная торговля находится в серой зоне, &lt;/span&gt;&lt;a id="_idIndexMarker699"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.409.1"&gt;где осуществимость зависит от силы сигнала и оборота портфеля.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N175" s="2"/>
       <x:c r="O175" s="2"/>
       <x:c r="P175" s="2"/>
@@ -17463,29 +17545,31 @@
         <x:v>strong,a</x:v>
       </x:c>
       <x:c r="U175" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V175" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W175" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X175" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y175" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z175" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA175" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB175" s="2"/>
+      <x:c r="AB175" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC175" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -17508,16 +17592,18 @@
         <x:v>/*/*[2]/*/*[101]</x:v>
       </x:c>
       <x:c r="G176" s="2"/>
-      <x:c r="H176" s="2" t="n">
+      <x:c r="H176" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I176" s="2" t="n">
+      <x:c r="I176" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J176" s="2" t="str">
         <x:v>The setup notebook writes these choices to versioned YAML artifacts ( setup.yaml ) that downstream chapters consume programmatically. Changing the mapping from long-only to long/short would require setup_version: v2 and a new baseline checkpoint; parameter changes, such as adjusting top-N from 10 to 20, remain within v1 .</x:v>
       </x:c>
-      <x:c r="K176" s="2"/>
+      <x:c r="K176" s="2" t="str">
+        <x:v>Ноутбук параметров торговли записывает эти решения в версионируемые артефакты YAML (setup.yaml), которые программно используются в последующих главах. Для изменения преобразования с только длинных позиций на длинные/короткие потребовались бы setup_version: v2 и новая контрольная точка базового варианта; изменения параметров, например увеличение top-N с 10 до 20, остаются в рамках v1.</x:v>
+      </x:c>
       <x:c r="L176" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.410.1"&gt;
@@ -17553,7 +17639,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M176" s="2"/>
+      <x:c r="M176" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.410.1"&gt;Ноутбук параметров торговли записывает эти решения в версионируемые артефакты YAML (&lt;/span&gt;&lt;code class="inlineCode"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.411.1"&gt;setup.yaml&lt;/span&gt;&lt;/code&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.412.1"&gt;), которые программно используются в последующих главах. &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.412.2"&gt;Для изменения преобразования с только длинных позиций на длинные/короткие потребовались бы &lt;/span&gt;&lt;code class="inlineCode"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.413.1"&gt;setup_version: v2 &lt;/span&gt;&lt;/code&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.414.1"&gt;и новая контрольная точка базового варианта; изменения параметров, например увеличение top-N с 10 до 20, остаются в рамках &lt;/span&gt;&lt;code class="inlineCode"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.415.1"&gt;v1&lt;/span&gt;&lt;/code&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.416.1"&gt;.&lt;/span&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N176" s="2"/>
       <x:c r="O176" s="2"/>
       <x:c r="P176" s="2"/>
@@ -17564,27 +17652,29 @@
         <x:v>code</x:v>
       </x:c>
       <x:c r="U176" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V176" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W176" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X176" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y176" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z176" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA176" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB176" s="2"/>
+      <x:c r="AB176" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC176" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -17611,16 +17701,18 @@
       <x:c r="G177" s="2" t="str">
         <x:v>_idParaDest-281</x:v>
       </x:c>
-      <x:c r="H177" s="2" t="n">
+      <x:c r="H177" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I177" s="2" t="n">
+      <x:c r="I177" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J177" s="2" t="str">
         <x:v>When a change requires a new setup version</x:v>
       </x:c>
-      <x:c r="K177" s="2"/>
+      <x:c r="K177" s="2" t="str">
+        <x:v>Когда изменение требует новой версии параметров торговли</x:v>
+      </x:c>
       <x:c r="L177" s="2" t="str">
         <x:v>&lt;h2 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-2" id="_idParaDest-281"&gt;
     &lt;a id="_idTextAnchor273"&gt;
@@ -17631,7 +17723,9 @@
    &lt;/h2&gt;
    </x:v>
       </x:c>
-      <x:c r="M177" s="2"/>
+      <x:c r="M177" s="2" t="str">
+        <x:v>&lt;h2 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-2" id="_idParaDest-281"&gt;&lt;a id="_idTextAnchor273"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.417.1"&gt;Когда изменение требует новой версии параметров торговли&lt;/span&gt;&lt;/h2&gt;</x:v>
+      </x:c>
       <x:c r="N177" s="2"/>
       <x:c r="O177" s="2"/>
       <x:c r="P177" s="2"/>
@@ -17642,27 +17736,29 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U177" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V177" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W177" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X177" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y177" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z177" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA177" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB177" s="2"/>
+      <x:c r="AB177" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC177" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -17687,16 +17783,18 @@
         <x:v>/*/*[2]/*/*[103]</x:v>
       </x:c>
       <x:c r="G178" s="2"/>
-      <x:c r="H178" s="2" t="n">
+      <x:c r="H178" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I178" s="2" t="n">
+      <x:c r="I178" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J178" s="2" t="str">
         <x:v>Treat the trading setup as versioned. Bump the setup version on any change that alters the strategy’s decision-time meaning or shifts its dominant frictions and constraints. Parameter tuning stays within a setup; changes to mechanics define a new setup. A change is a new setup version if it changes at least one of:</x:v>
       </x:c>
-      <x:c r="K178" s="2"/>
+      <x:c r="K178" s="2" t="str">
+        <x:v>Рассматривайте параметры торговли как версионируемый объект. Повышайте номер версии при любом изменении, которое меняет интерпретацию стратегии в момент принятия решения либо её преобладающие рыночные трения и ограничения. Настройка параметров выполняется в рамках одной версии; изменения торгового механизма определяют новую версию. Изменение требует новой версии параметров торговли, если затрагивает хотя бы один из следующих элементов:</x:v>
+      </x:c>
       <x:c r="L178" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.418.1"&gt;
@@ -17719,7 +17817,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M178" s="2"/>
+      <x:c r="M178" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.418.1"&gt;Рассматривайте параметры торговли как версионируемый объект. Повышайте номер версии при любом изменении, которое меняет интерпретацию стратегии в момент принятия решения либо её преобладающие рыночные трения и ограничения. Настройка параметров выполняется в рамках одной версии; изменения торгового механизма определяют новую версию. Изменение требует новой версии параметров торговли, если затрагивает хотя бы один из следующих элементов:&lt;/span&gt;&lt;a id="_idIndexMarker700"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.419.1"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.419.2"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.419.3"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.419.4"/&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N178" s="2"/>
       <x:c r="O178" s="2"/>
       <x:c r="P178" s="2"/>
@@ -17730,27 +17830,29 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U178" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V178" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W178" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X178" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y178" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z178" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA178" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB178" s="2"/>
+      <x:c r="AB178" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC178" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -17775,16 +17877,18 @@
         <x:v>/*/*[2]/*/*[104]/*[1]</x:v>
       </x:c>
       <x:c r="G179" s="2"/>
-      <x:c r="H179" s="2" t="n">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="I179" s="2" t="n">
-        <x:v>123</x:v>
+      <x:c r="H179" s="2" t="str">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="I179" s="2" t="str">
+        <x:v>135</x:v>
       </x:c>
       <x:c r="J179" s="2" t="str">
         <x:v>Universe or tradability rules , for example, eligibility, membership mechanics, instrument scope.</x:v>
       </x:c>
-      <x:c r="K179" s="2"/>
+      <x:c r="K179" s="2" t="str">
+        <x:v>Совокупность активов или правила торгуемости, например критерии включения, механизм изменения состава, охват инструментов.</x:v>
+      </x:c>
       <x:c r="L179" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -17798,7 +17902,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M179" s="2"/>
+      <x:c r="M179" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.420.1"&gt;Совокупность активов или правила торгуемости&lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.421.1"&gt;, например критерии включения, механизм изменения состава, охват инструментов.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N179" s="2"/>
       <x:c r="O179" s="2"/>
       <x:c r="P179" s="2"/>
@@ -17809,27 +17915,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U179" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V179" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W179" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X179" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y179" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z179" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA179" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB179" s="2"/>
+      <x:c r="AB179" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC179" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -17854,16 +17962,18 @@
         <x:v>/*/*[2]/*/*[104]/*[2]</x:v>
       </x:c>
       <x:c r="G180" s="2"/>
-      <x:c r="H180" s="2" t="n">
+      <x:c r="H180" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I180" s="2" t="n">
+      <x:c r="I180" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J180" s="2" t="str">
         <x:v>Decision schedule or admissible information , for example, rebalance snapshot, cadence, execution delay, and input availability rules.</x:v>
       </x:c>
-      <x:c r="K180" s="2"/>
+      <x:c r="K180" s="2" t="str">
+        <x:v>График принятия решений или допустимая информация, например момент снимка для ребалансировки, периодичность, задержка исполнения и правила доступности входных данных.</x:v>
+      </x:c>
       <x:c r="L180" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -17877,7 +17987,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M180" s="2"/>
+      <x:c r="M180" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.422.1"&gt;График принятия решений или допустимая информация&lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.423.1"&gt;, например момент снимка для ребалансировки, периодичность, задержка исполнения и правила доступности входных данных.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N180" s="2"/>
       <x:c r="O180" s="2"/>
       <x:c r="P180" s="2"/>
@@ -17888,27 +18000,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U180" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V180" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W180" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X180" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y180" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z180" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA180" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB180" s="2"/>
+      <x:c r="AB180" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC180" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -17933,16 +18047,18 @@
         <x:v>/*/*[2]/*/*[104]/*[3]</x:v>
       </x:c>
       <x:c r="G181" s="2"/>
-      <x:c r="H181" s="2" t="n">
+      <x:c r="H181" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I181" s="2" t="n">
+      <x:c r="I181" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J181" s="2" t="str">
         <x:v>Score-to-trade mapping at the level of state space, entry or exit form, sizing normalization, or order timing.</x:v>
       </x:c>
-      <x:c r="K181" s="2"/>
+      <x:c r="K181" s="2" t="str">
+        <x:v>Преобразование оценки модели в сделку на уровне пространства состояний, способа входа или выхода, нормализации размера позиции либо времени размещения заявок.</x:v>
+      </x:c>
       <x:c r="L181" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -17956,7 +18072,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M181" s="2"/>
+      <x:c r="M181" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.424.1"&gt;Преобразование оценки модели в сделку &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.425.1"&gt;на уровне пространства состояний, способа входа или выхода, нормализации размера позиции либо времени размещения заявок.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N181" s="2"/>
       <x:c r="O181" s="2"/>
       <x:c r="P181" s="2"/>
@@ -17967,27 +18085,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U181" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V181" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W181" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X181" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y181" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z181" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA181" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB181" s="2"/>
+      <x:c r="AB181" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC181" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18012,16 +18132,18 @@
         <x:v>/*/*[2]/*/*[104]/*[4]</x:v>
       </x:c>
       <x:c r="G182" s="2"/>
-      <x:c r="H182" s="2" t="n">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="I182" s="2" t="n">
-        <x:v>123</x:v>
+      <x:c r="H182" s="2" t="str">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="I182" s="2" t="str">
+        <x:v>135</x:v>
       </x:c>
       <x:c r="J182" s="2" t="str">
         <x:v>Constraint regime , such as binding exposure/leverage limits, concentration rules, capacity or liquidity constraints, action-changing overlays.</x:v>
       </x:c>
-      <x:c r="K182" s="2"/>
+      <x:c r="K182" s="2" t="str">
+        <x:v>Режим ограничений, например обязательные лимиты подверженности риску или кредитного плеча, правила концентрации, ограничения ёмкости стратегии или ликвидности, а также дополнительные механизмы, изменяющие торговые действия.</x:v>
+      </x:c>
       <x:c r="L182" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -18035,7 +18157,9 @@
     &lt;/li&gt;
     </x:v>
       </x:c>
-      <x:c r="M182" s="2"/>
+      <x:c r="M182" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.426.1"&gt;Режим ограничений&lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.427.1"&gt;, например обязательные лимиты подверженности риску или кредитного плеча, правила концентрации, ограничения ёмкости стратегии или ликвидности, а также дополнительные механизмы, изменяющие торговые действия.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N182" s="2"/>
       <x:c r="O182" s="2"/>
       <x:c r="P182" s="2"/>
@@ -18046,27 +18170,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U182" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V182" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W182" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X182" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y182" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z182" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA182" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB182" s="2"/>
+      <x:c r="AB182" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC182" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18091,16 +18217,18 @@
         <x:v>/*/*[2]/*/*[104]/*[5]</x:v>
       </x:c>
       <x:c r="G183" s="2"/>
-      <x:c r="H183" s="2" t="n">
+      <x:c r="H183" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I183" s="2" t="n">
+      <x:c r="I183" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J183" s="2" t="str">
         <x:v>Cost model class or included components , for example, adding funding or roll mechanics, or changing the slippage model in a way that affects feasibility.</x:v>
       </x:c>
-      <x:c r="K183" s="2"/>
+      <x:c r="K183" s="2" t="str">
+        <x:v>Класс модели издержек или включённые компоненты, например добавление механизма выплат по ставке финансирования или роллирования либо изменение модели проскальзывания, влияющее на осуществимость.</x:v>
+      </x:c>
       <x:c r="L183" s="2" t="str">
         <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;
      &lt;strong class="keyWord"&gt;
@@ -18114,7 +18242,9 @@
     &lt;/li&gt;
    </x:v>
       </x:c>
-      <x:c r="M183" s="2"/>
+      <x:c r="M183" s="2" t="str">
+        <x:v>&lt;li xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="bulletList"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.428.1"&gt;Класс модели издержек или включённые компоненты&lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.429.1"&gt;, например добавление механизма выплат по ставке финансирования или роллирования либо изменение модели проскальзывания, влияющее на осуществимость.&lt;/span&gt;&lt;/li&gt;</x:v>
+      </x:c>
       <x:c r="N183" s="2"/>
       <x:c r="O183" s="2"/>
       <x:c r="P183" s="2"/>
@@ -18125,27 +18255,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U183" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V183" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W183" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X183" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y183" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z183" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA183" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB183" s="2"/>
+      <x:c r="AB183" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC183" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18170,16 +18302,18 @@
         <x:v>/*/*[2]/*/*[105]</x:v>
       </x:c>
       <x:c r="G184" s="2"/>
-      <x:c r="H184" s="2" t="n">
+      <x:c r="H184" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I184" s="2" t="n">
+      <x:c r="I184" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J184" s="2" t="str">
         <x:v>To keep this boundary unambiguous, separate mechanics from parameters :</x:v>
       </x:c>
-      <x:c r="K184" s="2"/>
+      <x:c r="K184" s="2" t="str">
+        <x:v>Чтобы эта граница была однозначной, отделяйте торговый механизм от параметров:</x:v>
+      </x:c>
       <x:c r="L184" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.430.1"&gt;
@@ -18204,7 +18338,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M184" s="2"/>
+      <x:c r="M184" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.430.1"&gt;Чтобы эта граница была однозначной, отделяйте &lt;/span&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.431.1"&gt;торговый механизм &lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.432.1"&gt;от &lt;/span&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.433.1"&gt;параметров&lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.434.1"&gt;:&lt;/span&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N184" s="2"/>
       <x:c r="O184" s="2"/>
       <x:c r="P184" s="2"/>
@@ -18215,27 +18351,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U184" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V184" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W184" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X184" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y184" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z184" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA184" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB184" s="2"/>
+      <x:c r="AB184" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC184" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18260,16 +18398,18 @@
         <x:v>/*/*[2]/*/*[106]/*[1]/*/*[1]</x:v>
       </x:c>
       <x:c r="G185" s="2"/>
-      <x:c r="H185" s="2" t="n">
+      <x:c r="H185" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I185" s="2" t="n">
+      <x:c r="I185" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J185" s="2" t="str">
         <x:v>Same setup version (parameter tuning)</x:v>
       </x:c>
-      <x:c r="K185" s="2"/>
+      <x:c r="K185" s="2" t="str">
+        <x:v>Та же версия параметров торговли (настройка параметров)</x:v>
+      </x:c>
       <x:c r="L185" s="2" t="str">
         <x:v>&lt;th xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-head" scope="col"&gt;
        &lt;p class="normal"&gt;
@@ -18282,7 +18422,9 @@
       &lt;/th&gt;
       </x:v>
       </x:c>
-      <x:c r="M185" s="2"/>
+      <x:c r="M185" s="2" t="str">
+        <x:v>&lt;th xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-head" scope="col"&gt;&lt;p class="normal"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.435.1"&gt;Та же версия параметров торговли (настройка параметров)&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;&lt;/th&gt;</x:v>
+      </x:c>
       <x:c r="N185" s="2"/>
       <x:c r="O185" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18295,27 +18437,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U185" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V185" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W185" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X185" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y185" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z185" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA185" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB185" s="2"/>
+      <x:c r="AB185" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC185" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18340,16 +18484,18 @@
         <x:v>/*/*[2]/*/*[106]/*[1]/*/*[2]</x:v>
       </x:c>
       <x:c r="G186" s="2"/>
-      <x:c r="H186" s="2" t="n">
+      <x:c r="H186" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I186" s="2" t="n">
+      <x:c r="I186" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J186" s="2" t="str">
         <x:v>New setup version (mechanics changed)</x:v>
       </x:c>
-      <x:c r="K186" s="2"/>
+      <x:c r="K186" s="2" t="str">
+        <x:v>Новая версия параметров торговли (изменён торговый механизм)</x:v>
+      </x:c>
       <x:c r="L186" s="2" t="str">
         <x:v>&lt;th xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-head" scope="col"&gt;
        &lt;p class="normal"&gt;
@@ -18362,7 +18508,9 @@
       &lt;/th&gt;
      </x:v>
       </x:c>
-      <x:c r="M186" s="2"/>
+      <x:c r="M186" s="2" t="str">
+        <x:v>&lt;th xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-head" scope="col"&gt;&lt;p class="normal"&gt;&lt;strong class="keyWord"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.436.1"&gt;Новая версия параметров торговли (изменён торговый механизм)&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;&lt;/th&gt;</x:v>
+      </x:c>
       <x:c r="N186" s="2"/>
       <x:c r="O186" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18375,27 +18523,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U186" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V186" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W186" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X186" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y186" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z186" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA186" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB186" s="2"/>
+      <x:c r="AB186" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC186" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18420,16 +18570,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[1]/*[1]</x:v>
       </x:c>
       <x:c r="G187" s="2"/>
-      <x:c r="H187" s="2" t="n">
+      <x:c r="H187" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I187" s="2" t="n">
+      <x:c r="I187" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J187" s="2" t="str">
         <x:v>Threshold 1.8 → 2.0</x:v>
       </x:c>
-      <x:c r="K187" s="2"/>
+      <x:c r="K187" s="2" t="str">
+        <x:v>Порог 1,8 → 2,0</x:v>
+      </x:c>
       <x:c r="L187" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -18440,7 +18592,9 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M187" s="2"/>
+      <x:c r="M187" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.437.1"&gt;Порог 1,8 → 2,0&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N187" s="2"/>
       <x:c r="O187" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18451,29 +18605,31 @@
       <x:c r="S187" s="2"/>
       <x:c r="T187" s="2"/>
       <x:c r="U187" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V187" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W187" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X187" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y187" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z187" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA187" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB187" s="2"/>
+      <x:c r="AB187" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC187" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
@@ -18496,16 +18652,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[1]/*[2]</x:v>
       </x:c>
       <x:c r="G188" s="2"/>
-      <x:c r="H188" s="2" t="n">
+      <x:c r="H188" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I188" s="2" t="n">
+      <x:c r="I188" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J188" s="2" t="str">
         <x:v>Rank selection → threshold gating</x:v>
       </x:c>
-      <x:c r="K188" s="2"/>
+      <x:c r="K188" s="2" t="str">
+        <x:v>Отбор по рангу → применение порогового условия</x:v>
+      </x:c>
       <x:c r="L188" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -18516,7 +18674,9 @@
       &lt;/td&gt;
      </x:v>
       </x:c>
-      <x:c r="M188" s="2"/>
+      <x:c r="M188" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.438.1"&gt;Отбор по рангу → применение порогового условия&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N188" s="2"/>
       <x:c r="O188" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18527,27 +18687,29 @@
       <x:c r="S188" s="2"/>
       <x:c r="T188" s="2"/>
       <x:c r="U188" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V188" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W188" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X188" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y188" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z188" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA188" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB188" s="2"/>
+      <x:c r="AB188" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC188" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18572,16 +18734,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[2]/*[1]</x:v>
       </x:c>
       <x:c r="G189" s="2"/>
-      <x:c r="H189" s="2" t="n">
+      <x:c r="H189" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I189" s="2" t="n">
+      <x:c r="I189" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J189" s="2" t="str">
         <x:v>Top 10% → top 20%</x:v>
       </x:c>
-      <x:c r="K189" s="2"/>
+      <x:c r="K189" s="2" t="str">
+        <x:v>Верхние 10 % по рангу → верхние 20 % по рангу</x:v>
+      </x:c>
       <x:c r="L189" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -18592,7 +18756,9 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M189" s="2"/>
+      <x:c r="M189" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.439.1"&gt;Верхние 10 % по рангу → верхние 20 % по рангу&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N189" s="2"/>
       <x:c r="O189" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18603,29 +18769,31 @@
       <x:c r="S189" s="2"/>
       <x:c r="T189" s="2"/>
       <x:c r="U189" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V189" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W189" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X189" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y189" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z189" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA189" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB189" s="2"/>
+      <x:c r="AB189" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC189" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
@@ -18648,16 +18816,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[2]/*[2]</x:v>
       </x:c>
       <x:c r="G190" s="2"/>
-      <x:c r="H190" s="2" t="n">
+      <x:c r="H190" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I190" s="2" t="n">
+      <x:c r="I190" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J190" s="2" t="str">
         <x:v>Long-only → long/short</x:v>
       </x:c>
-      <x:c r="K190" s="2"/>
+      <x:c r="K190" s="2" t="str">
+        <x:v>Только длинные позиции → длинные/короткие позиции</x:v>
+      </x:c>
       <x:c r="L190" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -18668,7 +18838,9 @@
       &lt;/td&gt;
      </x:v>
       </x:c>
-      <x:c r="M190" s="2"/>
+      <x:c r="M190" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.440.1"&gt;Только длинные позиции → длинные/короткие позиции&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N190" s="2"/>
       <x:c r="O190" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18679,27 +18851,29 @@
       <x:c r="S190" s="2"/>
       <x:c r="T190" s="2"/>
       <x:c r="U190" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V190" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W190" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X190" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y190" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z190" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA190" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB190" s="2"/>
+      <x:c r="AB190" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC190" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18724,16 +18898,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[3]/*[1]</x:v>
       </x:c>
       <x:c r="G191" s="2"/>
-      <x:c r="H191" s="2" t="n">
+      <x:c r="H191" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I191" s="2" t="n">
+      <x:c r="I191" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J191" s="2" t="str">
         <x:v>20-day → 60-day normalization window</x:v>
       </x:c>
-      <x:c r="K191" s="2"/>
+      <x:c r="K191" s="2" t="str">
+        <x:v>20-дневное → 60-дневное окно нормализации</x:v>
+      </x:c>
       <x:c r="L191" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -18744,7 +18920,9 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M191" s="2"/>
+      <x:c r="M191" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.441.1"&gt;20-дневное → 60-дневное окно нормализации&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N191" s="2"/>
       <x:c r="O191" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18755,27 +18933,29 @@
       <x:c r="S191" s="2"/>
       <x:c r="T191" s="2"/>
       <x:c r="U191" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V191" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W191" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X191" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y191" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z191" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA191" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB191" s="2"/>
+      <x:c r="AB191" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC191" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18800,16 +18980,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[3]/*[2]</x:v>
       </x:c>
       <x:c r="G192" s="2"/>
-      <x:c r="H192" s="2" t="n">
+      <x:c r="H192" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I192" s="2" t="n">
+      <x:c r="I192" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J192" s="2" t="str">
         <x:v>Adding a stop rule when none existed</x:v>
       </x:c>
-      <x:c r="K192" s="2"/>
+      <x:c r="K192" s="2" t="str">
+        <x:v>Добавление правила принудительного выхода, которого раньше не было</x:v>
+      </x:c>
       <x:c r="L192" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -18820,7 +19002,9 @@
       &lt;/td&gt;
      </x:v>
       </x:c>
-      <x:c r="M192" s="2"/>
+      <x:c r="M192" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.442.1"&gt;Добавление правила принудительного выхода, которого раньше не было&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N192" s="2"/>
       <x:c r="O192" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18831,27 +19015,29 @@
       <x:c r="S192" s="2"/>
       <x:c r="T192" s="2"/>
       <x:c r="U192" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V192" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W192" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X192" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y192" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z192" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA192" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB192" s="2"/>
+      <x:c r="AB192" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC192" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18876,16 +19062,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[4]/*[1]</x:v>
       </x:c>
       <x:c r="G193" s="2"/>
-      <x:c r="H193" s="2" t="n">
+      <x:c r="H193" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I193" s="2" t="n">
+      <x:c r="I193" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J193" s="2" t="str">
         <x:v>Different lookback horizon</x:v>
       </x:c>
-      <x:c r="K193" s="2"/>
+      <x:c r="K193" s="2" t="str">
+        <x:v>Другой ретроспективный горизонт</x:v>
+      </x:c>
       <x:c r="L193" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -18896,7 +19084,9 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M193" s="2"/>
+      <x:c r="M193" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.443.1"&gt;Другой ретроспективный горизонт&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N193" s="2"/>
       <x:c r="O193" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18907,27 +19097,29 @@
       <x:c r="S193" s="2"/>
       <x:c r="T193" s="2"/>
       <x:c r="U193" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V193" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W193" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X193" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y193" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z193" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA193" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB193" s="2"/>
+      <x:c r="AB193" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC193" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -18952,16 +19144,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[4]/*[2]</x:v>
       </x:c>
       <x:c r="G194" s="2"/>
-      <x:c r="H194" s="2" t="n">
+      <x:c r="H194" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I194" s="2" t="n">
+      <x:c r="I194" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J194" s="2" t="str">
         <x:v>Changing rebalance cadence or execution delay</x:v>
       </x:c>
-      <x:c r="K194" s="2"/>
+      <x:c r="K194" s="2" t="str">
+        <x:v>Изменение периодичности ребалансировки или задержки исполнения</x:v>
+      </x:c>
       <x:c r="L194" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -18972,7 +19166,9 @@
       &lt;/td&gt;
      </x:v>
       </x:c>
-      <x:c r="M194" s="2"/>
+      <x:c r="M194" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.444.1"&gt;Изменение периодичности ребалансировки или задержки исполнения&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N194" s="2"/>
       <x:c r="O194" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -18983,27 +19179,29 @@
       <x:c r="S194" s="2"/>
       <x:c r="T194" s="2"/>
       <x:c r="U194" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V194" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W194" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X194" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y194" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z194" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA194" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB194" s="2"/>
+      <x:c r="AB194" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC194" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -19028,16 +19226,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[5]/*[1]</x:v>
       </x:c>
       <x:c r="G195" s="2"/>
-      <x:c r="H195" s="2" t="n">
+      <x:c r="H195" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I195" s="2" t="n">
+      <x:c r="I195" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J195" s="2" t="str">
         <x:v>Cost assumption 10 bps → 15 bps per leg</x:v>
       </x:c>
-      <x:c r="K195" s="2"/>
+      <x:c r="K195" s="2" t="str">
+        <x:v>Допущение об издержках: 10 б.п. → 15 б.п. на одну сторону сделки</x:v>
+      </x:c>
       <x:c r="L195" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -19048,7 +19248,9 @@
       &lt;/td&gt;
       </x:v>
       </x:c>
-      <x:c r="M195" s="2"/>
+      <x:c r="M195" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.445.1"&gt;Допущение об издержках: 10 б.п. → 15 б.п. на одну сторону сделки&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N195" s="2"/>
       <x:c r="O195" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -19059,29 +19261,31 @@
       <x:c r="S195" s="2"/>
       <x:c r="T195" s="2"/>
       <x:c r="U195" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V195" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W195" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X195" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y195" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z195" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA195" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB195" s="2"/>
+      <x:c r="AB195" s="2" t="str">
+        <x:v>Human acceptance corrections CH06-ERR-068–080; independently rechecked and verified</x:v>
+      </x:c>
       <x:c r="AC195" s="2" t="str">
-        <x:v>v0.1</x:v>
+        <x:v>v0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
@@ -19104,16 +19308,18 @@
         <x:v>/*/*[2]/*/*[106]/*[2]/*[5]/*[2]</x:v>
       </x:c>
       <x:c r="G196" s="2"/>
-      <x:c r="H196" s="2" t="n">
+      <x:c r="H196" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I196" s="2" t="n">
+      <x:c r="I196" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J196" s="2" t="str">
         <x:v>Adding funding/roll as a cost component</x:v>
       </x:c>
-      <x:c r="K196" s="2"/>
+      <x:c r="K196" s="2" t="str">
+        <x:v>Добавление платежей по ставке финансирования или роллирования как компонента издержек</x:v>
+      </x:c>
       <x:c r="L196" s="2" t="str">
         <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;
        &lt;p class="normal"&gt;
@@ -19124,7 +19330,9 @@
       &lt;/td&gt;
      </x:v>
       </x:c>
-      <x:c r="M196" s="2"/>
+      <x:c r="M196" s="2" t="str">
+        <x:v>&lt;td xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="table-cell"&gt;&lt;p class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.446.1"&gt;Добавление платежей по ставке финансирования или роллирования как компонента издержек&lt;/span&gt;&lt;/p&gt;&lt;/td&gt;</x:v>
+      </x:c>
       <x:c r="N196" s="2"/>
       <x:c r="O196" s="2" t="str">
         <x:v>CH06-TABLE-002</x:v>
@@ -19135,27 +19343,29 @@
       <x:c r="S196" s="2"/>
       <x:c r="T196" s="2"/>
       <x:c r="U196" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V196" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W196" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X196" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y196" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z196" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA196" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB196" s="2"/>
+      <x:c r="AB196" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC196" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -19180,16 +19390,18 @@
         <x:v>/*/*[2]/*/*[107]</x:v>
       </x:c>
       <x:c r="G197" s="2"/>
-      <x:c r="H197" s="2" t="n">
+      <x:c r="H197" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I197" s="2" t="n">
+      <x:c r="I197" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J197" s="2" t="str">
         <x:v>Table 6.2: Comparing mechanics and parameters</x:v>
       </x:c>
-      <x:c r="K197" s="2"/>
+      <x:c r="K197" s="2" t="str">
+        <x:v>Таблица 6.2. Сопоставление механизмов и параметров</x:v>
+      </x:c>
       <x:c r="L197" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="packt_figref"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.447.1"&gt;
@@ -19198,7 +19410,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M197" s="2"/>
+      <x:c r="M197" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="packt_figref"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.447.1"&gt;Таблица 6.2. Сопоставление механизмов и параметров&lt;/span&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N197" s="2"/>
       <x:c r="O197" s="2"/>
       <x:c r="P197" s="2"/>
@@ -19207,27 +19421,29 @@
       <x:c r="S197" s="2"/>
       <x:c r="T197" s="2"/>
       <x:c r="U197" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V197" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W197" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X197" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y197" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z197" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA197" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB197" s="2"/>
+      <x:c r="AB197" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC197" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -19252,16 +19468,18 @@
         <x:v>/*/*[2]/*/*[108]</x:v>
       </x:c>
       <x:c r="G198" s="2"/>
-      <x:c r="H198" s="2" t="n">
+      <x:c r="H198" s="2" t="str">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="I198" s="2" t="n">
+      <x:c r="I198" s="2" t="str">
         <x:v>135</x:v>
       </x:c>
       <x:c r="J198" s="2" t="str">
         <x:v>Results across setup versions can still be informative, but they are not direct competitors within a single research program. The next section defines what counts as improvement within a fixed setup, separating development diagnostics from strategy-level evaluation.</x:v>
       </x:c>
-      <x:c r="K198" s="2"/>
+      <x:c r="K198" s="2" t="str">
+        <x:v>Результаты разных версий параметров торговли по-прежнему могут быть информативными, однако они не подлежат прямому сопоставлению в рамках одной исследовательской программы. В следующем разделе определяется, что считается улучшением при фиксированных параметрах торговли, с отделением диагностики процесса разработки от оценки стратегии.</x:v>
+      </x:c>
       <x:c r="L198" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.448.1"&gt;
@@ -19273,7 +19491,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M198" s="2"/>
+      <x:c r="M198" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.448.1"&gt;Результаты разных версий параметров торговли по-прежнему могут быть информативными, однако они не подлежат прямому сопоставлению в рамках одной исследовательской программы. В следующем разделе определяется, что считается улучшением при фиксированных параметрах торговли, с отделением диагностики процесса разработки от оценки стратегии.&lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.448.2"/&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N198" s="2"/>
       <x:c r="O198" s="2"/>
       <x:c r="P198" s="2"/>
@@ -19282,27 +19502,29 @@
       <x:c r="S198" s="2"/>
       <x:c r="T198" s="2"/>
       <x:c r="U198" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V198" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W198" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X198" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y198" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z198" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA198" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB198" s="2"/>
+      <x:c r="AB198" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC198" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -19327,16 +19549,18 @@
         <x:v>/*/*[2]/*/*[109]/*</x:v>
       </x:c>
       <x:c r="G199" s="2"/>
-      <x:c r="H199" s="2" t="n">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="I199" s="2" t="n">
-        <x:v>123</x:v>
+      <x:c r="H199" s="2" t="str">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="I199" s="2" t="str">
+        <x:v>135</x:v>
       </x:c>
       <x:c r="J199" s="2" t="str">
         <x:v>Implementation : 02_case_study_overview inventories the trading setup for each of the nine case studies (universe, decision schedule, mapping, constraints, cost model) and is the source of the worked examples above.</x:v>
       </x:c>
-      <x:c r="K199" s="2"/>
+      <x:c r="K199" s="2" t="str">
+        <x:v>Реализация: 02_case_study_overview систематизирует параметры торговли для каждого из девяти практических примеров (совокупность активов, график принятия решений, преобразование, ограничения, модель издержек) и служит источником рассмотренных выше примеров.</x:v>
+      </x:c>
       <x:c r="L199" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
      &lt;strong class="screenText"&gt;
@@ -19358,7 +19582,9 @@
     &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M199" s="2"/>
+      <x:c r="M199" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;strong class="screenText"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.449.1"&gt;Реализация&lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.450.1"&gt;: &lt;/span&gt;&lt;code class="inlineCode"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.451.1"&gt;02_case_study_overview &lt;/span&gt;&lt;/code&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.452.1"&gt;систематизирует параметры торговли для каждого из девяти практических примеров (совокупность активов, график принятия решений, преобразование, ограничения, модель издержек) и служит источником рассмотренных выше примеров.&lt;/span&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N199" s="2"/>
       <x:c r="O199" s="2"/>
       <x:c r="P199" s="2"/>
@@ -19369,27 +19595,29 @@
         <x:v>strong,code</x:v>
       </x:c>
       <x:c r="U199" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V199" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W199" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X199" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y199" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z199" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA199" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB199" s="2"/>
+      <x:c r="AB199" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC199" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -19416,16 +19644,18 @@
       <x:c r="G200" s="2" t="str">
         <x:v>_idParaDest-282</x:v>
       </x:c>
-      <x:c r="H200" s="2" t="n">
+      <x:c r="H200" s="2" t="str">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="I200" s="2" t="n">
+      <x:c r="I200" s="2" t="str">
         <x:v>136</x:v>
       </x:c>
       <x:c r="J200" s="2" t="str">
         <x:v>6.4 Setting objectives and evaluation metrics</x:v>
       </x:c>
-      <x:c r="K200" s="2"/>
+      <x:c r="K200" s="2" t="str">
+        <x:v>6.4 Постановка целей и определение метрик оценки</x:v>
+      </x:c>
       <x:c r="L200" s="2" t="str">
         <x:v>&lt;h1 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-1" id="_idParaDest-282"&gt;
     &lt;a id="_idTextAnchor274"&gt;
@@ -19436,7 +19666,9 @@
    &lt;/h1&gt;
    </x:v>
       </x:c>
-      <x:c r="M200" s="2"/>
+      <x:c r="M200" s="2" t="str">
+        <x:v>&lt;h1 xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="heading-1" id="_idParaDest-282"&gt;&lt;a id="_idTextAnchor274"/&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.453.1"&gt;6.4 Постановка целей и определение метрик оценки&lt;/span&gt;&lt;/h1&gt;</x:v>
+      </x:c>
       <x:c r="N200" s="2"/>
       <x:c r="O200" s="2"/>
       <x:c r="P200" s="2"/>
@@ -19447,27 +19679,29 @@
         <x:v>a</x:v>
       </x:c>
       <x:c r="U200" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V200" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W200" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X200" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y200" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z200" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA200" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB200" s="2"/>
+      <x:c r="AB200" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC200" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
@@ -19492,16 +19726,18 @@
         <x:v>/*/*[2]/*/*[111]</x:v>
       </x:c>
       <x:c r="G201" s="2"/>
-      <x:c r="H201" s="2" t="n">
+      <x:c r="H201" s="2" t="str">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="I201" s="2" t="n">
+      <x:c r="I201" s="2" t="str">
         <x:v>136</x:v>
       </x:c>
       <x:c r="J201" s="2" t="str">
         <x:v>A research program needs an explicit definition of “better” before running large experiment grids. Here, “better” means economic value under a fixed trading setup : portfolio returns produced by mapping model outputs into positions and applying constraints and costs. This section specifies three important rules:</x:v>
       </x:c>
-      <x:c r="K201" s="2"/>
+      <x:c r="K201" s="2" t="str">
+        <x:v>До запуска крупных сеток экспериментов исследовательская программа должна явно определить, что означает «лучше». Здесь под «лучше» понимается экономическая ценность при фиксированных параметрах торговли: доходность портфеля, получаемая путём преобразования выходных данных модели в позиции с последующим применением ограничений и учётом издержек. В этом разделе устанавливаются три важных правила:</x:v>
+      </x:c>
       <x:c r="L201" s="2" t="str">
         <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;
     &lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.454.1"&gt;
@@ -19524,7 +19760,9 @@
    &lt;/p&gt;
    </x:v>
       </x:c>
-      <x:c r="M201" s="2"/>
+      <x:c r="M201" s="2" t="str">
+        <x:v>&lt;p xmlns="http://www.w3.org/1999/xhtml" xmlns:epub="http://www.idpf.org/2007/ops" class="normal"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.454.1"&gt;До запуска крупных сеток экспериментов исследовательская программа должна явно определить, что означает «лучше». &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.454.2"&gt;Здесь под «лучше» понимается &lt;/span&gt;&lt;strong class="screenText"&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.455.1"&gt;экономическая ценность при фиксированных параметрах торговли&lt;/span&gt;&lt;/strong&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.456.1"&gt;: доходность портфеля, получаемая путём преобразования выходных данных модели в позиции с последующим применением ограничений и учётом издержек. &lt;/span&gt;&lt;span xmlns="http://www.w3.org/1999/xhtml" class="koboSpan" id="kobo.456.2"&gt;В этом разделе устанавливаются три важных правила:&lt;/span&gt;&lt;/p&gt;</x:v>
+      </x:c>
       <x:c r="N201" s="2"/>
       <x:c r="O201" s="2"/>
       <x:c r="P201" s="2"/>
@@ -19535,27 +19773,29 @@
         <x:v>strong</x:v>
       </x:c>
       <x:c r="U201" s="2" t="str">
-        <x:v>PENDING_TRANSLATION</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="V201" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="W201" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="X201" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Y201" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="Z201" s="2" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>QA_PASS</x:v>
       </x:c>
       <x:c r="AA201" s="2" t="str">
         <x:v>CH06-BATCH-005</x:v>
       </x:c>
-      <x:c r="AB201" s="2"/>
+      <x:c r="AB201" s="2" t="str">
+        <x:v>Autonomous translation run CH06-B0161-B0200-20260816T184256Z</x:v>
+      </x:c>
       <x:c r="AC201" s="2" t="str">
         <x:v>v0.1</x:v>
       </x:c>
